--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_transportation_railroads.xlsx
@@ -644,10 +644,10 @@
         <v>0.1684753838009529</v>
       </c>
       <c r="X2">
-        <v>0.1221476857266876</v>
+        <v>0.1221120306047457</v>
       </c>
       <c r="Y2">
-        <v>0.04632769807426529</v>
+        <v>0.04636335319620719</v>
       </c>
       <c r="Z2">
         <v>1.929636816233914</v>
@@ -656,10 +656,10 @@
         <v>0.1360871560864034</v>
       </c>
       <c r="AB2">
-        <v>0.0679768645730226</v>
+        <v>0.06796718915966207</v>
       </c>
       <c r="AC2">
-        <v>0.06811029151338077</v>
+        <v>0.0681199669267413</v>
       </c>
       <c r="AD2">
         <v>1895.5</v>
@@ -775,10 +775,10 @@
         <v>0.1684753838009529</v>
       </c>
       <c r="X3">
-        <v>0.1221476857266876</v>
+        <v>0.1221120306047457</v>
       </c>
       <c r="Y3">
-        <v>0.04632769807426529</v>
+        <v>0.04636335319620719</v>
       </c>
       <c r="Z3">
         <v>1.929636816233914</v>
@@ -787,10 +787,10 @@
         <v>0.1360871560864034</v>
       </c>
       <c r="AB3">
-        <v>0.0679768645730226</v>
+        <v>0.06796718915966207</v>
       </c>
       <c r="AC3">
-        <v>0.06811029151338077</v>
+        <v>0.0681199669267413</v>
       </c>
       <c r="AD3">
         <v>1895.5</v>
@@ -1127,49 +1127,49 @@
         <v>1.48528015194682</v>
       </c>
       <c r="F2">
-        <v>4.516162747544</v>
+        <v>4.58401874697122</v>
       </c>
       <c r="G2">
         <v>3.40031315998142</v>
       </c>
       <c r="H2">
-        <v>1.72666581661689</v>
+        <v>1.77333246030924</v>
       </c>
       <c r="I2">
         <v>0.72863889299563</v>
       </c>
       <c r="J2">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="K2">
         <v>1204.3</v>
       </c>
       <c r="L2">
-        <v>2757.21661726515</v>
+        <v>2731.9563574366</v>
       </c>
       <c r="M2">
         <v>3852.69781514233</v>
       </c>
       <c r="N2">
-        <v>3813.97580886781</v>
+        <v>3833.09552719068</v>
       </c>
       <c r="O2">
         <v>3233.69781514233</v>
       </c>
       <c r="P2">
-        <v>1642.05919160266</v>
+        <v>1686.43916975409</v>
       </c>
       <c r="Q2">
-        <v>0.0679768645730226</v>
+        <v>0.0679671891596621</v>
       </c>
       <c r="R2">
-        <v>0.069557742540794</v>
+        <v>0.068763479811401</v>
       </c>
       <c r="S2">
         <v>0.0478024624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.122147685726688</v>
+        <v>0.122112030604746</v>
       </c>
       <c r="X2">
-        <v>0.0822906054237155</v>
+        <v>0.0827597484880303</v>
       </c>
       <c r="Y2">
         <v>1.48746351599436</v>
       </c>
       <c r="Z2">
-        <v>0.710937649618234</v>
+        <v>0.720414291175396</v>
       </c>
       <c r="AA2">
         <v>1895.5</v>
@@ -1224,7 +1224,7 @@
         <v>1204.3</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07113232112059591</v>
+        <v>0.07112049067688266</v>
       </c>
       <c r="C2">
-        <v>4361.474145438409</v>
+        <v>4361.524691136642</v>
       </c>
       <c r="D2">
-        <v>3776.17414543841</v>
+        <v>3776.224691136642</v>
       </c>
       <c r="E2">
         <v>-3233.697815142332</v>
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07113232112059591</v>
+        <v>0.07112049067688266</v>
       </c>
       <c r="T2">
         <v>0.4935434922969562</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07104326494276343</v>
+        <v>0.07102096407515947</v>
       </c>
       <c r="C3">
-        <v>4319.212178360601</v>
+        <v>4319.511981692611</v>
       </c>
       <c r="D3">
-        <v>3778.292156512024</v>
+        <v>3778.591959844035</v>
       </c>
       <c r="E3">
         <v>-3189.317836990908</v>
@@ -1527,37 +1527,37 @@
         <v>473.4</v>
       </c>
       <c r="M3">
-        <v>2.557911788205225</v>
+        <v>2.495779818793232</v>
       </c>
       <c r="N3">
-        <v>470.8420882117948</v>
+        <v>470.9042201812068</v>
       </c>
       <c r="O3">
-        <v>117.7105220529487</v>
+        <v>117.7260550453017</v>
       </c>
       <c r="P3">
-        <v>353.1315661588461</v>
+        <v>353.1781651359051</v>
       </c>
       <c r="Q3">
-        <v>1147.731566158846</v>
+        <v>1147.778165135905</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07132423264423679</v>
+        <v>0.07131231257594996</v>
       </c>
       <c r="T3">
         <v>0.4972824581476907</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>185.072840346916</v>
+        <v>189.6801939158639</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07095420876493093</v>
+        <v>0.07092143747343627</v>
       </c>
       <c r="C4">
-        <v>4276.95258855051</v>
+        <v>4277.502242133505</v>
       </c>
       <c r="D4">
-        <v>3780.412544853357</v>
+        <v>3780.962198436352</v>
       </c>
       <c r="E4">
         <v>-3144.937858839485</v>
@@ -1609,37 +1609,37 @@
         <v>473.4</v>
       </c>
       <c r="M4">
-        <v>5.11582357641045</v>
+        <v>4.991559637586464</v>
       </c>
       <c r="N4">
-        <v>468.2841764235895</v>
+        <v>468.4084403624135</v>
       </c>
       <c r="O4">
-        <v>117.0710441058974</v>
+        <v>117.1021100906034</v>
       </c>
       <c r="P4">
-        <v>351.2131323176922</v>
+        <v>351.3063302718101</v>
       </c>
       <c r="Q4">
-        <v>1145.813132317692</v>
+        <v>1145.90633027181</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07152006072958461</v>
+        <v>0.07150804920765128</v>
       </c>
       <c r="T4">
         <v>0.5010977294239504</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>92.536420173458</v>
+        <v>94.84009695793196</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07086515258709844</v>
+        <v>0.07082191087171306</v>
       </c>
       <c r="C5">
-        <v>4234.695380012775</v>
+        <v>4235.495478051688</v>
       </c>
       <c r="D5">
-        <v>3782.535314467044</v>
+        <v>3783.335412505958</v>
       </c>
       <c r="E5">
         <v>-3100.557880688062</v>
@@ -1691,37 +1691,37 @@
         <v>473.4</v>
       </c>
       <c r="M5">
-        <v>7.673735364615673</v>
+        <v>7.487339456379696</v>
       </c>
       <c r="N5">
-        <v>465.7262646353843</v>
+        <v>465.9126605436203</v>
       </c>
       <c r="O5">
-        <v>116.4315661588461</v>
+        <v>116.4781651359051</v>
       </c>
       <c r="P5">
-        <v>349.2946984765383</v>
+        <v>349.4344954077152</v>
       </c>
       <c r="Q5">
-        <v>1143.894698476538</v>
+        <v>1144.034495407715</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07171992650741385</v>
+        <v>0.0717078216461918</v>
       </c>
       <c r="T5">
         <v>0.5049916660873495</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>61.69094678230535</v>
+        <v>63.22673130528798</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07077609640926598</v>
+        <v>0.07072238426998986</v>
       </c>
       <c r="C6">
-        <v>4192.440556761027</v>
+        <v>4193.491695053573</v>
       </c>
       <c r="D6">
-        <v>3784.660469366721</v>
+        <v>3785.711607659267</v>
       </c>
       <c r="E6">
         <v>-3056.177902536639</v>
@@ -1773,37 +1773,37 @@
         <v>473.4</v>
       </c>
       <c r="M6">
-        <v>10.2316471528209</v>
+        <v>9.983119275172928</v>
       </c>
       <c r="N6">
-        <v>463.1683528471791</v>
+        <v>463.416880724827</v>
       </c>
       <c r="O6">
-        <v>115.7920882117948</v>
+        <v>115.8542201812068</v>
       </c>
       <c r="P6">
-        <v>347.3762646353843</v>
+        <v>347.5626605436203</v>
       </c>
       <c r="Q6">
-        <v>1141.976264635384</v>
+        <v>1142.16266054362</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07192395615561453</v>
+        <v>0.07191175601053525</v>
       </c>
       <c r="T6">
         <v>0.5089667264312361</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.26821008672899</v>
+        <v>47.42004847896598</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07068704023143349</v>
+        <v>0.07062285766826666</v>
       </c>
       <c r="C7">
-        <v>4150.188122817931</v>
+        <v>4151.490898759669</v>
       </c>
       <c r="D7">
-        <v>3786.788013575047</v>
+        <v>3788.090789516786</v>
       </c>
       <c r="E7">
         <v>-3011.797924385215</v>
@@ -1855,37 +1855,37 @@
         <v>473.4</v>
       </c>
       <c r="M7">
-        <v>12.78955894102612</v>
+        <v>12.47889909396616</v>
       </c>
       <c r="N7">
-        <v>460.6104410589738</v>
+        <v>460.9211009060338</v>
       </c>
       <c r="O7">
-        <v>115.1526102647435</v>
+        <v>115.2302752265085</v>
       </c>
       <c r="P7">
-        <v>345.4578307942304</v>
+        <v>345.6908256795253</v>
       </c>
       <c r="Q7">
-        <v>1140.057830794231</v>
+        <v>1140.290825679525</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07213228116482996</v>
+        <v>0.0721199837299175</v>
       </c>
       <c r="T7">
         <v>0.5130254722560466</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.01456806938319</v>
+        <v>37.93603878317278</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.070597984053601</v>
+        <v>0.07052333106654343</v>
       </c>
       <c r="C8">
-        <v>4107.938082215195</v>
+        <v>4109.493094804621</v>
       </c>
       <c r="D8">
-        <v>3788.917951123736</v>
+        <v>3790.472963713162</v>
       </c>
       <c r="E8">
         <v>-2967.417946233792</v>
@@ -1937,37 +1937,37 @@
         <v>473.4</v>
       </c>
       <c r="M8">
-        <v>15.34747072923135</v>
+        <v>14.97467891275939</v>
       </c>
       <c r="N8">
-        <v>458.0525292707686</v>
+        <v>458.4253210872406</v>
       </c>
       <c r="O8">
-        <v>114.5131323176922</v>
+        <v>114.6063302718102</v>
       </c>
       <c r="P8">
-        <v>343.5393969530764</v>
+        <v>343.8189908154304</v>
       </c>
       <c r="Q8">
-        <v>1138.139396953076</v>
+        <v>1138.41899081543</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07234503862104996</v>
+        <v>0.07233264182630789</v>
       </c>
       <c r="T8">
         <v>0.5171705743750019</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.84547339115267</v>
+        <v>31.61336565264399</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.0705089278757685</v>
+        <v>0.07042380446482024</v>
       </c>
       <c r="C9">
-        <v>4065.690438993608</v>
+        <v>4067.498288837257</v>
       </c>
       <c r="D9">
-        <v>3791.050286053572</v>
+        <v>3792.858135897221</v>
       </c>
       <c r="E9">
         <v>-2923.037968082368</v>
@@ -2019,37 +2019,37 @@
         <v>473.4</v>
       </c>
       <c r="M9">
-        <v>17.90538251743657</v>
+        <v>17.47045873155263</v>
       </c>
       <c r="N9">
-        <v>455.4946174825634</v>
+        <v>455.9295412684473</v>
       </c>
       <c r="O9">
-        <v>113.8736543706408</v>
+        <v>113.9823853171118</v>
       </c>
       <c r="P9">
-        <v>341.6209631119225</v>
+        <v>341.9471559513355</v>
       </c>
       <c r="Q9">
-        <v>1136.220963111923</v>
+        <v>1136.547155951336</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07256237150643599</v>
+        <v>0.07254987321509378</v>
       </c>
       <c r="T9">
         <v>0.5214048184750101</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.43897719241657</v>
+        <v>27.09717055940913</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07041987169793602</v>
+        <v>0.07032427786309704</v>
       </c>
       <c r="C10">
-        <v>4023.445197203057</v>
+        <v>4025.506486520632</v>
       </c>
       <c r="D10">
-        <v>3793.185022414444</v>
+        <v>3795.246311732019</v>
       </c>
       <c r="E10">
         <v>-2878.657989930945</v>
@@ -2101,37 +2101,37 @@
         <v>473.4</v>
       </c>
       <c r="M10">
-        <v>20.4632943056418</v>
+        <v>19.96623855034586</v>
       </c>
       <c r="N10">
-        <v>452.9367056943582</v>
+        <v>453.4337614496541</v>
       </c>
       <c r="O10">
-        <v>113.2341764235895</v>
+        <v>113.3584403624135</v>
       </c>
       <c r="P10">
-        <v>339.7025292707687</v>
+        <v>340.0753210872406</v>
       </c>
       <c r="Q10">
-        <v>1134.302529270769</v>
+        <v>1134.675321087241</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.0727844290197652</v>
+        <v>0.072771827025375</v>
       </c>
       <c r="T10">
         <v>0.5257311113598011</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.1341050433645</v>
+        <v>23.71002423948299</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2150,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07033081552010355</v>
+        <v>0.07022475126137384</v>
       </c>
       <c r="C11">
-        <v>3981.202360902556</v>
+        <v>3983.517693532073</v>
       </c>
       <c r="D11">
-        <v>3795.322164265367</v>
+        <v>3797.637496894883</v>
       </c>
       <c r="E11">
         <v>-2834.278011779522</v>
@@ -2183,37 +2183,37 @@
         <v>473.4</v>
       </c>
       <c r="M11">
-        <v>23.02120609384702</v>
+        <v>22.46201836913909</v>
       </c>
       <c r="N11">
-        <v>450.378793906153</v>
+        <v>450.9379816308609</v>
       </c>
       <c r="O11">
-        <v>112.5946984765382</v>
+        <v>112.7344954077152</v>
       </c>
       <c r="P11">
-        <v>337.7840954296147</v>
+        <v>338.2034862231457</v>
       </c>
       <c r="Q11">
-        <v>1132.384095429615</v>
+        <v>1132.803486223146</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07301136691800275</v>
+        <v>0.07299865894137669</v>
       </c>
       <c r="T11">
         <v>0.5301524876046974</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.56364892743511</v>
+        <v>21.07557710176266</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07024175934227107</v>
+        <v>0.07012522465965064</v>
       </c>
       <c r="C12">
-        <v>3938.961934160276</v>
+        <v>3941.531915563225</v>
       </c>
       <c r="D12">
-        <v>3797.461715674509</v>
+        <v>3800.031697077458</v>
       </c>
       <c r="E12">
         <v>-2789.898033628098</v>
@@ -2265,37 +2265,37 @@
         <v>473.4</v>
       </c>
       <c r="M12">
-        <v>25.57911788205225</v>
+        <v>24.95779818793232</v>
       </c>
       <c r="N12">
-        <v>447.8208821179477</v>
+        <v>448.4422018120677</v>
       </c>
       <c r="O12">
-        <v>111.9552205294869</v>
+        <v>112.1105504530169</v>
       </c>
       <c r="P12">
-        <v>335.8656615884608</v>
+        <v>336.3316513590507</v>
       </c>
       <c r="Q12">
-        <v>1130.465661588461</v>
+        <v>1130.931651359051</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07324334788064557</v>
+        <v>0.07323053156662288</v>
       </c>
       <c r="T12">
         <v>0.5346721166550358</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.5072840346916</v>
+        <v>18.96801939158639</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07015270316443858</v>
+        <v>0.07002569805792745</v>
       </c>
       <c r="C13">
-        <v>3896.723921053563</v>
+        <v>3899.549158320093</v>
       </c>
       <c r="D13">
-        <v>3799.603680719219</v>
+        <v>3802.42891798575</v>
       </c>
       <c r="E13">
         <v>-2745.518055476675</v>
@@ -2347,37 +2347,37 @@
         <v>473.4</v>
       </c>
       <c r="M13">
-        <v>28.13702967025747</v>
+        <v>27.45357800672555</v>
       </c>
       <c r="N13">
-        <v>445.2629703297425</v>
+        <v>445.9464219932744</v>
       </c>
       <c r="O13">
-        <v>111.3157425824356</v>
+        <v>111.4866054983186</v>
       </c>
       <c r="P13">
-        <v>333.9472277473069</v>
+        <v>334.4598164949558</v>
       </c>
       <c r="Q13">
-        <v>1128.547227747307</v>
+        <v>1129.059816494956</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07348054189862867</v>
+        <v>0.07346761481266111</v>
       </c>
       <c r="T13">
         <v>0.5392933104031347</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.82480366790146</v>
+        <v>17.24365399235127</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.0700636469866061</v>
+        <v>0.06992617145620425</v>
       </c>
       <c r="C14">
-        <v>3854.488325668967</v>
+        <v>3857.569427523094</v>
       </c>
       <c r="D14">
-        <v>3801.748063486047</v>
+        <v>3804.829165340173</v>
       </c>
       <c r="E14">
         <v>-2701.138077325252</v>
@@ -2429,37 +2429,37 @@
         <v>473.4</v>
       </c>
       <c r="M14">
-        <v>30.69494145846269</v>
+        <v>29.94935782551878</v>
       </c>
       <c r="N14">
-        <v>442.7050585415373</v>
+        <v>443.4506421744812</v>
       </c>
       <c r="O14">
-        <v>110.6762646353843</v>
+        <v>110.8626605436203</v>
       </c>
       <c r="P14">
-        <v>332.0287939061529</v>
+        <v>332.5879816308609</v>
       </c>
       <c r="Q14">
-        <v>1126.628793906153</v>
+        <v>1127.187981630861</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07372312668974776</v>
+        <v>0.07371008631429112</v>
       </c>
       <c r="T14">
         <v>0.5440195312818721</v>
       </c>
       <c r="U14">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.42273669557633</v>
+        <v>15.80668282632199</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06997459080877361</v>
+        <v>0.06982664485448105</v>
       </c>
       <c r="C15">
-        <v>3812.255152102271</v>
+        <v>3815.592728907091</v>
       </c>
       <c r="D15">
-        <v>3803.894868070775</v>
+        <v>3807.232444875594</v>
       </c>
       <c r="E15">
         <v>-2656.758099173829</v>
@@ -2511,37 +2511,37 @@
         <v>473.4</v>
       </c>
       <c r="M15">
-        <v>33.25285324666792</v>
+        <v>32.44513764431201</v>
       </c>
       <c r="N15">
-        <v>440.147146753332</v>
+        <v>440.954862355688</v>
       </c>
       <c r="O15">
-        <v>110.036786688333</v>
+        <v>110.238715588922</v>
       </c>
       <c r="P15">
-        <v>330.110360064999</v>
+        <v>330.716146766766</v>
       </c>
       <c r="Q15">
-        <v>1124.710360064999</v>
+        <v>1125.316146766766</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07397128814273166</v>
+        <v>0.07395813187342985</v>
       </c>
       <c r="T15">
         <v>0.5488544009164426</v>
       </c>
       <c r="U15">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.23637233437815</v>
+        <v>14.59078414737415</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06988553463094113</v>
+        <v>0.06972711825275785</v>
       </c>
       <c r="C16">
-        <v>3770.024404458513</v>
+        <v>3773.61906822145</v>
       </c>
       <c r="D16">
-        <v>3806.04409857844</v>
+        <v>3809.638762341377</v>
       </c>
       <c r="E16">
         <v>-2612.378121022405</v>
@@ -2593,37 +2593,37 @@
         <v>473.4</v>
       </c>
       <c r="M16">
-        <v>35.81076503487315</v>
+        <v>34.94091746310525</v>
       </c>
       <c r="N16">
-        <v>437.5892349651268</v>
+        <v>438.4590825368947</v>
       </c>
       <c r="O16">
-        <v>109.3973087412817</v>
+        <v>109.6147706342237</v>
       </c>
       <c r="P16">
-        <v>328.1919262238451</v>
+        <v>328.8443119026711</v>
       </c>
       <c r="Q16">
-        <v>1122.791926223845</v>
+        <v>1123.444311902671</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07422522079229657</v>
+        <v>0.07421194593394391</v>
       </c>
       <c r="T16">
         <v>0.5538017093797241</v>
       </c>
       <c r="U16">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.21948859620828</v>
+        <v>13.54858527970456</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06992022845310865</v>
+        <v>0.06979634165103464</v>
       </c>
       <c r="C17">
-        <v>3724.806856871751</v>
+        <v>3727.565110344381</v>
       </c>
       <c r="D17">
-        <v>3805.206529143101</v>
+        <v>3807.964782615731</v>
       </c>
       <c r="E17">
         <v>-2567.998142870982</v>
@@ -2675,37 +2675,37 @@
         <v>473.4</v>
       </c>
       <c r="M17">
-        <v>39.10094646257685</v>
+        <v>38.4352467903055</v>
       </c>
       <c r="N17">
-        <v>434.2990535374231</v>
+        <v>434.9647532096945</v>
       </c>
       <c r="O17">
-        <v>108.5747633843558</v>
+        <v>108.7411883024236</v>
       </c>
       <c r="P17">
-        <v>325.7242901530673</v>
+        <v>326.2235649072709</v>
       </c>
       <c r="Q17">
-        <v>1120.324290153067</v>
+        <v>1120.823564907271</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.0744851283277336</v>
+        <v>0.07447173208999948</v>
       </c>
       <c r="T17">
         <v>0.558865425100965</v>
       </c>
       <c r="U17">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.1071238122864</v>
+        <v>12.31681957404279</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06983942227527616</v>
+        <v>0.06970806504931144</v>
       </c>
       <c r="C18">
-        <v>3682.378251808271</v>
+        <v>3685.32012017972</v>
       </c>
       <c r="D18">
-        <v>3807.157902231044</v>
+        <v>3810.099770602493</v>
       </c>
       <c r="E18">
         <v>-2523.618164719559</v>
@@ -2757,37 +2757,37 @@
         <v>473.4</v>
       </c>
       <c r="M18">
-        <v>41.70767622674865</v>
+        <v>40.99759657632587</v>
       </c>
       <c r="N18">
-        <v>431.6923237732514</v>
+        <v>432.4024034236741</v>
       </c>
       <c r="O18">
-        <v>107.9230809433128</v>
+        <v>108.1006008559185</v>
       </c>
       <c r="P18">
-        <v>323.7692428299385</v>
+        <v>324.3018025677556</v>
       </c>
       <c r="Q18">
-        <v>1118.369242829939</v>
+        <v>1118.901802567756</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0747512241378239</v>
+        <v>0.07473770363072303</v>
       </c>
       <c r="T18">
         <v>0.5640497054822355</v>
       </c>
       <c r="U18">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.3504285740185</v>
+        <v>11.54701835066511</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06975861609744369</v>
+        <v>0.06961978844758825</v>
       </c>
       <c r="C19">
-        <v>3639.951649164703</v>
+        <v>3643.077525378987</v>
       </c>
       <c r="D19">
-        <v>3809.111277738899</v>
+        <v>3812.237153953183</v>
       </c>
       <c r="E19">
         <v>-2479.238186568135</v>
@@ -2839,37 +2839,37 @@
         <v>473.4</v>
       </c>
       <c r="M19">
-        <v>44.31440599092043</v>
+        <v>43.55994636234624</v>
       </c>
       <c r="N19">
-        <v>429.0855940090796</v>
+        <v>429.8400536376537</v>
       </c>
       <c r="O19">
-        <v>107.2713985022699</v>
+        <v>107.4600134094134</v>
       </c>
       <c r="P19">
-        <v>321.8141955068097</v>
+        <v>322.3800402282403</v>
       </c>
       <c r="Q19">
-        <v>1116.41419550681</v>
+        <v>1116.98004022824</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07502373189514529</v>
+        <v>0.07501008412423513</v>
       </c>
       <c r="T19">
         <v>0.569358908282332</v>
       </c>
       <c r="U19">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.68275630495859</v>
+        <v>10.86778197709658</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.0696778099196112</v>
+        <v>0.06953151184586503</v>
       </c>
       <c r="C20">
-        <v>3597.527052024833</v>
+        <v>3600.837329975687</v>
       </c>
       <c r="D20">
-        <v>3811.066658750453</v>
+        <v>3814.376936701307</v>
       </c>
       <c r="E20">
         <v>-2434.858208416712</v>
@@ -2921,37 +2921,37 @@
         <v>473.4</v>
       </c>
       <c r="M20">
-        <v>46.92113575509222</v>
+        <v>46.1222961483666</v>
       </c>
       <c r="N20">
-        <v>426.4788642449078</v>
+        <v>427.2777038516334</v>
       </c>
       <c r="O20">
-        <v>106.6197160612269</v>
+        <v>106.8194259629083</v>
       </c>
       <c r="P20">
-        <v>319.8591481836808</v>
+        <v>320.458277888725</v>
       </c>
       <c r="Q20">
-        <v>1114.459148183681</v>
+        <v>1115.058277888725</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07530288618313304</v>
+        <v>0.07528910804441821</v>
       </c>
       <c r="T20">
         <v>0.5747976038336501</v>
       </c>
       <c r="U20">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.089269843572</v>
+        <v>10.26401631170232</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06991050374177872</v>
+        <v>0.06968548524414185</v>
       </c>
       <c r="C21">
-        <v>3547.521678589691</v>
+        <v>3552.726667560803</v>
       </c>
       <c r="D21">
-        <v>3805.441263466735</v>
+        <v>3810.646252437846</v>
       </c>
       <c r="E21">
         <v>-2390.478230265289</v>
@@ -3003,37 +3003,37 @@
         <v>473.4</v>
       </c>
       <c r="M21">
-        <v>51.3829486059935</v>
+        <v>50.11811922867794</v>
       </c>
       <c r="N21">
-        <v>422.0170513940064</v>
+        <v>423.2818807713221</v>
       </c>
       <c r="O21">
-        <v>105.5042628485016</v>
+        <v>105.8204701928305</v>
       </c>
       <c r="P21">
-        <v>316.5127885455048</v>
+        <v>317.4614105784916</v>
       </c>
       <c r="Q21">
-        <v>1111.112788545505</v>
+        <v>1112.061410578492</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07558893316958963</v>
+        <v>0.07557502144411202</v>
       </c>
       <c r="T21">
         <v>0.5803705881640133</v>
       </c>
       <c r="U21">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.213173102035269</v>
+        <v>9.445685657915055</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06984619756394622</v>
+        <v>0.06960995864241865</v>
       </c>
       <c r="C22">
-        <v>3504.694647173186</v>
+        <v>3510.175741928796</v>
       </c>
       <c r="D22">
-        <v>3806.994210201652</v>
+        <v>3812.475304957262</v>
       </c>
       <c r="E22">
         <v>-2346.098252113865</v>
@@ -3085,37 +3085,37 @@
         <v>473.4</v>
       </c>
       <c r="M22">
-        <v>54.08731432209844</v>
+        <v>52.75591497755573</v>
       </c>
       <c r="N22">
-        <v>419.3126856779015</v>
+        <v>420.6440850224442</v>
       </c>
       <c r="O22">
-        <v>104.8281714194754</v>
+        <v>105.1610212556111</v>
       </c>
       <c r="P22">
-        <v>314.4845142584261</v>
+        <v>315.4830637668332</v>
       </c>
       <c r="Q22">
-        <v>1109.084514258426</v>
+        <v>1110.083063766833</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07588213133070763</v>
+        <v>0.07586808267879816</v>
       </c>
       <c r="T22">
         <v>0.5860828971026354</v>
       </c>
       <c r="U22">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.752514446933503</v>
+        <v>8.973401375019302</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06978189138611374</v>
+        <v>0.06953443204069544</v>
       </c>
       <c r="C23">
-        <v>3461.868883745306</v>
+        <v>3467.626572975014</v>
       </c>
       <c r="D23">
-        <v>3808.548424925196</v>
+        <v>3814.306114154904</v>
       </c>
       <c r="E23">
         <v>-2301.718273962442</v>
@@ -3167,37 +3167,37 @@
         <v>473.4</v>
       </c>
       <c r="M23">
-        <v>56.79168003820335</v>
+        <v>55.39371072643351</v>
       </c>
       <c r="N23">
-        <v>416.6083199617966</v>
+        <v>418.0062892735665</v>
       </c>
       <c r="O23">
-        <v>104.1520799904492</v>
+        <v>104.5015723183916</v>
       </c>
       <c r="P23">
-        <v>312.4562399713475</v>
+        <v>313.5047169551749</v>
       </c>
       <c r="Q23">
-        <v>1107.056239971348</v>
+        <v>1108.104716955175</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07618275223008179</v>
+        <v>0.07616856318524851</v>
       </c>
       <c r="T23">
         <v>0.5919398214574252</v>
       </c>
       <c r="U23">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.335728044698577</v>
+        <v>8.546096547637433</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06971758520828127</v>
+        <v>0.06945890543897223</v>
       </c>
       <c r="C24">
-        <v>3419.044389859666</v>
+        <v>3425.079163231424</v>
       </c>
       <c r="D24">
-        <v>3810.103909190979</v>
+        <v>3816.138682562737</v>
       </c>
       <c r="E24">
         <v>-2257.338295811019</v>
@@ -3249,37 +3249,37 @@
         <v>473.4</v>
       </c>
       <c r="M24">
-        <v>59.49604575430828</v>
+        <v>58.0315064753113</v>
       </c>
       <c r="N24">
-        <v>413.9039542456917</v>
+        <v>415.3684935246887</v>
       </c>
       <c r="O24">
-        <v>103.4759885614229</v>
+        <v>103.8421233811722</v>
       </c>
       <c r="P24">
-        <v>310.4279656842688</v>
+        <v>311.5263701435165</v>
       </c>
       <c r="Q24">
-        <v>1105.027965684269</v>
+        <v>1106.126370143516</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07649108135764504</v>
+        <v>0.07647674832006937</v>
       </c>
       <c r="T24">
         <v>0.5979469233597737</v>
       </c>
       <c r="U24">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.956831315394095</v>
+        <v>8.157637613653911</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06991202903044878</v>
+        <v>0.06938337883724904</v>
       </c>
       <c r="C25">
-        <v>3369.964946770111</v>
+        <v>3382.533515234863</v>
       </c>
       <c r="D25">
-        <v>3805.404444252848</v>
+        <v>3817.973012717599</v>
       </c>
       <c r="E25">
         <v>-2212.958317659595</v>
@@ -3331,45 +3331,45 @@
         <v>473.4</v>
       </c>
       <c r="M25">
-        <v>63.7315207166373</v>
+        <v>60.66930222418909</v>
       </c>
       <c r="N25">
-        <v>409.6684792833627</v>
+        <v>412.7306977758109</v>
       </c>
       <c r="O25">
-        <v>102.4171198208407</v>
+        <v>103.1826744439527</v>
       </c>
       <c r="P25">
-        <v>307.251359462522</v>
+        <v>309.5480233318582</v>
       </c>
       <c r="Q25">
-        <v>1101.851359462522</v>
+        <v>1104.148023331858</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07680741903397616</v>
+        <v>0.07679293826358689</v>
       </c>
       <c r="T25">
         <v>0.6041100538829626</v>
       </c>
       <c r="U25">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04682746249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.428035525855851</v>
+        <v>7.802957717408089</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06985897285261629</v>
+        <v>0.06945185223552584</v>
       </c>
       <c r="C26">
-        <v>3326.866119894446</v>
+        <v>3336.490434916431</v>
       </c>
       <c r="D26">
-        <v>3806.685595528606</v>
+        <v>3816.309910550591</v>
       </c>
       <c r="E26">
         <v>-2168.578339508172</v>
@@ -3413,37 +3413,37 @@
         <v>473.4</v>
       </c>
       <c r="M26">
-        <v>66.50245639996936</v>
+        <v>64.1591935535742</v>
       </c>
       <c r="N26">
-        <v>406.8975436000306</v>
+        <v>409.2408064464258</v>
       </c>
       <c r="O26">
-        <v>101.7243859000077</v>
+        <v>102.3102016116064</v>
       </c>
       <c r="P26">
-        <v>305.173157700023</v>
+        <v>306.9306048348193</v>
       </c>
       <c r="Q26">
-        <v>1099.773157700023</v>
+        <v>1101.530604834819</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.0771320813860002</v>
+        <v>0.07711744899509171</v>
       </c>
       <c r="T26">
         <v>0.6104353720514984</v>
       </c>
       <c r="U26">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.118534045611857</v>
+        <v>7.378521670549079</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3462,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06980591667478379</v>
+        <v>0.06938232563380263</v>
       </c>
       <c r="C27">
-        <v>3283.768155950112</v>
+        <v>3293.799150768318</v>
       </c>
       <c r="D27">
-        <v>3807.967609735695</v>
+        <v>3817.998604553901</v>
       </c>
       <c r="E27">
         <v>-2124.198361356749</v>
@@ -3495,37 +3495,37 @@
         <v>473.4</v>
       </c>
       <c r="M27">
-        <v>69.27339208330142</v>
+        <v>66.83249328497313</v>
       </c>
       <c r="N27">
-        <v>404.1266079166986</v>
+        <v>406.5675067150269</v>
       </c>
       <c r="O27">
-        <v>101.0316519791746</v>
+        <v>101.6418766787567</v>
       </c>
       <c r="P27">
-        <v>303.0949559375239</v>
+        <v>304.9256300362701</v>
       </c>
       <c r="Q27">
-        <v>1097.694955937524</v>
+        <v>1099.52563003627</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07746540140074487</v>
+        <v>0.07745061334610331</v>
       </c>
       <c r="T27">
         <v>0.6169293653711951</v>
       </c>
       <c r="U27">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.833792683787382</v>
+        <v>7.083380803727116</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06975286049695133</v>
+        <v>0.06931279903207944</v>
       </c>
       <c r="C28">
-        <v>3240.671055809257</v>
+        <v>3251.109361755513</v>
       </c>
       <c r="D28">
-        <v>3809.250487746264</v>
+        <v>3819.688793692519</v>
       </c>
       <c r="E28">
         <v>-2079.818383205326</v>
@@ -3577,37 +3577,37 @@
         <v>473.4</v>
       </c>
       <c r="M28">
-        <v>72.04432776663347</v>
+        <v>69.50579301637205</v>
       </c>
       <c r="N28">
-        <v>401.3556722333665</v>
+        <v>403.8942069836279</v>
       </c>
       <c r="O28">
-        <v>100.3389180583416</v>
+        <v>100.973551745907</v>
       </c>
       <c r="P28">
-        <v>301.0167541750249</v>
+        <v>302.9206552377209</v>
       </c>
       <c r="Q28">
-        <v>1095.616754175025</v>
+        <v>1097.520655237721</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07780773006453673</v>
+        <v>0.07779278213903418</v>
       </c>
       <c r="T28">
         <v>0.6235988720238568</v>
       </c>
       <c r="U28">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.570954503641714</v>
+        <v>6.810943080506841</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06969980431911885</v>
+        <v>0.06924327243035625</v>
       </c>
       <c r="C29">
-        <v>3197.574820345205</v>
+        <v>3208.421069864541</v>
       </c>
       <c r="D29">
-        <v>3810.534230433635</v>
+        <v>3821.380479952971</v>
       </c>
       <c r="E29">
         <v>-2035.438405053902</v>
@@ -3659,37 +3659,37 @@
         <v>473.4</v>
       </c>
       <c r="M29">
-        <v>74.81526344996554</v>
+        <v>72.17909274777099</v>
       </c>
       <c r="N29">
-        <v>398.5847365500344</v>
+        <v>401.220907252229</v>
       </c>
       <c r="O29">
-        <v>99.64618413750861</v>
+        <v>100.3052268130572</v>
       </c>
       <c r="P29">
-        <v>298.9385524125258</v>
+        <v>300.9156804391718</v>
       </c>
       <c r="Q29">
-        <v>1093.538552412526</v>
+        <v>1095.515680439172</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07815943759582972</v>
+        <v>0.07814432541944258</v>
       </c>
       <c r="T29">
         <v>0.6304511048861804</v>
       </c>
       <c r="U29">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.32758581832165</v>
+        <v>6.558685929376957</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06994074814128635</v>
+        <v>0.06917374582863305</v>
       </c>
       <c r="C30">
-        <v>3147.371933277019</v>
+        <v>3165.734277085445</v>
       </c>
       <c r="D30">
-        <v>3804.711321516872</v>
+        <v>3823.073665325298</v>
       </c>
       <c r="E30">
         <v>-1991.058426902479</v>
@@ -3741,45 +3741,45 @@
         <v>473.4</v>
       </c>
       <c r="M30">
-        <v>79.32589427683338</v>
+        <v>74.85239247916991</v>
       </c>
       <c r="N30">
-        <v>394.0741057231666</v>
+        <v>398.5476075208301</v>
       </c>
       <c r="O30">
-        <v>98.51852643079165</v>
+        <v>99.63690188020752</v>
       </c>
       <c r="P30">
-        <v>295.5555792923749</v>
+        <v>298.9107056406226</v>
       </c>
       <c r="Q30">
-        <v>1090.155579292375</v>
+        <v>1093.510705640623</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07852091478076972</v>
+        <v>0.07850563379097344</v>
       </c>
       <c r="T30">
         <v>0.6374936775502351</v>
       </c>
       <c r="U30">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>5.967786487825999</v>
+        <v>6.324447146184924</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06989819196345387</v>
+        <v>0.06910421922690983</v>
       </c>
       <c r="C31">
-        <v>3104.019119365434</v>
+        <v>3123.048985411799</v>
       </c>
       <c r="D31">
-        <v>3805.738485756709</v>
+        <v>3824.768351803075</v>
       </c>
       <c r="E31">
         <v>-1946.678448751056</v>
@@ -3823,45 +3823,45 @@
         <v>473.4</v>
       </c>
       <c r="M31">
-        <v>82.15896192957742</v>
+        <v>77.52569221056882</v>
       </c>
       <c r="N31">
-        <v>391.2410380704226</v>
+        <v>395.8743077894312</v>
       </c>
       <c r="O31">
-        <v>97.81025951760564</v>
+        <v>98.96857694735779</v>
       </c>
       <c r="P31">
-        <v>293.4307785528169</v>
+        <v>296.9057308420734</v>
       </c>
       <c r="Q31">
-        <v>1088.030778552817</v>
+        <v>1091.505730842073</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07889257442162353</v>
+        <v>0.0788771198631108</v>
       </c>
       <c r="T31">
         <v>0.6447346325428547</v>
       </c>
       <c r="U31">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>5.762000746866483</v>
+        <v>6.10636276183372</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06985563578562137</v>
+        <v>0.06925969262518662</v>
       </c>
       <c r="C32">
-        <v>3060.666860214092</v>
+        <v>3074.881472356926</v>
       </c>
       <c r="D32">
-        <v>3806.766204756791</v>
+        <v>3820.980816899626</v>
       </c>
       <c r="E32">
         <v>-1902.298470599632</v>
@@ -3905,37 +3905,37 @@
         <v>473.4</v>
       </c>
       <c r="M32">
-        <v>84.99202958232146</v>
+        <v>81.53039128651045</v>
       </c>
       <c r="N32">
-        <v>388.4079704176785</v>
+        <v>391.8696087134895</v>
       </c>
       <c r="O32">
-        <v>97.10199260441962</v>
+        <v>97.96740217837238</v>
       </c>
       <c r="P32">
-        <v>291.3059778132589</v>
+        <v>293.9022065351172</v>
       </c>
       <c r="Q32">
-        <v>1085.905977813259</v>
+        <v>1088.502206535117</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07927485290935887</v>
+        <v>0.07925921982302352</v>
       </c>
       <c r="T32">
         <v>0.6521824719638349</v>
       </c>
       <c r="U32">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.569934055304266</v>
+        <v>5.806423746163549</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06981307960778889</v>
+        <v>0.06919766602346342</v>
       </c>
       <c r="C33">
-        <v>3017.315156272545</v>
+        <v>3032.011643454216</v>
       </c>
       <c r="D33">
-        <v>3807.794478966669</v>
+        <v>3822.490966148339</v>
       </c>
       <c r="E33">
         <v>-1857.918492448209</v>
@@ -3987,37 +3987,37 @@
         <v>473.4</v>
       </c>
       <c r="M33">
-        <v>87.82509723506551</v>
+        <v>84.24807099606079</v>
       </c>
       <c r="N33">
-        <v>385.5749027649344</v>
+        <v>389.1519290039392</v>
       </c>
       <c r="O33">
-        <v>96.39372569123361</v>
+        <v>97.2879822509848</v>
       </c>
       <c r="P33">
-        <v>289.1811770737008</v>
+        <v>291.8639467529544</v>
       </c>
       <c r="Q33">
-        <v>1083.781177073701</v>
+        <v>1086.463946752954</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07966821193297061</v>
+        <v>0.07965239514409311</v>
       </c>
       <c r="T33">
         <v>0.6598461907883217</v>
       </c>
       <c r="U33">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.390258763197677</v>
+        <v>5.619119754351822</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.0697705234299564</v>
+        <v>0.06913563942174022</v>
       </c>
       <c r="C34">
-        <v>2973.964007990831</v>
+        <v>2989.143008722611</v>
       </c>
       <c r="D34">
-        <v>3808.823308836378</v>
+        <v>3824.002309568158</v>
       </c>
       <c r="E34">
         <v>-1813.538514296785</v>
@@ -4069,37 +4069,37 @@
         <v>473.4</v>
       </c>
       <c r="M34">
-        <v>90.65816488780958</v>
+        <v>86.96575070561116</v>
       </c>
       <c r="N34">
-        <v>382.7418351121904</v>
+        <v>386.4342492943888</v>
       </c>
       <c r="O34">
-        <v>95.6854587780476</v>
+        <v>96.6085623235972</v>
       </c>
       <c r="P34">
-        <v>287.0563763341428</v>
+        <v>289.8256869707916</v>
       </c>
       <c r="Q34">
-        <v>1081.656376334143</v>
+        <v>1084.425686970792</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08007314033962976</v>
+        <v>0.08005713444519419</v>
       </c>
       <c r="T34">
         <v>0.6677353131076466</v>
       </c>
       <c r="U34">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.221813176847749</v>
+        <v>5.443522262028326</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06972796725212393</v>
+        <v>0.06907361282001702</v>
       </c>
       <c r="C35">
-        <v>2930.613415819474</v>
+        <v>2946.275569579132</v>
       </c>
       <c r="D35">
-        <v>3809.852694816444</v>
+        <v>3825.514848576101</v>
       </c>
       <c r="E35">
         <v>-1769.158536145362</v>
@@ -4151,37 +4151,37 @@
         <v>473.4</v>
       </c>
       <c r="M35">
-        <v>93.49123254055363</v>
+        <v>89.68343041516151</v>
       </c>
       <c r="N35">
-        <v>379.9087674594464</v>
+        <v>383.7165695848385</v>
       </c>
       <c r="O35">
-        <v>94.9771918648616</v>
+        <v>95.92914239620961</v>
       </c>
       <c r="P35">
-        <v>284.9315755945848</v>
+        <v>287.7874271886288</v>
       </c>
       <c r="Q35">
-        <v>1079.531575594585</v>
+        <v>1082.387427188629</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08049015616141306</v>
+        <v>0.08047395551647737</v>
       </c>
       <c r="T35">
         <v>0.675859931615608</v>
       </c>
       <c r="U35">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.063576413912969</v>
+        <v>5.278567041966862</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.06968541107429144</v>
+        <v>0.06901158621829383</v>
       </c>
       <c r="C36">
-        <v>2887.263380209484</v>
+        <v>2903.409327443042</v>
       </c>
       <c r="D36">
-        <v>3810.882637357877</v>
+        <v>3827.028584591435</v>
       </c>
       <c r="E36">
         <v>-1724.778557993939</v>
@@ -4233,37 +4233,37 @@
         <v>473.4</v>
       </c>
       <c r="M36">
-        <v>96.32430019329767</v>
+        <v>92.40111012471185</v>
       </c>
       <c r="N36">
-        <v>377.0756998067023</v>
+        <v>380.9988898752881</v>
       </c>
       <c r="O36">
-        <v>94.26892495167557</v>
+        <v>95.24972246882203</v>
       </c>
       <c r="P36">
-        <v>282.8067748550267</v>
+        <v>285.7491674064661</v>
       </c>
       <c r="Q36">
-        <v>1077.406774855027</v>
+        <v>1080.349167406466</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08091980882628069</v>
+        <v>0.0809034075293146</v>
       </c>
       <c r="T36">
         <v>0.6842307506844165</v>
       </c>
       <c r="U36">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.914647695856704</v>
+        <v>5.123315070144307</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4282,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.06964285489645895</v>
+        <v>0.06894955961657062</v>
       </c>
       <c r="C37">
-        <v>2843.91390161236</v>
+        <v>2860.544283735851</v>
       </c>
       <c r="D37">
-        <v>3811.913136912176</v>
+        <v>3828.543519035668</v>
       </c>
       <c r="E37">
         <v>-1680.398579842516</v>
@@ -4315,37 +4315,37 @@
         <v>473.4</v>
       </c>
       <c r="M37">
-        <v>99.15736784604172</v>
+        <v>95.1187898342622</v>
       </c>
       <c r="N37">
-        <v>374.2426321539583</v>
+        <v>378.2812101657378</v>
       </c>
       <c r="O37">
-        <v>93.56065803848956</v>
+        <v>94.57030254143444</v>
       </c>
       <c r="P37">
-        <v>280.6819741154687</v>
+        <v>283.7109076243033</v>
       </c>
       <c r="Q37">
-        <v>1075.281974115469</v>
+        <v>1078.310907624303</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08136268157314425</v>
+        <v>0.08134607345023911</v>
       </c>
       <c r="T37">
         <v>0.6928591334168808</v>
       </c>
       <c r="U37">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.774229190260799</v>
+        <v>4.976934639568755</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.06960029871862648</v>
+        <v>0.06888753301484743</v>
       </c>
       <c r="C38">
-        <v>2800.564980480089</v>
+        <v>2817.680439881325</v>
       </c>
       <c r="D38">
-        <v>3812.944193931328</v>
+        <v>3830.059653332565</v>
       </c>
       <c r="E38">
         <v>-1636.018601691092</v>
@@ -4397,37 +4397,37 @@
         <v>473.4</v>
       </c>
       <c r="M38">
-        <v>101.9904354987858</v>
+        <v>97.83646954381254</v>
       </c>
       <c r="N38">
-        <v>371.4095645012142</v>
+        <v>375.5635304561874</v>
       </c>
       <c r="O38">
-        <v>92.85239112530355</v>
+        <v>93.89088261404686</v>
       </c>
       <c r="P38">
-        <v>278.5571733759107</v>
+        <v>281.6726478421406</v>
       </c>
       <c r="Q38">
-        <v>1073.157173375911</v>
+        <v>1076.27264784214</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08181939409334731</v>
+        <v>0.08180257268119254</v>
       </c>
       <c r="T38">
         <v>0.7017571531097345</v>
       </c>
       <c r="U38">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.641611712753555</v>
+        <v>4.83868645513629</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.069557742540794</v>
+        <v>0.06882550641312422</v>
       </c>
       <c r="C39">
-        <v>2757.216617265147</v>
+        <v>2774.81779730548</v>
       </c>
       <c r="D39">
-        <v>3813.97580886781</v>
+        <v>3831.576988908143</v>
       </c>
       <c r="E39">
         <v>-1591.638623539669</v>
@@ -4479,37 +4479,37 @@
         <v>473.4</v>
       </c>
       <c r="M39">
-        <v>104.8235031515298</v>
+        <v>100.5541492533629</v>
       </c>
       <c r="N39">
-        <v>368.5764968484701</v>
+        <v>372.8458507466371</v>
       </c>
       <c r="O39">
-        <v>92.14412421211753</v>
+        <v>93.21146268665927</v>
       </c>
       <c r="P39">
-        <v>276.4323726363526</v>
+        <v>279.6343880599778</v>
       </c>
       <c r="Q39">
-        <v>1071.032372636353</v>
+        <v>1074.234388059978</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08229060542371552</v>
+        <v>0.08227356395122383</v>
       </c>
       <c r="T39">
         <v>0.7109376496182345</v>
       </c>
       <c r="U39">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.516162747544</v>
+        <v>4.707911145538013</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4528,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07025618636296151</v>
+        <v>0.06876347981140102</v>
       </c>
       <c r="C40">
-        <v>2695.975776792256</v>
+        <v>2731.956357436598</v>
       </c>
       <c r="D40">
-        <v>3797.114946546341</v>
+        <v>3833.095527190684</v>
       </c>
       <c r="E40">
         <v>-1547.258645388246</v>
@@ -4561,45 +4561,45 @@
         <v>473.4</v>
       </c>
       <c r="M40">
-        <v>112.0413126456345</v>
+        <v>103.2718289629132</v>
       </c>
       <c r="N40">
-        <v>361.3586873543655</v>
+        <v>370.1281710370868</v>
       </c>
       <c r="O40">
-        <v>90.33967183859137</v>
+        <v>92.53204275927169</v>
       </c>
       <c r="P40">
-        <v>271.0190155157741</v>
+        <v>277.5961282778151</v>
       </c>
       <c r="Q40">
-        <v>1065.619015515774</v>
+        <v>1072.196128277815</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08277701711957951</v>
+        <v>0.08275974848803033</v>
       </c>
       <c r="T40">
         <v>0.7204142911753957</v>
       </c>
       <c r="U40">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.225227184701725</v>
+        <v>4.584018746971223</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07023313018512903</v>
+        <v>0.06943270320967782</v>
       </c>
       <c r="C41">
-        <v>2652.150009215861</v>
+        <v>2671.255713897268</v>
       </c>
       <c r="D41">
-        <v>3797.669157121371</v>
+        <v>3816.774861802778</v>
       </c>
       <c r="E41">
         <v>-1502.878667236822</v>
@@ -4643,37 +4643,37 @@
         <v>473.4</v>
       </c>
       <c r="M41">
-        <v>114.9897682415722</v>
+        <v>110.3165565422274</v>
       </c>
       <c r="N41">
-        <v>358.4102317584278</v>
+        <v>363.0834434577726</v>
       </c>
       <c r="O41">
-        <v>89.60255793960694</v>
+        <v>90.77086086444315</v>
       </c>
       <c r="P41">
-        <v>268.8076738188208</v>
+        <v>272.3125825933295</v>
       </c>
       <c r="Q41">
-        <v>1063.407673818821</v>
+        <v>1066.912582593329</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08327937673989805</v>
+        <v>0.08326187350145345</v>
       </c>
       <c r="T41">
         <v>0.7302016422918081</v>
       </c>
       <c r="U41">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.11688802611963</v>
+        <v>4.291286954907719</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4692,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07021007400729654</v>
+        <v>0.06938942660795462</v>
       </c>
       <c r="C42">
-        <v>2608.324403443469</v>
+        <v>2627.926938258624</v>
       </c>
       <c r="D42">
-        <v>3798.223529500402</v>
+        <v>3817.826064315558</v>
       </c>
       <c r="E42">
         <v>-1458.498689085399</v>
@@ -4725,37 +4725,37 @@
         <v>473.4</v>
       </c>
       <c r="M42">
-        <v>117.93822383751</v>
+        <v>113.1451861971563</v>
       </c>
       <c r="N42">
-        <v>355.46177616249</v>
+        <v>360.2548138028437</v>
       </c>
       <c r="O42">
-        <v>88.86544404062249</v>
+        <v>90.06370345071093</v>
       </c>
       <c r="P42">
-        <v>266.5963321218675</v>
+        <v>270.1911103521328</v>
       </c>
       <c r="Q42">
-        <v>1061.196332121867</v>
+        <v>1064.791110352133</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08379848168089385</v>
+        <v>0.08378073601532399</v>
       </c>
       <c r="T42">
         <v>0.7403152384454342</v>
       </c>
       <c r="U42">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.013965825466639</v>
+        <v>4.184004781035025</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07101726782946406</v>
+        <v>0.06934615000623141</v>
       </c>
       <c r="C43">
-        <v>2544.631786241719</v>
+        <v>2584.598741816391</v>
       </c>
       <c r="D43">
-        <v>3778.910890450076</v>
+        <v>3818.877846024748</v>
       </c>
       <c r="E43">
         <v>-1414.118710933976</v>
@@ -4807,45 +4807,45 @@
         <v>473.4</v>
       </c>
       <c r="M43">
-        <v>125.7995430148103</v>
+        <v>115.9738158520852</v>
       </c>
       <c r="N43">
-        <v>347.6004569851897</v>
+        <v>357.4261841479148</v>
       </c>
       <c r="O43">
-        <v>86.90011424629742</v>
+        <v>89.3565460369787</v>
       </c>
       <c r="P43">
-        <v>260.7003427388922</v>
+        <v>268.0696381109361</v>
       </c>
       <c r="Q43">
-        <v>1055.300342738892</v>
+        <v>1062.669638110936</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08433518339955055</v>
+        <v>0.08431718708898675</v>
       </c>
       <c r="T43">
         <v>0.7507716683669799</v>
       </c>
       <c r="U43">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.763129727301687</v>
+        <v>4.08195588393661</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07101446165163158</v>
+        <v>0.07040537340450823</v>
       </c>
       <c r="C44">
-        <v>2500.318607525733</v>
+        <v>2514.641086532197</v>
       </c>
       <c r="D44">
-        <v>3778.977689885512</v>
+        <v>3793.300168891976</v>
       </c>
       <c r="E44">
         <v>-1369.738732782552</v>
@@ -4889,37 +4889,37 @@
         <v>473.4</v>
       </c>
       <c r="M44">
-        <v>128.8678245517569</v>
+        <v>125.3263022952733</v>
       </c>
       <c r="N44">
-        <v>344.5321754482431</v>
+        <v>348.0736977047267</v>
       </c>
       <c r="O44">
-        <v>86.13304386206077</v>
+        <v>87.01842442618167</v>
       </c>
       <c r="P44">
-        <v>258.3991315861823</v>
+        <v>261.055273278545</v>
       </c>
       <c r="Q44">
-        <v>1052.999131586182</v>
+        <v>1055.655273278545</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08489039207402299</v>
+        <v>0.08487213647553445</v>
       </c>
       <c r="T44">
         <v>0.7615886648375444</v>
       </c>
       <c r="U44">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.673531400461171</v>
+        <v>3.777339563443374</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07101165547379909</v>
+        <v>0.07038834680278502</v>
       </c>
       <c r="C45">
-        <v>2456.005431171401</v>
+        <v>2470.669549742961</v>
       </c>
       <c r="D45">
-        <v>3779.044491682604</v>
+        <v>3793.708610254164</v>
       </c>
       <c r="E45">
         <v>-1325.358754631129</v>
@@ -4971,37 +4971,37 @@
         <v>473.4</v>
       </c>
       <c r="M45">
-        <v>131.9361060887035</v>
+        <v>128.3102618737322</v>
       </c>
       <c r="N45">
-        <v>341.4638939112965</v>
+        <v>345.0897381262678</v>
       </c>
       <c r="O45">
-        <v>85.36597347782413</v>
+        <v>86.27243453156694</v>
       </c>
       <c r="P45">
-        <v>256.0979204334724</v>
+        <v>258.8173035947008</v>
       </c>
       <c r="Q45">
-        <v>1050.697920433473</v>
+        <v>1053.417303594701</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08546508175461727</v>
+        <v>0.08544655777038206</v>
       </c>
       <c r="T45">
         <v>0.7727852050439181</v>
       </c>
       <c r="U45">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.588100437659749</v>
+        <v>3.689494457316783</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07100884929596661</v>
+        <v>0.07037132020106182</v>
       </c>
       <c r="C46">
-        <v>2411.692257178851</v>
+        <v>2426.698100920564</v>
       </c>
       <c r="D46">
-        <v>3779.111295841477</v>
+        <v>3794.11713958319</v>
       </c>
       <c r="E46">
         <v>-1280.978776479706</v>
@@ -5053,37 +5053,37 @@
         <v>473.4</v>
       </c>
       <c r="M46">
-        <v>135.0043876256501</v>
+        <v>131.2942214521911</v>
       </c>
       <c r="N46">
-        <v>338.3956123743499</v>
+        <v>342.1057785478089</v>
       </c>
       <c r="O46">
-        <v>84.59890309358747</v>
+        <v>85.52644463695222</v>
       </c>
       <c r="P46">
-        <v>253.7967092807624</v>
+        <v>256.5793339108567</v>
       </c>
       <c r="Q46">
-        <v>1048.396709280762</v>
+        <v>1051.179333910857</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08606029606666135</v>
+        <v>0.08604149411147423</v>
       </c>
       <c r="T46">
         <v>0.7843816216862339</v>
       </c>
       <c r="U46">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.506552700440208</v>
+        <v>3.605642310559584</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5102,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07259229311813414</v>
+        <v>0.07035429359933862</v>
       </c>
       <c r="C47">
-        <v>2329.988289157849</v>
+        <v>2382.726740093426</v>
       </c>
       <c r="D47">
-        <v>3741.787305971899</v>
+        <v>3794.525756907476</v>
       </c>
       <c r="E47">
         <v>-1236.598798328282</v>
@@ -5135,45 +5135,45 @@
         <v>473.4</v>
       </c>
       <c r="M47">
-        <v>147.4590345416227</v>
+        <v>134.27818103065</v>
       </c>
       <c r="N47">
-        <v>325.9409654583773</v>
+        <v>339.12181896935</v>
       </c>
       <c r="O47">
-        <v>81.48524136459432</v>
+        <v>84.7804547423375</v>
       </c>
       <c r="P47">
-        <v>244.4557240937829</v>
+        <v>254.3413642270125</v>
       </c>
       <c r="Q47">
-        <v>1039.055724093783</v>
+        <v>1048.941364227012</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08667715453550703</v>
+        <v>0.08665806450133337</v>
       </c>
       <c r="T47">
         <v>0.7963997262064519</v>
       </c>
       <c r="U47">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.05537746249690058</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.210383151304135</v>
+        <v>3.525516925880482</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07262473694030165</v>
+        <v>0.07130326699761542</v>
       </c>
       <c r="C48">
-        <v>2284.851270783921</v>
+        <v>2315.706025611707</v>
       </c>
       <c r="D48">
-        <v>3741.030265749394</v>
+        <v>3771.88502057718</v>
       </c>
       <c r="E48">
         <v>-1192.218820176859</v>
@@ -5217,37 +5217,37 @@
         <v>473.4</v>
       </c>
       <c r="M48">
-        <v>150.735901975881</v>
+        <v>142.9782817950122</v>
       </c>
       <c r="N48">
-        <v>322.664098024119</v>
+        <v>330.4217182049878</v>
       </c>
       <c r="O48">
-        <v>80.66602450602974</v>
+        <v>82.60542955124694</v>
       </c>
       <c r="P48">
-        <v>241.9980735180892</v>
+        <v>247.8162886537408</v>
       </c>
       <c r="Q48">
-        <v>1036.598073518089</v>
+        <v>1042.416288653741</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08731685961430996</v>
+        <v>0.0872974708315577</v>
       </c>
       <c r="T48">
         <v>0.8088629457089004</v>
       </c>
       <c r="U48">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.140592213232305</v>
+        <v>3.31099236930762</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07265718076246916</v>
+        <v>0.07130724039589222</v>
       </c>
       <c r="C49">
-        <v>2239.714558677518</v>
+        <v>2271.231817567193</v>
       </c>
       <c r="D49">
-        <v>3740.273531794414</v>
+        <v>3771.79079068409</v>
       </c>
       <c r="E49">
         <v>-1147.838842025435</v>
@@ -5299,37 +5299,37 @@
         <v>473.4</v>
       </c>
       <c r="M49">
-        <v>154.0127694101393</v>
+        <v>146.0865053122951</v>
       </c>
       <c r="N49">
-        <v>319.3872305898607</v>
+        <v>327.3134946877049</v>
       </c>
       <c r="O49">
-        <v>79.84680764746517</v>
+        <v>81.82837367192623</v>
       </c>
       <c r="P49">
-        <v>239.5404229423955</v>
+        <v>245.4851210157787</v>
       </c>
       <c r="Q49">
-        <v>1034.140422942396</v>
+        <v>1040.085121015779</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08798070450740733</v>
+        <v>0.08796100570254518</v>
       </c>
       <c r="T49">
         <v>0.8217964753812524</v>
       </c>
       <c r="U49">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.073771102312469</v>
+        <v>3.240545723152139</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07268962458463668</v>
+        <v>0.07131121379416902</v>
       </c>
       <c r="C50">
-        <v>2194.578152652824</v>
+        <v>2226.757614230698</v>
       </c>
       <c r="D50">
-        <v>3739.517103921143</v>
+        <v>3771.696565499018</v>
       </c>
       <c r="E50">
         <v>-1103.458863874012</v>
@@ -5381,37 +5381,37 @@
         <v>473.4</v>
       </c>
       <c r="M50">
-        <v>157.2896368443976</v>
+        <v>149.1947288295779</v>
       </c>
       <c r="N50">
-        <v>316.1103631556024</v>
+        <v>324.2052711704221</v>
       </c>
       <c r="O50">
-        <v>79.0275907889006</v>
+        <v>81.05131779260552</v>
       </c>
       <c r="P50">
-        <v>237.0827723667018</v>
+        <v>243.1539533778165</v>
       </c>
       <c r="Q50">
-        <v>1031.682772366702</v>
+        <v>1037.753953377817</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.08867008189639307</v>
+        <v>0.08865006114549373</v>
       </c>
       <c r="T50">
         <v>0.8352274485025412</v>
       </c>
       <c r="U50">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.009734204347626</v>
+        <v>3.173034353919803</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07613981840680417</v>
+        <v>0.07131518719244581</v>
       </c>
       <c r="C51">
-        <v>2071.466424316812</v>
+        <v>2182.283415601868</v>
       </c>
       <c r="D51">
-        <v>3660.785353736554</v>
+        <v>3771.60234502161</v>
       </c>
       <c r="E51">
         <v>-1059.078885722589</v>
@@ -5463,45 +5463,45 @@
         <v>473.4</v>
       </c>
       <c r="M51">
-        <v>180.7904603222594</v>
+        <v>152.3029523468608</v>
       </c>
       <c r="N51">
-        <v>292.6095396777406</v>
+        <v>321.0970476531392</v>
       </c>
       <c r="O51">
-        <v>73.15238491943515</v>
+        <v>80.27426191328479</v>
       </c>
       <c r="P51">
-        <v>219.4571547583054</v>
+        <v>240.8227857398544</v>
       </c>
       <c r="Q51">
-        <v>1014.057154758306</v>
+        <v>1035.422785739854</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.08938649369279</v>
+        <v>0.08936613837051868</v>
       </c>
       <c r="T51">
         <v>0.8491851264521156</v>
       </c>
       <c r="U51">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.618500993670592</v>
+        <v>3.108278550778582</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.0762420122289717</v>
+        <v>0.07131916059072262</v>
       </c>
       <c r="C52">
-        <v>2024.804953647021</v>
+        <v>2137.809221680348</v>
       </c>
       <c r="D52">
-        <v>3658.503861218187</v>
+        <v>3771.508129251515</v>
       </c>
       <c r="E52">
         <v>-1014.698907571166</v>
@@ -5545,45 +5545,45 @@
         <v>473.4</v>
       </c>
       <c r="M52">
-        <v>184.480061553326</v>
+        <v>155.4111758641437</v>
       </c>
       <c r="N52">
-        <v>288.919938446674</v>
+        <v>317.9888241358563</v>
       </c>
       <c r="O52">
-        <v>72.2299846116685</v>
+        <v>79.49720603396408</v>
       </c>
       <c r="P52">
-        <v>216.6899538350055</v>
+        <v>238.4916181018922</v>
       </c>
       <c r="Q52">
-        <v>1011.289953835005</v>
+        <v>1033.091618101892</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09013156196104284</v>
+        <v>0.09011085868454466</v>
       </c>
       <c r="T52">
         <v>0.8637011115196733</v>
       </c>
       <c r="U52">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.56613097379718</v>
+        <v>3.046112979763011</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.07634420605113923</v>
+        <v>0.07430663398899941</v>
       </c>
       <c r="C53">
-        <v>1978.146324971838</v>
+        <v>2023.899043603045</v>
       </c>
       <c r="D53">
-        <v>3656.225210694427</v>
+        <v>3701.977929325634</v>
       </c>
       <c r="E53">
         <v>-970.3189294197423</v>
@@ -5627,37 +5627,37 @@
         <v>473.4</v>
       </c>
       <c r="M53">
-        <v>188.1696627843925</v>
+        <v>176.1737546900628</v>
       </c>
       <c r="N53">
-        <v>285.2303372156075</v>
+        <v>297.2262453099372</v>
       </c>
       <c r="O53">
-        <v>71.30758430390188</v>
+        <v>74.3065613274843</v>
       </c>
       <c r="P53">
-        <v>213.9227529117056</v>
+        <v>222.9196839824529</v>
       </c>
       <c r="Q53">
-        <v>1008.522752911706</v>
+        <v>1017.519683982453</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09090704117902026</v>
+        <v>0.09088597574608187</v>
       </c>
       <c r="T53">
         <v>0.8788095857736617</v>
       </c>
       <c r="U53">
-        <v>0.08313661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.06235246249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.515814680193313</v>
+        <v>2.687119888162901</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5676,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07827939987330673</v>
+        <v>0.0743691073872762</v>
       </c>
       <c r="C54">
-        <v>1891.146221733059</v>
+        <v>1978.09242037907</v>
       </c>
       <c r="D54">
-        <v>3613.605085607072</v>
+        <v>3700.551284253082</v>
       </c>
       <c r="E54">
         <v>-925.9389512683192</v>
@@ -5709,45 +5709,45 @@
         <v>473.4</v>
       </c>
       <c r="M54">
-        <v>202.7057306756668</v>
+        <v>179.6281420369268</v>
       </c>
       <c r="N54">
-        <v>270.6942693243332</v>
+        <v>293.7718579630732</v>
       </c>
       <c r="O54">
-        <v>67.67356733108329</v>
+        <v>73.4429644907683</v>
       </c>
       <c r="P54">
-        <v>203.0207019932499</v>
+        <v>220.3288934723049</v>
       </c>
       <c r="Q54">
-        <v>997.6207019932499</v>
+        <v>1014.928893472305</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09171483203108008</v>
+        <v>0.09169338935184981</v>
       </c>
       <c r="T54">
         <v>0.8945475797882331</v>
       </c>
       <c r="U54">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.335405113718513</v>
+        <v>2.635444505698231</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.07841684369547425</v>
+        <v>0.07443158078555301</v>
       </c>
       <c r="C55">
-        <v>1843.776982710344</v>
+        <v>1932.286896314597</v>
       </c>
       <c r="D55">
-        <v>3610.61582473578</v>
+        <v>3699.125738340033</v>
       </c>
       <c r="E55">
         <v>-881.5589731168957</v>
@@ -5791,45 +5791,45 @@
         <v>473.4</v>
       </c>
       <c r="M55">
-        <v>206.6039178040451</v>
+        <v>183.0825293837908</v>
       </c>
       <c r="N55">
-        <v>266.7960821959549</v>
+        <v>290.3174706162092</v>
       </c>
       <c r="O55">
-        <v>66.69902054898873</v>
+        <v>72.57936765405231</v>
       </c>
       <c r="P55">
-        <v>200.0970616469662</v>
+        <v>217.7381029621569</v>
       </c>
       <c r="Q55">
-        <v>994.6970616469662</v>
+        <v>1012.338102962157</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09255699696195097</v>
+        <v>0.09253516098339512</v>
       </c>
       <c r="T55">
         <v>0.910955275675765</v>
       </c>
       <c r="U55">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.291340866289862</v>
+        <v>2.585719137666188</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.07855428751764176</v>
+        <v>0.07449405418382982</v>
       </c>
       <c r="C56">
-        <v>1796.41268517661</v>
+        <v>1886.482470139841</v>
       </c>
       <c r="D56">
-        <v>3607.631505353469</v>
+        <v>3697.701290316701</v>
       </c>
       <c r="E56">
         <v>-837.1789949654722</v>
@@ -5873,45 +5873,45 @@
         <v>473.4</v>
       </c>
       <c r="M56">
-        <v>210.5021049324233</v>
+        <v>186.5369167306547</v>
       </c>
       <c r="N56">
-        <v>262.8978950675767</v>
+        <v>286.8630832693452</v>
       </c>
       <c r="O56">
-        <v>65.72447376689416</v>
+        <v>71.71577081733631</v>
       </c>
       <c r="P56">
-        <v>197.1734213006825</v>
+        <v>215.1473124520089</v>
       </c>
       <c r="Q56">
-        <v>991.7734213006825</v>
+        <v>1009.747312452009</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09343577775938143</v>
+        <v>0.09341353138152936</v>
       </c>
       <c r="T56">
         <v>0.9280763496453632</v>
       </c>
       <c r="U56">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.248908628025234</v>
+        <v>2.537835449931629</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.07869173133980928</v>
+        <v>0.0761652775821066</v>
       </c>
       <c r="C57">
-        <v>1749.053316888958</v>
+        <v>1804.400191044563</v>
       </c>
       <c r="D57">
-        <v>3604.652115217241</v>
+        <v>3659.998989372845</v>
       </c>
       <c r="E57">
         <v>-792.7990168140491</v>
@@ -5955,37 +5955,37 @@
         <v>473.4</v>
       </c>
       <c r="M57">
-        <v>214.4002920608015</v>
+        <v>199.510809390999</v>
       </c>
       <c r="N57">
-        <v>258.9997079391985</v>
+        <v>273.889190609001</v>
       </c>
       <c r="O57">
-        <v>64.74992698479963</v>
+        <v>68.47229765225026</v>
       </c>
       <c r="P57">
-        <v>194.2497809543989</v>
+        <v>205.4168929567508</v>
       </c>
       <c r="Q57">
-        <v>988.849780954399</v>
+        <v>1000.016892956751</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09435361548114216</v>
+        <v>0.0943309404640251</v>
       </c>
       <c r="T57">
         <v>0.9459583602358328</v>
       </c>
       <c r="U57">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.208019380242958</v>
+        <v>2.372803766598111</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6004,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07882917516197679</v>
+        <v>0.0762570009803834</v>
       </c>
       <c r="C58">
-        <v>1701.698865644898</v>
+        <v>1757.973204326931</v>
       </c>
       <c r="D58">
-        <v>3601.677642124604</v>
+        <v>3657.951980806637</v>
       </c>
       <c r="E58">
         <v>-748.4190386626256</v>
@@ -6037,37 +6037,37 @@
         <v>473.4</v>
       </c>
       <c r="M58">
-        <v>218.2984791891797</v>
+        <v>203.1382786526535</v>
       </c>
       <c r="N58">
-        <v>255.1015208108203</v>
+        <v>270.2617213473465</v>
       </c>
       <c r="O58">
-        <v>63.77538020270507</v>
+        <v>67.56543033683661</v>
       </c>
       <c r="P58">
-        <v>191.3261406081152</v>
+        <v>202.6962910105098</v>
       </c>
       <c r="Q58">
-        <v>985.9261406081152</v>
+        <v>997.2962910105099</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09531317309934653</v>
+        <v>0.09529004995936155</v>
       </c>
       <c r="T58">
         <v>0.9646531894895052</v>
       </c>
       <c r="U58">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.168590462738619</v>
+        <v>2.330432270766001</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07896661898414431</v>
+        <v>0.07634872437866021</v>
       </c>
       <c r="C59">
-        <v>1654.349319282184</v>
+        <v>1711.548506080867</v>
       </c>
       <c r="D59">
-        <v>3598.708073913314</v>
+        <v>3655.907260711996</v>
       </c>
       <c r="E59">
         <v>-704.0390605112025</v>
@@ -6119,37 +6119,37 @@
         <v>473.4</v>
       </c>
       <c r="M59">
-        <v>222.1966663175579</v>
+        <v>206.765747914308</v>
       </c>
       <c r="N59">
-        <v>251.2033336824421</v>
+        <v>266.634252085692</v>
       </c>
       <c r="O59">
-        <v>62.80083342061052</v>
+        <v>66.65856302142299</v>
       </c>
       <c r="P59">
-        <v>188.4025002618316</v>
+        <v>199.975689064269</v>
       </c>
       <c r="Q59">
-        <v>983.0025002618315</v>
+        <v>994.575689064269</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09631736130444417</v>
+        <v>0.09629376919866717</v>
       </c>
       <c r="T59">
         <v>0.9842175456852091</v>
       </c>
       <c r="U59">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.130545016023906</v>
+        <v>2.289547494085896</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07910406280631183</v>
+        <v>0.07644044777693701</v>
       </c>
       <c r="C60">
-        <v>1607.004665678649</v>
+        <v>1665.126092470886</v>
       </c>
       <c r="D60">
-        <v>3595.743398461202</v>
+        <v>3653.864825253439</v>
       </c>
       <c r="E60">
         <v>-659.6590823597794</v>
@@ -6201,37 +6201,37 @@
         <v>473.4</v>
       </c>
       <c r="M60">
-        <v>226.0948534459361</v>
+        <v>210.3932171759625</v>
       </c>
       <c r="N60">
-        <v>247.3051465540639</v>
+        <v>263.0067828240375</v>
       </c>
       <c r="O60">
-        <v>61.82628663851597</v>
+        <v>65.75169570600937</v>
       </c>
       <c r="P60">
-        <v>185.4788599155479</v>
+        <v>197.2550871180281</v>
       </c>
       <c r="Q60">
-        <v>980.0788599155479</v>
+        <v>991.8550871180281</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09736936799549881</v>
+        <v>0.09734528459222541</v>
       </c>
       <c r="T60">
         <v>1.004713537890232</v>
       </c>
       <c r="U60">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.093811481264874</v>
+        <v>2.250072537291312</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07924150662847934</v>
+        <v>0.0765321711752138</v>
       </c>
       <c r="C61">
-        <v>1559.664892752037</v>
+        <v>1618.705959670073</v>
       </c>
       <c r="D61">
-        <v>3592.783603686013</v>
+        <v>3651.82467060405</v>
       </c>
       <c r="E61">
         <v>-615.2791042083559</v>
@@ -6283,37 +6283,37 @@
         <v>473.4</v>
       </c>
       <c r="M61">
-        <v>229.9930405743143</v>
+        <v>214.0206864376171</v>
       </c>
       <c r="N61">
-        <v>243.4069594256857</v>
+        <v>259.3793135623829</v>
       </c>
       <c r="O61">
-        <v>60.85173985642142</v>
+        <v>64.84482839059572</v>
       </c>
       <c r="P61">
-        <v>182.5552195692642</v>
+        <v>194.5344851717872</v>
       </c>
       <c r="Q61">
-        <v>977.1552195692643</v>
+        <v>989.1344851717872</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.09847269208611709</v>
+        <v>0.09844809341961577</v>
       </c>
       <c r="T61">
         <v>1.026209334593061</v>
       </c>
       <c r="U61">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.058323151073943</v>
+        <v>2.211935714625357</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6332,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.07937895045064687</v>
+        <v>0.0766238945734906</v>
       </c>
       <c r="C62">
-        <v>1512.329988459842</v>
+        <v>1572.288103860056</v>
       </c>
       <c r="D62">
-        <v>3589.828677545241</v>
+        <v>3649.786792945456</v>
       </c>
       <c r="E62">
         <v>-570.8991260569328</v>
@@ -6365,37 +6365,37 @@
         <v>473.4</v>
       </c>
       <c r="M62">
-        <v>233.8912277026925</v>
+        <v>217.6481556992716</v>
       </c>
       <c r="N62">
-        <v>239.5087722973075</v>
+        <v>255.7518443007284</v>
       </c>
       <c r="O62">
-        <v>59.87719307432688</v>
+        <v>63.9379610751821</v>
       </c>
       <c r="P62">
-        <v>179.6315792229806</v>
+        <v>191.8138832255463</v>
       </c>
       <c r="Q62">
-        <v>974.2315792229806</v>
+        <v>986.4138832255463</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.09963118238126631</v>
+        <v>0.09960604268837564</v>
       </c>
       <c r="T62">
         <v>1.048779921131032</v>
       </c>
       <c r="U62">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.024017765222712</v>
+        <v>2.175070119381601</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08697364427281438</v>
+        <v>0.0767156179717674</v>
       </c>
       <c r="C63">
-        <v>1311.896867967844</v>
+        <v>1525.872521230979</v>
       </c>
       <c r="D63">
-        <v>3433.775535204666</v>
+        <v>3647.751188467802</v>
       </c>
       <c r="E63">
         <v>-526.5191479055093</v>
@@ -6447,45 +6447,45 @@
         <v>473.4</v>
       </c>
       <c r="M63">
-        <v>281.9164271070309</v>
+        <v>221.2756249609261</v>
       </c>
       <c r="N63">
-        <v>191.4835728929691</v>
+        <v>252.1243750390739</v>
       </c>
       <c r="O63">
-        <v>47.87089322324226</v>
+        <v>63.03109375976847</v>
       </c>
       <c r="P63">
-        <v>143.6126796697268</v>
+        <v>189.0932812793054</v>
       </c>
       <c r="Q63">
-        <v>938.2126796697269</v>
+        <v>983.6932812793054</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1008490824351411</v>
+        <v>0.1008233739709181</v>
       </c>
       <c r="T63">
         <v>1.072507973645309</v>
       </c>
       <c r="U63">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.679221054473251</v>
+        <v>2.139413232178624</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6496,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.0872333380949819</v>
+        <v>0.0768073413700442</v>
       </c>
       <c r="C64">
-        <v>1262.42033184606</v>
+        <v>1479.459207981482</v>
       </c>
       <c r="D64">
-        <v>3428.678977234306</v>
+        <v>3645.717853369728</v>
       </c>
       <c r="E64">
         <v>-482.1391697540862</v>
@@ -6529,45 +6529,45 @@
         <v>473.4</v>
       </c>
       <c r="M64">
-        <v>286.5380078792774</v>
+        <v>224.9030942225806</v>
       </c>
       <c r="N64">
-        <v>186.8619921207226</v>
+        <v>248.4969057774194</v>
       </c>
       <c r="O64">
-        <v>46.71549803018065</v>
+        <v>62.12422644435484</v>
       </c>
       <c r="P64">
-        <v>140.146494090542</v>
+        <v>186.3726793330645</v>
       </c>
       <c r="Q64">
-        <v>934.746494090542</v>
+        <v>980.9726793330645</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1021310824918514</v>
+        <v>0.1021047753209628</v>
       </c>
       <c r="T64">
         <v>1.097484871028758</v>
       </c>
       <c r="U64">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.652136843917231</v>
+        <v>2.104906567143485</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6578,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08749303191714941</v>
+        <v>0.07689906476832101</v>
       </c>
       <c r="C65">
-        <v>1212.958902365315</v>
+        <v>1433.048160318676</v>
       </c>
       <c r="D65">
-        <v>3423.597525904984</v>
+        <v>3643.686783858345</v>
       </c>
       <c r="E65">
         <v>-437.7591916026627</v>
@@ -6611,45 +6611,45 @@
         <v>473.4</v>
       </c>
       <c r="M65">
-        <v>291.1595886515237</v>
+        <v>228.5305634842352</v>
       </c>
       <c r="N65">
-        <v>182.2404113484762</v>
+        <v>244.8694365157648</v>
       </c>
       <c r="O65">
-        <v>45.56010283711906</v>
+        <v>61.2173591289412</v>
       </c>
       <c r="P65">
-        <v>136.6803085113572</v>
+        <v>183.6520773868236</v>
       </c>
       <c r="Q65">
-        <v>931.2803085113571</v>
+        <v>978.2520773868237</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1034823798489245</v>
+        <v>0.1034554416088477</v>
       </c>
       <c r="T65">
         <v>1.123811870973475</v>
       </c>
       <c r="U65">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.625912449569339</v>
+        <v>2.071495351792001</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08775272573931693</v>
+        <v>0.0769907881665978</v>
       </c>
       <c r="C66">
-        <v>1163.512512458907</v>
+        <v>1386.63937445812</v>
       </c>
       <c r="D66">
-        <v>3418.53111415</v>
+        <v>3641.657976149213</v>
       </c>
       <c r="E66">
         <v>-393.3792134512391</v>
@@ -6693,45 +6693,45 @@
         <v>473.4</v>
       </c>
       <c r="M66">
-        <v>295.7811694237702</v>
+        <v>232.1580327458897</v>
       </c>
       <c r="N66">
-        <v>177.6188305762298</v>
+        <v>241.2419672541103</v>
       </c>
       <c r="O66">
-        <v>44.40470764405745</v>
+        <v>60.31049181352757</v>
       </c>
       <c r="P66">
-        <v>133.2141229321724</v>
+        <v>180.9314754405827</v>
       </c>
       <c r="Q66">
-        <v>927.8141229321724</v>
+        <v>975.5314754405828</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1049087492813904</v>
+        <v>0.1048811449127262</v>
       </c>
       <c r="T66">
         <v>1.151601482026231</v>
       </c>
       <c r="U66">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.600507567544818</v>
+        <v>2.039128236920251</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08801241956148445</v>
+        <v>0.0770825115648746</v>
       </c>
       <c r="C67">
-        <v>1114.081095456546</v>
+        <v>1340.232846623797</v>
       </c>
       <c r="D67">
-        <v>3413.479675299061</v>
+        <v>3639.631426466312</v>
       </c>
       <c r="E67">
         <v>-348.9992352998161</v>
@@ -6775,45 +6775,45 @@
         <v>473.4</v>
       </c>
       <c r="M67">
-        <v>300.4027501960166</v>
+        <v>235.7855020075442</v>
       </c>
       <c r="N67">
-        <v>172.9972498039834</v>
+        <v>237.6144979924558</v>
       </c>
       <c r="O67">
-        <v>43.24931245099584</v>
+        <v>59.40362449811394</v>
       </c>
       <c r="P67">
-        <v>129.7479373529875</v>
+        <v>178.2108734943418</v>
       </c>
       <c r="Q67">
-        <v>924.3479373529876</v>
+        <v>972.8108734943419</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1064166255385688</v>
+        <v>0.1063883169768264</v>
       </c>
       <c r="T67">
         <v>1.180979070853431</v>
       </c>
       <c r="U67">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.575884374197974</v>
+        <v>2.007757033275325</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08827211338365196</v>
+        <v>0.08420323496315139</v>
       </c>
       <c r="C68">
-        <v>1064.66458508142</v>
+        <v>1145.125835921453</v>
       </c>
       <c r="D68">
-        <v>3408.443143075359</v>
+        <v>3488.904393915393</v>
       </c>
       <c r="E68">
         <v>-304.6192571483925</v>
@@ -6857,37 +6857,37 @@
         <v>473.4</v>
       </c>
       <c r="M68">
-        <v>305.024330968263</v>
+        <v>281.0058867927127</v>
       </c>
       <c r="N68">
-        <v>168.3756690317369</v>
+        <v>192.3941132072873</v>
       </c>
       <c r="O68">
-        <v>42.09391725793424</v>
+        <v>48.09852830182182</v>
       </c>
       <c r="P68">
-        <v>126.2817517738027</v>
+        <v>144.2955849054654</v>
       </c>
       <c r="Q68">
-        <v>920.8817517738028</v>
+        <v>938.8955849054655</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1080132003991105</v>
+        <v>0.1079841462211677</v>
       </c>
       <c r="T68">
         <v>1.212084753141054</v>
       </c>
       <c r="U68">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.552007338225277</v>
+        <v>1.684662216166343</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08853180720581946</v>
+        <v>0.08440145836142819</v>
       </c>
       <c r="C69">
-        <v>1015.262915447306</v>
+        <v>1096.728382296647</v>
       </c>
       <c r="D69">
-        <v>3403.421451592669</v>
+        <v>3484.88691844201</v>
       </c>
       <c r="E69">
         <v>-260.239278996969</v>
@@ -6939,37 +6939,37 @@
         <v>473.4</v>
       </c>
       <c r="M69">
-        <v>309.6459117405095</v>
+        <v>285.2635517441175</v>
       </c>
       <c r="N69">
-        <v>163.7540882594905</v>
+        <v>188.1364482558825</v>
       </c>
       <c r="O69">
-        <v>40.93852206487263</v>
+        <v>47.03411206397062</v>
       </c>
       <c r="P69">
-        <v>122.8155661946179</v>
+        <v>141.1023361919119</v>
       </c>
       <c r="Q69">
-        <v>917.4155661946179</v>
+        <v>935.7023361919119</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1097065373724124</v>
+        <v>0.1096766923894085</v>
       </c>
       <c r="T69">
         <v>1.245075628294594</v>
       </c>
       <c r="U69">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.528843049595049</v>
+        <v>1.659518003984756</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.088791501027987</v>
+        <v>0.084599681759705</v>
       </c>
       <c r="C70">
-        <v>965.8760210556916</v>
+        <v>1048.340170280891</v>
       </c>
       <c r="D70">
-        <v>3398.414535352478</v>
+        <v>3480.878684577677</v>
       </c>
       <c r="E70">
         <v>-215.8593008455459</v>
@@ -7021,37 +7021,37 @@
         <v>473.4</v>
       </c>
       <c r="M70">
-        <v>314.2674925127558</v>
+        <v>289.5212166955222</v>
       </c>
       <c r="N70">
-        <v>159.1325074872441</v>
+        <v>183.8787833044778</v>
       </c>
       <c r="O70">
-        <v>39.78312687181104</v>
+        <v>45.96969582611945</v>
       </c>
       <c r="P70">
-        <v>119.3493806154331</v>
+        <v>137.9090874783583</v>
       </c>
       <c r="Q70">
-        <v>913.9493806154331</v>
+        <v>932.5090874783584</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1115057079065457</v>
+        <v>0.1114750226931644</v>
       </c>
       <c r="T70">
         <v>1.28012843314523</v>
       </c>
       <c r="U70">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.506360063571593</v>
+        <v>1.635113327455568</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7070,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1258584830655462</v>
+        <v>0.0847979051579818</v>
       </c>
       <c r="C71">
-        <v>331.7324354749876</v>
+        <v>999.9611680223838</v>
       </c>
       <c r="D71">
-        <v>2808.650927923197</v>
+        <v>3476.879660470594</v>
       </c>
       <c r="E71">
         <v>-171.4793226941224</v>
@@ -7103,45 +7103,45 @@
         <v>473.4</v>
       </c>
       <c r="M71">
-        <v>519.1581626911152</v>
+        <v>293.7788816469269</v>
       </c>
       <c r="N71">
-        <v>-45.75816269111522</v>
+        <v>179.621118353073</v>
       </c>
       <c r="O71">
-        <v>-11.4395406727788</v>
+        <v>44.90527958826826</v>
       </c>
       <c r="P71">
-        <v>-34.31862201833641</v>
+        <v>134.7158387648048</v>
       </c>
       <c r="Q71">
-        <v>760.2813779816636</v>
+        <v>929.3158387648048</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1146633821054889</v>
+        <v>0.11338937430684</v>
       </c>
       <c r="T71">
-        <v>1.341648636693233</v>
+        <v>1.317442709276553</v>
       </c>
       <c r="U71">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V71">
-        <v>0.2279652108068943</v>
+        <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.1308881661055719</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.9118608432275771</v>
+        <v>1.611416032854763</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7152,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1270958492321715</v>
+        <v>0.0849961285562586</v>
       </c>
       <c r="C72">
-        <v>271.1753177680894</v>
+        <v>951.5913438155312</v>
       </c>
       <c r="D72">
-        <v>2792.473788367722</v>
+        <v>3472.889814415164</v>
       </c>
       <c r="E72">
         <v>-127.0993445426993</v>
@@ -7185,45 +7185,45 @@
         <v>473.4</v>
       </c>
       <c r="M72">
-        <v>526.6821940344646</v>
+        <v>298.0365465983317</v>
       </c>
       <c r="N72">
-        <v>-53.28219403446462</v>
+        <v>175.3634534016683</v>
       </c>
       <c r="O72">
-        <v>-13.32054850861616</v>
+        <v>43.84086335041708</v>
       </c>
       <c r="P72">
-        <v>-39.96164552584847</v>
+        <v>131.5225900512513</v>
       </c>
       <c r="Q72">
-        <v>754.6383544741516</v>
+        <v>926.1225900512513</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1169588281756718</v>
+        <v>0.1154313493614273</v>
       </c>
       <c r="T72">
-        <v>1.386370257916341</v>
+        <v>1.35724460381663</v>
       </c>
       <c r="U72">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V72">
-        <v>0.2247085649382244</v>
+        <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.1314402868278142</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.8988342597528977</v>
+        <v>1.588395803813981</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1283332153987968</v>
+        <v>0.0851943519545354</v>
       </c>
       <c r="C73">
-        <v>210.8034855638439</v>
+        <v>903.2306661001035</v>
       </c>
       <c r="D73">
-        <v>2776.4819343149</v>
+        <v>3468.909114851159</v>
       </c>
       <c r="E73">
         <v>-82.71936639127625</v>
@@ -7267,45 +7267,45 @@
         <v>473.4</v>
       </c>
       <c r="M73">
-        <v>534.2062253778141</v>
+        <v>302.2942115497364</v>
       </c>
       <c r="N73">
-        <v>-60.80622537781414</v>
+        <v>171.1057884502636</v>
       </c>
       <c r="O73">
-        <v>-15.20155634445354</v>
+        <v>42.7764471125659</v>
       </c>
       <c r="P73">
-        <v>-45.60466903336061</v>
+        <v>128.3293413376977</v>
       </c>
       <c r="Q73">
-        <v>748.9953309666394</v>
+        <v>922.9293413376977</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1194125808713846</v>
+        <v>0.1176141502818482</v>
       </c>
       <c r="T73">
-        <v>1.434176128878973</v>
+        <v>1.39979145660085</v>
       </c>
       <c r="U73">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V73">
-        <v>0.2215436555728973</v>
+        <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.1319768548536553</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8861746222915892</v>
+        <v>1.566024031929277</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7316,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1295705815654222</v>
+        <v>0.08539257535281219</v>
       </c>
       <c r="C74">
-        <v>150.6137737260956</v>
+        <v>854.879103460406</v>
       </c>
       <c r="D74">
-        <v>2760.672200628575</v>
+        <v>3464.937530362885</v>
       </c>
       <c r="E74">
         <v>-38.33938823985272</v>
@@ -7349,45 +7349,45 @@
         <v>473.4</v>
       </c>
       <c r="M74">
-        <v>541.7302567211636</v>
+        <v>306.5518765011411</v>
       </c>
       <c r="N74">
-        <v>-68.33025672116366</v>
+        <v>166.8481234988589</v>
       </c>
       <c r="O74">
-        <v>-17.08256418029092</v>
+        <v>41.71203087471471</v>
       </c>
       <c r="P74">
-        <v>-51.24769254087275</v>
+        <v>125.1360926241441</v>
       </c>
       <c r="Q74">
-        <v>743.3523074591272</v>
+        <v>919.7360926241441</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1220416016167912</v>
+        <v>0.1199528655537278</v>
       </c>
       <c r="T74">
-        <v>1.485396704910365</v>
+        <v>1.445377370298229</v>
       </c>
       <c r="U74">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V74">
-        <v>0.218466660356607</v>
+        <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.132498518212112</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.8738666414264281</v>
+        <v>1.544273698152482</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1308079477320475</v>
+        <v>0.08559079875108899</v>
       </c>
       <c r="C75">
-        <v>90.60308880168759</v>
+        <v>806.5366246244503</v>
       </c>
       <c r="D75">
-        <v>2745.04149385559</v>
+        <v>3460.975029678353</v>
       </c>
       <c r="E75">
         <v>6.040589911570351</v>
@@ -7431,45 +7431,45 @@
         <v>473.4</v>
       </c>
       <c r="M75">
-        <v>549.254288064513</v>
+        <v>310.8095414525458</v>
       </c>
       <c r="N75">
-        <v>-75.85428806451307</v>
+        <v>162.5904585474541</v>
       </c>
       <c r="O75">
-        <v>-18.96357201612827</v>
+        <v>40.64761463686354</v>
       </c>
       <c r="P75">
-        <v>-56.8907160483848</v>
+        <v>121.9428439105906</v>
       </c>
       <c r="Q75">
-        <v>737.7092839516152</v>
+        <v>916.5428439105906</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1248653646396353</v>
+        <v>0.1224648189938947</v>
       </c>
       <c r="T75">
-        <v>1.540411397684822</v>
+        <v>1.494340018343562</v>
       </c>
       <c r="U75">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V75">
-        <v>0.2154739663791193</v>
+        <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.1330058894237616</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8618958655164772</v>
+        <v>1.523119263931215</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1320453138986729</v>
+        <v>0.08578902214936579</v>
       </c>
       <c r="C76">
-        <v>30.76840700256525</v>
+        <v>758.2031984631376</v>
       </c>
       <c r="D76">
-        <v>2729.586790207891</v>
+        <v>3457.021581668464</v>
       </c>
       <c r="E76">
         <v>50.42056806299388</v>
@@ -7513,45 +7513,45 @@
         <v>473.4</v>
       </c>
       <c r="M76">
-        <v>556.7783194078626</v>
+        <v>315.0672064039506</v>
       </c>
       <c r="N76">
-        <v>-83.37831940786259</v>
+        <v>158.3327935960494</v>
       </c>
       <c r="O76">
-        <v>-20.84457985196565</v>
+        <v>39.58319839901235</v>
       </c>
       <c r="P76">
-        <v>-62.53373955589694</v>
+        <v>118.749595197037</v>
       </c>
       <c r="Q76">
-        <v>732.0662604441031</v>
+        <v>913.349595197037</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1279063402026982</v>
+        <v>0.1251699996217668</v>
       </c>
       <c r="T76">
-        <v>1.59965798990347</v>
+        <v>1.547069023930843</v>
       </c>
       <c r="U76">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V76">
-        <v>0.2125621560226447</v>
+        <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.1334995478999612</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.8502486240905789</v>
+        <v>1.502536571175388</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1332826800652982</v>
+        <v>0.1202346280086119</v>
       </c>
       <c r="C77">
-        <v>-28.89322774432458</v>
+        <v>141.2629658018068</v>
       </c>
       <c r="D77">
-        <v>2714.305133612425</v>
+        <v>2884.461327158556</v>
       </c>
       <c r="E77">
         <v>94.80054621441741</v>
@@ -7595,37 +7595,37 @@
         <v>473.4</v>
       </c>
       <c r="M77">
-        <v>564.3023507512121</v>
+        <v>508.3835782804187</v>
       </c>
       <c r="N77">
-        <v>-90.90235075121211</v>
+        <v>-34.98357828041873</v>
       </c>
       <c r="O77">
-        <v>-22.72558768780303</v>
+        <v>-8.745894570104682</v>
       </c>
       <c r="P77">
-        <v>-68.17676306340908</v>
+        <v>-26.23768371031404</v>
       </c>
       <c r="Q77">
-        <v>726.4232369365909</v>
+        <v>768.362316289686</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1311905938108062</v>
+        <v>0.1293983855840611</v>
       </c>
       <c r="T77">
-        <v>1.663644309499609</v>
+        <v>1.629488136626613</v>
       </c>
       <c r="U77">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V77">
-        <v>0.2097279939423428</v>
+        <v>0.2327966619227017</v>
       </c>
       <c r="W77">
-        <v>0.1339800421501289</v>
+        <v>0.1171800421501289</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.838911975769371</v>
+        <v>0.9311866476908068</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1345200462319235</v>
+        <v>0.1213039941752373</v>
       </c>
       <c r="C78">
-        <v>-88.38470568200455</v>
+        <v>82.12765100856768</v>
       </c>
       <c r="D78">
-        <v>2699.193633826168</v>
+        <v>2869.70599051674</v>
       </c>
       <c r="E78">
         <v>139.1805243658405</v>
@@ -7677,37 +7677,37 @@
         <v>473.4</v>
       </c>
       <c r="M78">
-        <v>571.8263820945616</v>
+        <v>515.1620259908243</v>
       </c>
       <c r="N78">
-        <v>-98.42638209456163</v>
+        <v>-41.76202599082433</v>
       </c>
       <c r="O78">
-        <v>-24.60659552364041</v>
+        <v>-10.44050649770608</v>
       </c>
       <c r="P78">
-        <v>-73.81978657092122</v>
+        <v>-31.32151949311825</v>
       </c>
       <c r="Q78">
-        <v>720.7802134290788</v>
+        <v>763.2784805068818</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1347485352195898</v>
+        <v>0.1328816516500637</v>
       </c>
       <c r="T78">
-        <v>1.732962822395426</v>
+        <v>1.697383475652721</v>
       </c>
       <c r="U78">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V78">
-        <v>0.2069684150746804</v>
+        <v>0.2297335479500346</v>
       </c>
       <c r="W78">
-        <v>0.1344478918147658</v>
+        <v>0.1176478918147658</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8278736602987214</v>
+        <v>0.9189341918001384</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7726,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1357574123985489</v>
+        <v>0.1223733603418626</v>
       </c>
       <c r="C79">
-        <v>-147.7088530458236</v>
+        <v>23.14252848079877</v>
       </c>
       <c r="D79">
-        <v>2684.249464613772</v>
+        <v>2855.100846140395</v>
       </c>
       <c r="E79">
         <v>183.560502517264</v>
@@ -7759,37 +7759,37 @@
         <v>473.4</v>
       </c>
       <c r="M79">
-        <v>579.3504134379111</v>
+        <v>521.9404737012298</v>
       </c>
       <c r="N79">
-        <v>-105.9504134379112</v>
+        <v>-48.54047370122987</v>
       </c>
       <c r="O79">
-        <v>-26.48760335947779</v>
+        <v>-12.13511842530747</v>
       </c>
       <c r="P79">
-        <v>-79.46281007843336</v>
+        <v>-36.4053552759224</v>
       </c>
       <c r="Q79">
-        <v>715.1371899215667</v>
+        <v>758.1946447240776</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1386158628378328</v>
+        <v>0.1366678104174577</v>
       </c>
       <c r="T79">
-        <v>1.808309032064792</v>
+        <v>1.77118275720284</v>
       </c>
       <c r="U79">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V79">
-        <v>0.204280513580204</v>
+        <v>0.2267499953792549</v>
       </c>
       <c r="W79">
-        <v>0.1349035895400615</v>
+        <v>0.1181035895400615</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.817122054320816</v>
+        <v>0.9069999815170197</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1369947785651742</v>
+        <v>0.1234427265084879</v>
       </c>
       <c r="C80">
-        <v>-206.8684338255862</v>
+        <v>-35.69468334505291</v>
       </c>
       <c r="D80">
-        <v>2669.469861985433</v>
+        <v>2840.643612465966</v>
       </c>
       <c r="E80">
         <v>227.9404806686871</v>
@@ -7841,37 +7841,37 @@
         <v>473.4</v>
       </c>
       <c r="M80">
-        <v>586.8744447812605</v>
+        <v>528.7189214116354</v>
       </c>
       <c r="N80">
-        <v>-113.4744447812606</v>
+        <v>-55.31892141163542</v>
       </c>
       <c r="O80">
-        <v>-28.36861119531514</v>
+        <v>-13.82973035290885</v>
       </c>
       <c r="P80">
-        <v>-85.10583358594542</v>
+        <v>-41.48919105872656</v>
       </c>
       <c r="Q80">
-        <v>709.4941664140546</v>
+        <v>753.1108089412735</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1428347656940979</v>
+        <v>0.1407981654364331</v>
       </c>
       <c r="T80">
-        <v>1.890504897158646</v>
+        <v>1.851691064348423</v>
       </c>
       <c r="U80">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V80">
-        <v>0.2016615326368681</v>
+        <v>0.223842944156444</v>
       </c>
       <c r="W80">
-        <v>0.1353476027082983</v>
+        <v>0.1185476027082983</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8066461305474723</v>
+        <v>0.8953717766257759</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1804081941906341</v>
+        <v>0.1245120926751133</v>
       </c>
       <c r="C81">
-        <v>-683.4477541922815</v>
+        <v>-94.38622005320121</v>
       </c>
       <c r="D81">
-        <v>2237.270519770161</v>
+        <v>2826.332053909241</v>
       </c>
       <c r="E81">
         <v>272.3204588201106</v>
@@ -7923,45 +7923,45 @@
         <v>473.4</v>
       </c>
       <c r="M81">
-        <v>777.4126300254496</v>
+        <v>535.4973691220411</v>
       </c>
       <c r="N81">
-        <v>-304.0126300254497</v>
+        <v>-62.09736912204107</v>
       </c>
       <c r="O81">
-        <v>-76.00315750636241</v>
+        <v>-15.52434228051027</v>
       </c>
       <c r="P81">
-        <v>-228.0094725190872</v>
+        <v>-46.5730268415308</v>
       </c>
       <c r="Q81">
-        <v>566.5905274809128</v>
+        <v>748.0269731584692</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1519223710073146</v>
+        <v>0.1453218876000728</v>
       </c>
       <c r="T81">
-        <v>2.067556515979899</v>
+        <v>1.939866829317396</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V81">
-        <v>0.1522357566999209</v>
+        <v>0.2210094891671219</v>
       </c>
       <c r="W81">
-        <v>0.1879803750368329</v>
+        <v>0.1189803750368329</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.6089430267996837</v>
+        <v>0.8840379566684875</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +7972,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1821675603572595</v>
+        <v>0.1255814588417386</v>
       </c>
       <c r="C82">
-        <v>-742.4114961232772</v>
+        <v>-152.9342724009648</v>
       </c>
       <c r="D82">
-        <v>2222.686755990589</v>
+        <v>2812.163979712901</v>
       </c>
       <c r="E82">
         <v>316.7004369715341</v>
@@ -8005,45 +8005,45 @@
         <v>473.4</v>
       </c>
       <c r="M82">
-        <v>787.2532962283034</v>
+        <v>542.2758168324467</v>
       </c>
       <c r="N82">
-        <v>-313.8532962283034</v>
+        <v>-68.87581683244673</v>
       </c>
       <c r="O82">
-        <v>-78.46332405707585</v>
+        <v>-17.21895420811168</v>
       </c>
       <c r="P82">
-        <v>-235.3899721712276</v>
+        <v>-51.65686262433505</v>
       </c>
       <c r="Q82">
-        <v>559.2100278287725</v>
+        <v>742.9431373756649</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1572284895576803</v>
+        <v>0.1502979819800764</v>
       </c>
       <c r="T82">
-        <v>2.170934341778894</v>
+        <v>2.036860170783267</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V82">
-        <v>0.1503328097411719</v>
+        <v>0.2182468705525328</v>
       </c>
       <c r="W82">
-        <v>0.1884023280571542</v>
+        <v>0.1194023280571542</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.6013312389646877</v>
+        <v>0.8729874822101313</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1839269265238848</v>
+        <v>0.126650825008364</v>
       </c>
       <c r="C83">
-        <v>-801.1863393608414</v>
+        <v>-211.3409874367185</v>
       </c>
       <c r="D83">
-        <v>2208.291890904448</v>
+        <v>2798.137242828571</v>
       </c>
       <c r="E83">
         <v>361.0804151229572</v>
@@ -8087,45 +8087,45 @@
         <v>473.4</v>
       </c>
       <c r="M83">
-        <v>797.0939624311571</v>
+        <v>549.0542645428523</v>
       </c>
       <c r="N83">
-        <v>-323.6939624311572</v>
+        <v>-75.65426454285227</v>
       </c>
       <c r="O83">
-        <v>-80.92349060778929</v>
+        <v>-18.91356613571307</v>
       </c>
       <c r="P83">
-        <v>-242.7704718233679</v>
+        <v>-56.74069840713921</v>
       </c>
       <c r="Q83">
-        <v>551.8295281766322</v>
+        <v>737.8593015928608</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1630931469028214</v>
+        <v>0.1557978757685015</v>
       </c>
       <c r="T83">
-        <v>2.285194043977783</v>
+        <v>2.144063337666596</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V83">
-        <v>0.1484768491270834</v>
+        <v>0.2155524647432423</v>
       </c>
       <c r="W83">
-        <v>0.1888138624843811</v>
+        <v>0.1198138624843811</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5939073965083336</v>
+        <v>0.8622098589729692</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1856862926905101</v>
+        <v>0.1277201911749893</v>
       </c>
       <c r="C84">
-        <v>-859.7759304029601</v>
+        <v>-269.608469584567</v>
       </c>
       <c r="D84">
-        <v>2194.082278013752</v>
+        <v>2784.249738832146</v>
       </c>
       <c r="E84">
         <v>405.4603932743807</v>
@@ -8169,45 +8169,45 @@
         <v>473.4</v>
       </c>
       <c r="M84">
-        <v>806.934628634011</v>
+        <v>555.8327122532578</v>
       </c>
       <c r="N84">
-        <v>-333.534628634011</v>
+        <v>-82.43271225325782</v>
       </c>
       <c r="O84">
-        <v>-83.38365715850276</v>
+        <v>-20.60817806331445</v>
       </c>
       <c r="P84">
-        <v>-250.1509714755083</v>
+        <v>-61.82453418994336</v>
       </c>
       <c r="Q84">
-        <v>544.4490285244917</v>
+        <v>732.7754658100566</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.169609432841867</v>
+        <v>0.1619088688667516</v>
       </c>
       <c r="T84">
-        <v>2.412149268643216</v>
+        <v>2.263177967536962</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V84">
-        <v>0.1466661558450458</v>
+        <v>0.2129237761488125</v>
       </c>
       <c r="W84">
-        <v>0.1892153594865537</v>
+        <v>0.1202153594865537</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.5866646233801831</v>
+        <v>0.8516951045952501</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8218,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1874456588571355</v>
+        <v>0.1287895573416147</v>
       </c>
       <c r="C85">
-        <v>-918.1838224917524</v>
+        <v>-327.7387816968608</v>
       </c>
       <c r="D85">
-        <v>2180.054364076384</v>
+        <v>2770.499404871275</v>
       </c>
       <c r="E85">
         <v>449.8403714258043</v>
@@ -8251,45 +8251,45 @@
         <v>473.4</v>
       </c>
       <c r="M85">
-        <v>816.7752948368649</v>
+        <v>562.6111599636635</v>
       </c>
       <c r="N85">
-        <v>-343.3752948368649</v>
+        <v>-89.21115996366348</v>
       </c>
       <c r="O85">
-        <v>-85.84382370921622</v>
+        <v>-22.30278999091587</v>
       </c>
       <c r="P85">
-        <v>-257.5314711276487</v>
+        <v>-66.90836997274761</v>
       </c>
       <c r="Q85">
-        <v>537.0685288723514</v>
+        <v>727.6916300272524</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1768923406560945</v>
+        <v>0.1687388023295017</v>
       </c>
       <c r="T85">
-        <v>2.554040402092816</v>
+        <v>2.396306083274431</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V85">
-        <v>0.1448990937264308</v>
+        <v>0.2103584294482244</v>
       </c>
       <c r="W85">
-        <v>0.1896071818621679</v>
+        <v>0.1206071818621679</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.579596374905723</v>
+        <v>0.8414337177928977</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1892050250237608</v>
+        <v>0.12985892350824</v>
       </c>
       <c r="C86">
-        <v>-976.4134785757001</v>
+        <v>-385.7339460756898</v>
       </c>
       <c r="D86">
-        <v>2166.204686143859</v>
+        <v>2756.884218643869</v>
       </c>
       <c r="E86">
         <v>494.2203495772269</v>
@@ -8333,45 +8333,45 @@
         <v>473.4</v>
       </c>
       <c r="M86">
-        <v>826.6159610397185</v>
+        <v>569.3896076740689</v>
       </c>
       <c r="N86">
-        <v>-353.2159610397185</v>
+        <v>-95.98960767406891</v>
       </c>
       <c r="O86">
-        <v>-88.30399025992963</v>
+        <v>-23.99740191851723</v>
       </c>
       <c r="P86">
-        <v>-264.9119707797889</v>
+        <v>-71.99220575555168</v>
       </c>
       <c r="Q86">
-        <v>529.6880292202111</v>
+        <v>722.6077942444483</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1850856119471003</v>
+        <v>0.1764224774750955</v>
       </c>
       <c r="T86">
-        <v>2.713667927223616</v>
+        <v>2.546075213479082</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V86">
-        <v>0.1431741045154018</v>
+        <v>0.2078541624309837</v>
       </c>
       <c r="W86">
-        <v>0.1899896751336009</v>
+        <v>0.1209896751336008</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5726964180616074</v>
+        <v>0.8314166497239348</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8382,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1909643911903861</v>
+        <v>0.1309282896748653</v>
       </c>
       <c r="C87">
-        <v>-1034.468274159679</v>
+        <v>-443.5959454644012</v>
       </c>
       <c r="D87">
-        <v>2152.529868711303</v>
+        <v>2743.402197406581</v>
       </c>
       <c r="E87">
         <v>538.6003277286504</v>
@@ -8415,45 +8415,45 @@
         <v>473.4</v>
       </c>
       <c r="M87">
-        <v>836.4566272425723</v>
+        <v>576.1680553844745</v>
       </c>
       <c r="N87">
-        <v>-363.0566272425723</v>
+        <v>-102.7680553844746</v>
       </c>
       <c r="O87">
-        <v>-90.76415681064307</v>
+        <v>-25.69201384611864</v>
       </c>
       <c r="P87">
-        <v>-272.2924704319292</v>
+        <v>-77.07604153835592</v>
       </c>
       <c r="Q87">
-        <v>522.3075295680708</v>
+        <v>717.523958461644</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1943713194102404</v>
+        <v>0.1851306426401018</v>
       </c>
       <c r="T87">
-        <v>2.894579122371858</v>
+        <v>2.715813561044353</v>
       </c>
       <c r="U87">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V87">
-        <v>0.1414897032858089</v>
+        <v>0.2054088193435603</v>
       </c>
       <c r="W87">
-        <v>0.190363168563353</v>
+        <v>0.121363168563353</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.5659588131432356</v>
+        <v>0.8216352773742414</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8464,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1927237573570114</v>
+        <v>0.1319976558414907</v>
       </c>
       <c r="C88">
-        <v>-1092.351500047713</v>
+        <v>-501.3267240101586</v>
       </c>
       <c r="D88">
-        <v>2139.026620974693</v>
+        <v>2730.051397012247</v>
       </c>
       <c r="E88">
         <v>582.9803058800735</v>
@@ -8497,45 +8497,45 @@
         <v>473.4</v>
       </c>
       <c r="M88">
-        <v>846.297293445426</v>
+        <v>582.9465030948801</v>
       </c>
       <c r="N88">
-        <v>-372.897293445426</v>
+        <v>-109.5465030948801</v>
       </c>
       <c r="O88">
-        <v>-93.22432336135651</v>
+        <v>-27.38662577372003</v>
       </c>
       <c r="P88">
-        <v>-279.6729700840696</v>
+        <v>-82.15987732116008</v>
       </c>
       <c r="Q88">
-        <v>514.9270299159305</v>
+        <v>712.44012267884</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2049835565109718</v>
+        <v>0.1950828314001091</v>
       </c>
       <c r="T88">
-        <v>3.101334773969847</v>
+        <v>2.909800243976093</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V88">
-        <v>0.1398444741778344</v>
+        <v>0.2030203447000306</v>
       </c>
       <c r="W88">
-        <v>0.19072797609939</v>
+        <v>0.12172797609939</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5593778967113374</v>
+        <v>0.8120813788001223</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1944831235236368</v>
+        <v>0.133067022008116</v>
       </c>
       <c r="C89">
-        <v>-1150.066364983135</v>
+        <v>-558.9281881985462</v>
       </c>
       <c r="D89">
-        <v>2125.691734190694</v>
+        <v>2716.829910975282</v>
       </c>
       <c r="E89">
         <v>627.360284031497</v>
@@ -8579,45 +8579,45 @@
         <v>473.4</v>
       </c>
       <c r="M89">
-        <v>856.1379596482799</v>
+        <v>589.7249508052856</v>
       </c>
       <c r="N89">
-        <v>-382.7379596482799</v>
+        <v>-116.3249508052857</v>
       </c>
       <c r="O89">
-        <v>-95.68448991206998</v>
+        <v>-29.08123770132141</v>
       </c>
       <c r="P89">
-        <v>-287.0534697362099</v>
+        <v>-87.24371310396424</v>
       </c>
       <c r="Q89">
-        <v>507.5465302637901</v>
+        <v>707.3562868960357</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2172284454733543</v>
+        <v>0.2065661261231944</v>
       </c>
       <c r="T89">
-        <v>3.339898987352143</v>
+        <v>3.133631031974255</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V89">
-        <v>0.1382370664286638</v>
+        <v>0.2006867775195705</v>
       </c>
       <c r="W89">
-        <v>0.1910843972552882</v>
+        <v>0.1220843972552882</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5529482657146554</v>
+        <v>0.8027471100782819</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1962424896902621</v>
+        <v>0.1828111342232197</v>
       </c>
       <c r="C90">
-        <v>-1207.615998190615</v>
+        <v>-1102.826485258935</v>
       </c>
       <c r="D90">
-        <v>2112.522079134638</v>
+        <v>2217.311592066317</v>
       </c>
       <c r="E90">
         <v>671.7402621829206</v>
@@ -8661,37 +8661,37 @@
         <v>473.4</v>
       </c>
       <c r="M90">
-        <v>865.9786258511338</v>
+        <v>807.3970546912549</v>
       </c>
       <c r="N90">
-        <v>-392.5786258511338</v>
+        <v>-333.9970546912549</v>
       </c>
       <c r="O90">
-        <v>-98.14465646278344</v>
+        <v>-83.49926367281373</v>
       </c>
       <c r="P90">
-        <v>-294.4339693883503</v>
+        <v>-250.4977910184412</v>
       </c>
       <c r="Q90">
-        <v>500.1660306116497</v>
+        <v>544.1022089815589</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2315141492628005</v>
+        <v>0.2295861870374467</v>
       </c>
       <c r="T90">
-        <v>3.618223902964822</v>
+        <v>3.582334866409878</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.1366661906737927</v>
+        <v>0.1465821547308672</v>
       </c>
       <c r="W90">
-        <v>0.1914327179303705</v>
+        <v>0.1764327179303705</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5466647626951706</v>
+        <v>0.5863286189234689</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8710,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1980018558568875</v>
+        <v>0.184420500389845</v>
       </c>
       <c r="C91">
-        <v>-1265.003451824263</v>
+        <v>-1160.317987099972</v>
       </c>
       <c r="D91">
-        <v>2099.514603652412</v>
+        <v>2204.200068376703</v>
       </c>
       <c r="E91">
         <v>716.1202403343436</v>
@@ -8743,37 +8743,37 @@
         <v>473.4</v>
       </c>
       <c r="M91">
-        <v>875.8192920539875</v>
+        <v>816.5720212218373</v>
       </c>
       <c r="N91">
-        <v>-402.4192920539875</v>
+        <v>-343.1720212218373</v>
       </c>
       <c r="O91">
-        <v>-100.6048230134969</v>
+        <v>-85.79300530545933</v>
       </c>
       <c r="P91">
-        <v>-301.8144690404906</v>
+        <v>-257.379015916378</v>
       </c>
       <c r="Q91">
-        <v>492.7855309595094</v>
+        <v>537.2209840836221</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2483972537412369</v>
+        <v>0.2462940222226691</v>
       </c>
       <c r="T91">
-        <v>3.947153348688897</v>
+        <v>3.90800167244714</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.1351306154976826</v>
+        <v>0.1449351642282732</v>
       </c>
       <c r="W91">
-        <v>0.1917732111745522</v>
+        <v>0.1767732111745521</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5405224619907305</v>
+        <v>0.579740656913093</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1997612220235128</v>
+        <v>0.1860298665564704</v>
       </c>
       <c r="C92">
-        <v>-1322.231703325857</v>
+        <v>-1217.655336975628</v>
       </c>
       <c r="D92">
-        <v>2086.666330302241</v>
+        <v>2191.242696652471</v>
       </c>
       <c r="E92">
         <v>760.5002184857672</v>
@@ -8825,37 +8825,37 @@
         <v>473.4</v>
       </c>
       <c r="M92">
-        <v>885.6599582568413</v>
+        <v>825.7469877524197</v>
       </c>
       <c r="N92">
-        <v>-412.2599582568413</v>
+        <v>-352.3469877524197</v>
       </c>
       <c r="O92">
-        <v>-103.0649895642103</v>
+        <v>-88.08674693810494</v>
       </c>
       <c r="P92">
-        <v>-309.1949686926309</v>
+        <v>-264.2602408143148</v>
       </c>
       <c r="Q92">
-        <v>485.4050313073691</v>
+        <v>530.3397591856852</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2686569791153606</v>
+        <v>0.266343424444936</v>
       </c>
       <c r="T92">
-        <v>4.341868683557788</v>
+        <v>4.298801839691854</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.133629164214375</v>
+        <v>0.1433247735146257</v>
       </c>
       <c r="W92">
-        <v>0.1921061379021964</v>
+        <v>0.1771061379021964</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5345166568575002</v>
+        <v>0.573299094058503</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2015205881901382</v>
+        <v>0.1876392327230957</v>
       </c>
       <c r="C93">
-        <v>-1379.303657696993</v>
+        <v>-1274.841237541493</v>
       </c>
       <c r="D93">
-        <v>2073.97435408253</v>
+        <v>2178.436774238029</v>
       </c>
       <c r="E93">
         <v>804.8801966371902</v>
@@ -8907,37 +8907,37 @@
         <v>473.4</v>
       </c>
       <c r="M93">
-        <v>895.500624459695</v>
+        <v>834.9219542830022</v>
       </c>
       <c r="N93">
-        <v>-422.100624459695</v>
+        <v>-361.5219542830022</v>
       </c>
       <c r="O93">
-        <v>-105.5251561149238</v>
+        <v>-90.38048857075054</v>
       </c>
       <c r="P93">
-        <v>-316.5754683447713</v>
+        <v>-271.1414657122516</v>
       </c>
       <c r="Q93">
-        <v>478.0245316552288</v>
+        <v>523.4585342877484</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.293418865683734</v>
+        <v>0.2908482493832623</v>
       </c>
       <c r="T93">
-        <v>4.824298537286431</v>
+        <v>4.776446488546505</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.1321607118603709</v>
+        <v>0.141749776003476</v>
       </c>
       <c r="W93">
-        <v>0.1924317475589034</v>
+        <v>0.1774317475589034</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5286428474414837</v>
+        <v>0.5669991040139041</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2032799543567635</v>
+        <v>0.189248598889721</v>
       </c>
       <c r="C94">
-        <v>-1436.222149688828</v>
+        <v>-1331.878328641481</v>
       </c>
       <c r="D94">
-        <v>2061.435840242118</v>
+        <v>2165.779661289464</v>
       </c>
       <c r="E94">
         <v>849.2601747886138</v>
@@ -8989,37 +8989,37 @@
         <v>473.4</v>
       </c>
       <c r="M94">
-        <v>905.3412906625489</v>
+        <v>844.0969208135847</v>
       </c>
       <c r="N94">
-        <v>-431.9412906625489</v>
+        <v>-370.6969208135847</v>
       </c>
       <c r="O94">
-        <v>-107.9853226656372</v>
+        <v>-92.67423020339618</v>
       </c>
       <c r="P94">
-        <v>-323.9559679969117</v>
+        <v>-278.0226906101885</v>
       </c>
       <c r="Q94">
-        <v>470.6440320030883</v>
+        <v>516.5773093898115</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3243712238942008</v>
+        <v>0.3214792805561701</v>
       </c>
       <c r="T94">
-        <v>5.427335854447236</v>
+        <v>5.373502299614819</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.1307241823836278</v>
+        <v>0.1402090175686556</v>
       </c>
       <c r="W94">
-        <v>0.1927502787448124</v>
+        <v>0.1777502787448124</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5228967295345111</v>
+        <v>0.5608360702746225</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9038,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2050393205233889</v>
+        <v>0.1908579650563464</v>
       </c>
       <c r="C95">
-        <v>-1492.989945912865</v>
+        <v>-1388.769189122026</v>
       </c>
       <c r="D95">
-        <v>2049.048022169504</v>
+        <v>2153.268778960344</v>
       </c>
       <c r="E95">
         <v>893.6401529400373</v>
@@ -9071,37 +9071,37 @@
         <v>473.4</v>
       </c>
       <c r="M95">
-        <v>915.1819568654028</v>
+        <v>853.2718873441671</v>
       </c>
       <c r="N95">
-        <v>-441.7819568654028</v>
+        <v>-379.8718873441671</v>
       </c>
       <c r="O95">
-        <v>-110.4454892163507</v>
+        <v>-94.96797183604178</v>
       </c>
       <c r="P95">
-        <v>-331.3364676490521</v>
+        <v>-284.9039155081254</v>
       </c>
       <c r="Q95">
-        <v>463.2635323509479</v>
+        <v>509.6960844918747</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3641671130219438</v>
+        <v>0.3608620349213373</v>
       </c>
       <c r="T95">
-        <v>6.202669547939699</v>
+        <v>6.14114548527408</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.1293185460139113</v>
+        <v>0.1387013937238314</v>
       </c>
       <c r="W95">
-        <v>0.1930619597976912</v>
+        <v>0.1780619597976912</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5172741840556453</v>
+        <v>0.5548055748953253</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2067986866900142</v>
+        <v>0.1924673312229717</v>
       </c>
       <c r="C96">
-        <v>-1549.609746876085</v>
+        <v>-1445.51633858375</v>
       </c>
       <c r="D96">
-        <v>2036.808199357708</v>
+        <v>2140.901607650042</v>
       </c>
       <c r="E96">
         <v>938.0201310914608</v>
@@ -9153,37 +9153,37 @@
         <v>473.4</v>
       </c>
       <c r="M96">
-        <v>925.0226230682565</v>
+        <v>862.4468538747496</v>
       </c>
       <c r="N96">
-        <v>-451.6226230682565</v>
+        <v>-389.0468538747497</v>
       </c>
       <c r="O96">
-        <v>-112.9056557670641</v>
+        <v>-97.26171346868742</v>
       </c>
       <c r="P96">
-        <v>-338.7169673011924</v>
+        <v>-291.7851404060623</v>
       </c>
       <c r="Q96">
-        <v>455.8830326988076</v>
+        <v>502.8148595939377</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4172282985256012</v>
+        <v>0.4133723740748937</v>
       </c>
       <c r="T96">
-        <v>7.236447805929651</v>
+        <v>7.164669732819763</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.1279428168009974</v>
+        <v>0.1372258469820885</v>
       </c>
       <c r="W96">
-        <v>0.1933670093388065</v>
+        <v>0.1783670093388065</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5117712672039896</v>
+        <v>0.5489033879283538</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9202,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2085580528566395</v>
+        <v>0.1940766973895971</v>
       </c>
       <c r="C97">
-        <v>-1606.084188943574</v>
+        <v>-1502.122239073135</v>
       </c>
       <c r="D97">
-        <v>2024.713735441641</v>
+        <v>2128.67568531208</v>
       </c>
       <c r="E97">
         <v>982.4001092428834</v>
@@ -9235,37 +9235,37 @@
         <v>473.4</v>
       </c>
       <c r="M97">
-        <v>934.8632892711101</v>
+        <v>871.621820405332</v>
       </c>
       <c r="N97">
-        <v>-461.4632892711102</v>
+        <v>-398.221820405332</v>
       </c>
       <c r="O97">
-        <v>-115.3658223177775</v>
+        <v>-99.555455101333</v>
       </c>
       <c r="P97">
-        <v>-346.0974669533326</v>
+        <v>-298.666365303999</v>
       </c>
       <c r="Q97">
-        <v>448.5025330466674</v>
+        <v>495.933634696001</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.4915139582307217</v>
+        <v>0.4868868488898726</v>
       </c>
       <c r="T97">
-        <v>8.683737367115585</v>
+        <v>8.597603679383719</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.1265960503083553</v>
+        <v>0.135781364382277</v>
       </c>
       <c r="W97">
-        <v>0.1936656367843194</v>
+        <v>0.1786656367843194</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5063842012334212</v>
+        <v>0.543125457529108</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9284,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2103174190232649</v>
+        <v>0.1956860635562224</v>
       </c>
       <c r="C98">
-        <v>-1662.415846231642</v>
+        <v>-1558.589296716538</v>
       </c>
       <c r="D98">
-        <v>2012.762056304997</v>
+        <v>2116.5886058201</v>
       </c>
       <c r="E98">
         <v>1026.780087394307</v>
@@ -9317,37 +9317,37 @@
         <v>473.4</v>
       </c>
       <c r="M98">
-        <v>944.703955473964</v>
+        <v>880.7967869359144</v>
       </c>
       <c r="N98">
-        <v>-471.303955473964</v>
+        <v>-407.3967869359144</v>
       </c>
       <c r="O98">
-        <v>-117.825988868491</v>
+        <v>-101.8491967339786</v>
       </c>
       <c r="P98">
-        <v>-353.4779666054731</v>
+        <v>-305.5475902019358</v>
       </c>
       <c r="Q98">
-        <v>441.122033394527</v>
+        <v>489.0524097980642</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6029424477884008</v>
+        <v>0.5971585611123394</v>
       </c>
       <c r="T98">
-        <v>10.85467170889446</v>
+        <v>10.74700459922962</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.1252773414509766</v>
+        <v>0.1343669751699616</v>
       </c>
       <c r="W98">
-        <v>0.1939580428247175</v>
+        <v>0.1789580428247175</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5011093658039064</v>
+        <v>0.5374679006798465</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9366,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2415398579024877</v>
+        <v>0.1972954297228477</v>
       </c>
       <c r="C99">
-        <v>-1897.650251598161</v>
+        <v>-1614.91986329886</v>
       </c>
       <c r="D99">
-        <v>1821.907629089901</v>
+        <v>2104.638017389202</v>
       </c>
       <c r="E99">
         <v>1071.160065545731</v>
@@ -9399,45 +9399,45 @@
         <v>473.4</v>
       </c>
       <c r="M99">
-        <v>1083.69035809746</v>
+        <v>889.9717534664969</v>
       </c>
       <c r="N99">
-        <v>-610.2903580974597</v>
+        <v>-416.5717534664969</v>
       </c>
       <c r="O99">
-        <v>-152.5725895243649</v>
+        <v>-104.1429383666242</v>
       </c>
       <c r="P99">
-        <v>-457.7177685730948</v>
+        <v>-312.4288150998727</v>
       </c>
       <c r="Q99">
-        <v>336.8822314269053</v>
+        <v>482.1711849001273</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8007590208044527</v>
+        <v>0.780944748149786</v>
       </c>
       <c r="T99">
-        <v>14.70868420999058</v>
+        <v>14.3293394656395</v>
       </c>
       <c r="U99">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.1092101624007957</v>
+        <v>0.1329817486218177</v>
       </c>
       <c r="W99">
-        <v>0.2242444198745919</v>
+        <v>0.1792444198745919</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.4368406496031827</v>
+        <v>0.5319269944872707</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9448,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2435992240691131</v>
+        <v>0.1989047958894731</v>
       </c>
       <c r="C100">
-        <v>-1953.354107438973</v>
+        <v>-1671.116237789037</v>
       </c>
       <c r="D100">
-        <v>1810.583751400512</v>
+        <v>2092.821621050448</v>
       </c>
       <c r="E100">
         <v>1115.540043697153</v>
@@ -9481,45 +9481,45 @@
         <v>473.4</v>
       </c>
       <c r="M100">
-        <v>1094.862423644856</v>
+        <v>899.1467199970791</v>
       </c>
       <c r="N100">
-        <v>-621.4624236448561</v>
+        <v>-425.7467199970791</v>
       </c>
       <c r="O100">
-        <v>-155.365605911214</v>
+        <v>-106.4366799992698</v>
       </c>
       <c r="P100">
-        <v>-466.0968177336421</v>
+        <v>-319.3100399978093</v>
       </c>
       <c r="Q100">
-        <v>328.503182266358</v>
+        <v>475.2899600021907</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.178238531206679</v>
+        <v>1.148517122224679</v>
       </c>
       <c r="T100">
-        <v>22.06302631498588</v>
+        <v>21.49400919845925</v>
       </c>
       <c r="U100">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.1080957729885427</v>
+        <v>0.1316247920032277</v>
       </c>
       <c r="W100">
-        <v>0.224524952494877</v>
+        <v>0.179524952494877</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.4323830919541707</v>
+        <v>0.526499168012911</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9530,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2456585902357384</v>
+        <v>0.2005141620560984</v>
       </c>
       <c r="C101">
-        <v>-2008.918068012385</v>
+        <v>-1727.180667814425</v>
       </c>
       <c r="D101">
-        <v>1799.399768978523</v>
+        <v>2081.137169176484</v>
       </c>
       <c r="E101">
         <v>1159.920021848577</v>
@@ -9563,45 +9563,45 @@
         <v>473.4</v>
       </c>
       <c r="M101">
-        <v>1106.034489192253</v>
+        <v>908.3216865276617</v>
       </c>
       <c r="N101">
-        <v>-632.6344891922525</v>
+        <v>-434.9216865276617</v>
       </c>
       <c r="O101">
-        <v>-158.1586222980631</v>
+        <v>-108.7304216319154</v>
       </c>
       <c r="P101">
-        <v>-474.4758668941894</v>
+        <v>-326.1912648957463</v>
       </c>
       <c r="Q101">
-        <v>320.1241331058106</v>
+        <v>468.4087351042538</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.310677062413358</v>
+        <v>2.251234244449358</v>
       </c>
       <c r="T101">
-        <v>44.12605262997175</v>
+        <v>42.9880183969185</v>
       </c>
       <c r="U101">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.1070038964937089</v>
+        <v>0.1302952486496598</v>
       </c>
       <c r="W101">
-        <v>0.2247998177894998</v>
+        <v>0.1797998177894998</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.4280155859748357</v>
+        <v>0.5211809945986391</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_transportation_railroads.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07112049067688266</v>
+        <v>0.07102096407515947</v>
       </c>
       <c r="C2">
-        <v>4361.524691136642</v>
+        <v>4319.511981692611</v>
       </c>
       <c r="D2">
-        <v>3776.224691136642</v>
+        <v>3778.591959844035</v>
       </c>
       <c r="E2">
-        <v>-3233.697815142332</v>
+        <v>-3189.317836990908</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>44.37997815142332</v>
       </c>
       <c r="G2">
         <v>585.3</v>
@@ -1445,28 +1445,28 @@
         <v>473.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.495779818793232</v>
       </c>
       <c r="N2">
-        <v>473.4</v>
+        <v>470.9042201812068</v>
       </c>
       <c r="O2">
-        <v>118.35</v>
+        <v>117.7260550453017</v>
       </c>
       <c r="P2">
-        <v>355.05</v>
+        <v>353.1781651359051</v>
       </c>
       <c r="Q2">
-        <v>1149.65</v>
+        <v>1147.778165135905</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07112049067688266</v>
+        <v>0.07131231257594996</v>
       </c>
       <c r="T2">
-        <v>0.4935434922969562</v>
+        <v>0.4972824581476907</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>189.6801939158639</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07102096407515947</v>
+        <v>0.07092143747343627</v>
       </c>
       <c r="C3">
-        <v>4319.511981692611</v>
+        <v>4277.502242133505</v>
       </c>
       <c r="D3">
-        <v>3778.591959844035</v>
+        <v>3780.962198436352</v>
       </c>
       <c r="E3">
-        <v>-3189.317836990908</v>
+        <v>-3144.937858839485</v>
       </c>
       <c r="F3">
-        <v>44.37997815142332</v>
+        <v>88.75995630284665</v>
       </c>
       <c r="G3">
         <v>585.3</v>
@@ -1527,28 +1527,28 @@
         <v>473.4</v>
       </c>
       <c r="M3">
-        <v>2.495779818793232</v>
+        <v>4.991559637586464</v>
       </c>
       <c r="N3">
-        <v>470.9042201812068</v>
+        <v>468.4084403624135</v>
       </c>
       <c r="O3">
-        <v>117.7260550453017</v>
+        <v>117.1021100906034</v>
       </c>
       <c r="P3">
-        <v>353.1781651359051</v>
+        <v>351.3063302718101</v>
       </c>
       <c r="Q3">
-        <v>1147.778165135905</v>
+        <v>1145.90633027181</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07131231257594996</v>
+        <v>0.07150804920765128</v>
       </c>
       <c r="T3">
-        <v>0.4972824581476907</v>
+        <v>0.5010977294239504</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>189.6801939158639</v>
+        <v>94.84009695793196</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07092143747343627</v>
+        <v>0.07082191087171306</v>
       </c>
       <c r="C4">
-        <v>4277.502242133505</v>
+        <v>4235.495478051688</v>
       </c>
       <c r="D4">
-        <v>3780.962198436352</v>
+        <v>3783.335412505958</v>
       </c>
       <c r="E4">
-        <v>-3144.937858839485</v>
+        <v>-3100.557880688062</v>
       </c>
       <c r="F4">
-        <v>88.75995630284665</v>
+        <v>133.13993445427</v>
       </c>
       <c r="G4">
         <v>585.3</v>
@@ -1609,28 +1609,28 @@
         <v>473.4</v>
       </c>
       <c r="M4">
-        <v>4.991559637586464</v>
+        <v>7.487339456379696</v>
       </c>
       <c r="N4">
-        <v>468.4084403624135</v>
+        <v>465.9126605436203</v>
       </c>
       <c r="O4">
-        <v>117.1021100906034</v>
+        <v>116.4781651359051</v>
       </c>
       <c r="P4">
-        <v>351.3063302718101</v>
+        <v>349.4344954077152</v>
       </c>
       <c r="Q4">
-        <v>1145.90633027181</v>
+        <v>1144.034495407715</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07150804920765128</v>
+        <v>0.0717078216461918</v>
       </c>
       <c r="T4">
-        <v>0.5010977294239504</v>
+        <v>0.5049916660873495</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>94.84009695793196</v>
+        <v>63.22673130528798</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07082191087171306</v>
+        <v>0.07072238426998986</v>
       </c>
       <c r="C5">
-        <v>4235.495478051688</v>
+        <v>4193.491695053573</v>
       </c>
       <c r="D5">
-        <v>3783.335412505958</v>
+        <v>3785.711607659267</v>
       </c>
       <c r="E5">
-        <v>-3100.557880688062</v>
+        <v>-3056.177902536639</v>
       </c>
       <c r="F5">
-        <v>133.13993445427</v>
+        <v>177.5199126056933</v>
       </c>
       <c r="G5">
         <v>585.3</v>
@@ -1691,28 +1691,28 @@
         <v>473.4</v>
       </c>
       <c r="M5">
-        <v>7.487339456379696</v>
+        <v>9.983119275172928</v>
       </c>
       <c r="N5">
-        <v>465.9126605436203</v>
+        <v>463.416880724827</v>
       </c>
       <c r="O5">
-        <v>116.4781651359051</v>
+        <v>115.8542201812068</v>
       </c>
       <c r="P5">
-        <v>349.4344954077152</v>
+        <v>347.5626605436203</v>
       </c>
       <c r="Q5">
-        <v>1144.034495407715</v>
+        <v>1142.16266054362</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0717078216461918</v>
+        <v>0.07191175601053525</v>
       </c>
       <c r="T5">
-        <v>0.5049916660873495</v>
+        <v>0.5089667264312361</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.22673130528798</v>
+        <v>47.42004847896598</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07072238426998986</v>
+        <v>0.07062285766826666</v>
       </c>
       <c r="C6">
-        <v>4193.491695053573</v>
+        <v>4151.490898759669</v>
       </c>
       <c r="D6">
-        <v>3785.711607659267</v>
+        <v>3788.090789516786</v>
       </c>
       <c r="E6">
-        <v>-3056.177902536639</v>
+        <v>-3011.797924385215</v>
       </c>
       <c r="F6">
-        <v>177.5199126056933</v>
+        <v>221.8998907571166</v>
       </c>
       <c r="G6">
         <v>585.3</v>
@@ -1773,28 +1773,28 @@
         <v>473.4</v>
       </c>
       <c r="M6">
-        <v>9.983119275172928</v>
+        <v>12.47889909396616</v>
       </c>
       <c r="N6">
-        <v>463.416880724827</v>
+        <v>460.9211009060338</v>
       </c>
       <c r="O6">
-        <v>115.8542201812068</v>
+        <v>115.2302752265085</v>
       </c>
       <c r="P6">
-        <v>347.5626605436203</v>
+        <v>345.6908256795253</v>
       </c>
       <c r="Q6">
-        <v>1142.16266054362</v>
+        <v>1140.290825679525</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07191175601053525</v>
+        <v>0.0721199837299175</v>
       </c>
       <c r="T6">
-        <v>0.5089667264312361</v>
+        <v>0.5130254722560466</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.42004847896598</v>
+        <v>37.93603878317278</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07062285766826666</v>
+        <v>0.07052333106654345</v>
       </c>
       <c r="C7">
-        <v>4151.490898759669</v>
+        <v>4109.493094804621</v>
       </c>
       <c r="D7">
-        <v>3788.090789516786</v>
+        <v>3790.472963713161</v>
       </c>
       <c r="E7">
-        <v>-3011.797924385215</v>
+        <v>-2967.417946233792</v>
       </c>
       <c r="F7">
-        <v>221.8998907571166</v>
+        <v>266.2798689085399</v>
       </c>
       <c r="G7">
         <v>585.3</v>
@@ -1855,28 +1855,28 @@
         <v>473.4</v>
       </c>
       <c r="M7">
-        <v>12.47889909396616</v>
+        <v>14.97467891275939</v>
       </c>
       <c r="N7">
-        <v>460.9211009060338</v>
+        <v>458.4253210872406</v>
       </c>
       <c r="O7">
-        <v>115.2302752265085</v>
+        <v>114.6063302718102</v>
       </c>
       <c r="P7">
-        <v>345.6908256795253</v>
+        <v>343.8189908154304</v>
       </c>
       <c r="Q7">
-        <v>1140.290825679525</v>
+        <v>1138.41899081543</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0721199837299175</v>
+        <v>0.07233264182630789</v>
       </c>
       <c r="T7">
-        <v>0.5130254722560466</v>
+        <v>0.5171705743750019</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.93603878317278</v>
+        <v>31.61336565264399</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07052333106654343</v>
+        <v>0.07042380446482024</v>
       </c>
       <c r="C8">
-        <v>4109.493094804621</v>
+        <v>4067.498288837257</v>
       </c>
       <c r="D8">
-        <v>3790.472963713162</v>
+        <v>3792.858135897221</v>
       </c>
       <c r="E8">
-        <v>-2967.417946233792</v>
+        <v>-2923.037968082368</v>
       </c>
       <c r="F8">
-        <v>266.2798689085399</v>
+        <v>310.6598470599632</v>
       </c>
       <c r="G8">
         <v>585.3</v>
@@ -1937,28 +1937,28 @@
         <v>473.4</v>
       </c>
       <c r="M8">
-        <v>14.97467891275939</v>
+        <v>17.47045873155262</v>
       </c>
       <c r="N8">
-        <v>458.4253210872406</v>
+        <v>455.9295412684473</v>
       </c>
       <c r="O8">
-        <v>114.6063302718102</v>
+        <v>113.9823853171118</v>
       </c>
       <c r="P8">
-        <v>343.8189908154304</v>
+        <v>341.9471559513355</v>
       </c>
       <c r="Q8">
-        <v>1138.41899081543</v>
+        <v>1136.547155951336</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07233264182630789</v>
+        <v>0.07254987321509378</v>
       </c>
       <c r="T8">
-        <v>0.5171705743750019</v>
+        <v>0.5214048184750101</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.61336565264399</v>
+        <v>27.09717055940914</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07042380446482024</v>
+        <v>0.07032427786309704</v>
       </c>
       <c r="C9">
-        <v>4067.498288837257</v>
+        <v>4025.506486520632</v>
       </c>
       <c r="D9">
-        <v>3792.858135897221</v>
+        <v>3795.246311732019</v>
       </c>
       <c r="E9">
-        <v>-2923.037968082368</v>
+        <v>-2878.657989930945</v>
       </c>
       <c r="F9">
-        <v>310.6598470599633</v>
+        <v>355.0398252113866</v>
       </c>
       <c r="G9">
         <v>585.3</v>
@@ -2019,28 +2019,28 @@
         <v>473.4</v>
       </c>
       <c r="M9">
-        <v>17.47045873155263</v>
+        <v>19.96623855034586</v>
       </c>
       <c r="N9">
-        <v>455.9295412684473</v>
+        <v>453.4337614496541</v>
       </c>
       <c r="O9">
-        <v>113.9823853171118</v>
+        <v>113.3584403624135</v>
       </c>
       <c r="P9">
-        <v>341.9471559513355</v>
+        <v>340.0753210872406</v>
       </c>
       <c r="Q9">
-        <v>1136.547155951336</v>
+        <v>1134.675321087241</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07254987321509378</v>
+        <v>0.072771827025375</v>
       </c>
       <c r="T9">
-        <v>0.5214048184750101</v>
+        <v>0.5257311113598011</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.09717055940913</v>
+        <v>23.71002423948299</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07032427786309704</v>
+        <v>0.07022475126137384</v>
       </c>
       <c r="C10">
-        <v>4025.506486520632</v>
+        <v>3983.517693532073</v>
       </c>
       <c r="D10">
-        <v>3795.246311732019</v>
+        <v>3797.637496894883</v>
       </c>
       <c r="E10">
-        <v>-2878.657989930945</v>
+        <v>-2834.278011779522</v>
       </c>
       <c r="F10">
-        <v>355.0398252113866</v>
+        <v>399.4198033628099</v>
       </c>
       <c r="G10">
         <v>585.3</v>
@@ -2101,28 +2101,28 @@
         <v>473.4</v>
       </c>
       <c r="M10">
-        <v>19.96623855034586</v>
+        <v>22.46201836913909</v>
       </c>
       <c r="N10">
-        <v>453.4337614496541</v>
+        <v>450.9379816308609</v>
       </c>
       <c r="O10">
-        <v>113.3584403624135</v>
+        <v>112.7344954077152</v>
       </c>
       <c r="P10">
-        <v>340.0753210872406</v>
+        <v>338.2034862231457</v>
       </c>
       <c r="Q10">
-        <v>1134.675321087241</v>
+        <v>1132.803486223146</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.072771827025375</v>
+        <v>0.07299865894137669</v>
       </c>
       <c r="T10">
-        <v>0.5257311113598011</v>
+        <v>0.5301524876046974</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.71002423948299</v>
+        <v>21.07557710176266</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07022475126137384</v>
+        <v>0.07012522465965064</v>
       </c>
       <c r="C11">
-        <v>3983.517693532073</v>
+        <v>3941.531915563226</v>
       </c>
       <c r="D11">
-        <v>3797.637496894883</v>
+        <v>3800.031697077458</v>
       </c>
       <c r="E11">
-        <v>-2834.278011779522</v>
+        <v>-2789.898033628099</v>
       </c>
       <c r="F11">
-        <v>399.4198033628099</v>
+        <v>443.7997815142332</v>
       </c>
       <c r="G11">
         <v>585.3</v>
@@ -2183,28 +2183,28 @@
         <v>473.4</v>
       </c>
       <c r="M11">
-        <v>22.46201836913909</v>
+        <v>24.95779818793232</v>
       </c>
       <c r="N11">
-        <v>450.9379816308609</v>
+        <v>448.4422018120677</v>
       </c>
       <c r="O11">
-        <v>112.7344954077152</v>
+        <v>112.1105504530169</v>
       </c>
       <c r="P11">
-        <v>338.2034862231457</v>
+        <v>336.3316513590507</v>
       </c>
       <c r="Q11">
-        <v>1132.803486223146</v>
+        <v>1130.931651359051</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07299865894137669</v>
+        <v>0.07323053156662288</v>
       </c>
       <c r="T11">
-        <v>0.5301524876046974</v>
+        <v>0.5346721166550358</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.07557710176266</v>
+        <v>18.96801939158639</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07012522465965064</v>
+        <v>0.07002569805792745</v>
       </c>
       <c r="C12">
-        <v>3941.531915563225</v>
+        <v>3899.549158320093</v>
       </c>
       <c r="D12">
-        <v>3800.031697077458</v>
+        <v>3802.42891798575</v>
       </c>
       <c r="E12">
-        <v>-2789.898033628098</v>
+        <v>-2745.518055476675</v>
       </c>
       <c r="F12">
-        <v>443.7997815142332</v>
+        <v>488.1797596656565</v>
       </c>
       <c r="G12">
         <v>585.3</v>
@@ -2265,28 +2265,28 @@
         <v>473.4</v>
       </c>
       <c r="M12">
-        <v>24.95779818793232</v>
+        <v>27.45357800672555</v>
       </c>
       <c r="N12">
-        <v>448.4422018120677</v>
+        <v>445.9464219932744</v>
       </c>
       <c r="O12">
-        <v>112.1105504530169</v>
+        <v>111.4866054983186</v>
       </c>
       <c r="P12">
-        <v>336.3316513590507</v>
+        <v>334.4598164949558</v>
       </c>
       <c r="Q12">
-        <v>1130.931651359051</v>
+        <v>1129.059816494956</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07323053156662288</v>
+        <v>0.07346761481266111</v>
       </c>
       <c r="T12">
-        <v>0.5346721166550358</v>
+        <v>0.5392933104031347</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.96801939158639</v>
+        <v>17.24365399235127</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07002569805792745</v>
+        <v>0.06992617145620425</v>
       </c>
       <c r="C13">
-        <v>3899.549158320093</v>
+        <v>3857.569427523094</v>
       </c>
       <c r="D13">
-        <v>3802.42891798575</v>
+        <v>3804.829165340173</v>
       </c>
       <c r="E13">
-        <v>-2745.518055476675</v>
+        <v>-2701.138077325252</v>
       </c>
       <c r="F13">
-        <v>488.1797596656565</v>
+        <v>532.5597378170798</v>
       </c>
       <c r="G13">
         <v>585.3</v>
@@ -2347,28 +2347,28 @@
         <v>473.4</v>
       </c>
       <c r="M13">
-        <v>27.45357800672555</v>
+        <v>29.94935782551878</v>
       </c>
       <c r="N13">
-        <v>445.9464219932744</v>
+        <v>443.4506421744812</v>
       </c>
       <c r="O13">
-        <v>111.4866054983186</v>
+        <v>110.8626605436203</v>
       </c>
       <c r="P13">
-        <v>334.4598164949558</v>
+        <v>332.5879816308609</v>
       </c>
       <c r="Q13">
-        <v>1129.059816494956</v>
+        <v>1127.187981630861</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07346761481266111</v>
+        <v>0.07371008631429112</v>
       </c>
       <c r="T13">
-        <v>0.5392933104031347</v>
+        <v>0.5440195312818721</v>
       </c>
       <c r="U13">
         <v>0.0562366166625341</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.24365399235127</v>
+        <v>15.80668282632199</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06992617145620425</v>
+        <v>0.06982664485448105</v>
       </c>
       <c r="C14">
-        <v>3857.569427523094</v>
+        <v>3815.592728907091</v>
       </c>
       <c r="D14">
-        <v>3804.829165340173</v>
+        <v>3807.232444875594</v>
       </c>
       <c r="E14">
-        <v>-2701.138077325252</v>
+        <v>-2656.758099173829</v>
       </c>
       <c r="F14">
-        <v>532.5597378170798</v>
+        <v>576.9397159685032</v>
       </c>
       <c r="G14">
         <v>585.3</v>
@@ -2429,28 +2429,28 @@
         <v>473.4</v>
       </c>
       <c r="M14">
-        <v>29.94935782551878</v>
+        <v>32.44513764431201</v>
       </c>
       <c r="N14">
-        <v>443.4506421744812</v>
+        <v>440.954862355688</v>
       </c>
       <c r="O14">
-        <v>110.8626605436203</v>
+        <v>110.238715588922</v>
       </c>
       <c r="P14">
-        <v>332.5879816308609</v>
+        <v>330.716146766766</v>
       </c>
       <c r="Q14">
-        <v>1127.187981630861</v>
+        <v>1125.316146766766</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07371008631429112</v>
+        <v>0.07395813187342985</v>
       </c>
       <c r="T14">
-        <v>0.5440195312818721</v>
+        <v>0.5488544009164426</v>
       </c>
       <c r="U14">
         <v>0.0562366166625341</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.80668282632199</v>
+        <v>14.59078414737415</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06982664485448105</v>
+        <v>0.06972711825275785</v>
       </c>
       <c r="C15">
-        <v>3815.592728907091</v>
+        <v>3773.61906822145</v>
       </c>
       <c r="D15">
-        <v>3807.232444875594</v>
+        <v>3809.638762341377</v>
       </c>
       <c r="E15">
-        <v>-2656.758099173829</v>
+        <v>-2612.378121022405</v>
       </c>
       <c r="F15">
-        <v>576.9397159685032</v>
+        <v>621.3196941199266</v>
       </c>
       <c r="G15">
         <v>585.3</v>
@@ -2511,28 +2511,28 @@
         <v>473.4</v>
       </c>
       <c r="M15">
-        <v>32.44513764431201</v>
+        <v>34.94091746310525</v>
       </c>
       <c r="N15">
-        <v>440.954862355688</v>
+        <v>438.4590825368947</v>
       </c>
       <c r="O15">
-        <v>110.238715588922</v>
+        <v>109.6147706342237</v>
       </c>
       <c r="P15">
-        <v>330.716146766766</v>
+        <v>328.8443119026711</v>
       </c>
       <c r="Q15">
-        <v>1125.316146766766</v>
+        <v>1123.444311902671</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07395813187342985</v>
+        <v>0.07421194593394391</v>
       </c>
       <c r="T15">
-        <v>0.5488544009164426</v>
+        <v>0.5538017093797241</v>
       </c>
       <c r="U15">
         <v>0.0562366166625341</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.59078414737415</v>
+        <v>13.54858527970456</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06972711825275785</v>
+        <v>0.06979634165103464</v>
       </c>
       <c r="C16">
-        <v>3773.61906822145</v>
+        <v>3727.565110344381</v>
       </c>
       <c r="D16">
-        <v>3809.638762341377</v>
+        <v>3807.964782615731</v>
       </c>
       <c r="E16">
-        <v>-2612.378121022405</v>
+        <v>-2567.998142870982</v>
       </c>
       <c r="F16">
-        <v>621.3196941199266</v>
+        <v>665.6996722713499</v>
       </c>
       <c r="G16">
         <v>585.3</v>
@@ -2593,45 +2593,45 @@
         <v>473.4</v>
       </c>
       <c r="M16">
-        <v>34.94091746310525</v>
+        <v>38.43524679030551</v>
       </c>
       <c r="N16">
-        <v>438.4590825368947</v>
+        <v>434.9647532096945</v>
       </c>
       <c r="O16">
-        <v>109.6147706342237</v>
+        <v>108.7411883024236</v>
       </c>
       <c r="P16">
-        <v>328.8443119026711</v>
+        <v>326.2235649072709</v>
       </c>
       <c r="Q16">
-        <v>1123.444311902671</v>
+        <v>1120.823564907271</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07421194593394391</v>
+        <v>0.07447173208999948</v>
       </c>
       <c r="T16">
-        <v>0.5538017093797241</v>
+        <v>0.558865425100965</v>
       </c>
       <c r="U16">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04217746249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.54858527970456</v>
+        <v>12.31681957404279</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06979634165103464</v>
+        <v>0.06970806504931144</v>
       </c>
       <c r="C17">
-        <v>3727.565110344381</v>
+        <v>3685.32012017972</v>
       </c>
       <c r="D17">
-        <v>3807.964782615731</v>
+        <v>3810.099770602493</v>
       </c>
       <c r="E17">
-        <v>-2567.998142870982</v>
+        <v>-2523.618164719559</v>
       </c>
       <c r="F17">
-        <v>665.6996722713498</v>
+        <v>710.0796504227732</v>
       </c>
       <c r="G17">
         <v>585.3</v>
@@ -2675,28 +2675,28 @@
         <v>473.4</v>
       </c>
       <c r="M17">
-        <v>38.4352467903055</v>
+        <v>40.99759657632587</v>
       </c>
       <c r="N17">
-        <v>434.9647532096945</v>
+        <v>432.4024034236741</v>
       </c>
       <c r="O17">
-        <v>108.7411883024236</v>
+        <v>108.1006008559185</v>
       </c>
       <c r="P17">
-        <v>326.2235649072709</v>
+        <v>324.3018025677556</v>
       </c>
       <c r="Q17">
-        <v>1120.823564907271</v>
+        <v>1118.901802567756</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07447173208999948</v>
+        <v>0.07473770363072303</v>
       </c>
       <c r="T17">
-        <v>0.558865425100965</v>
+        <v>0.5640497054822355</v>
       </c>
       <c r="U17">
         <v>0.05773661666253409</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.31681957404279</v>
+        <v>11.54701835066511</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06970806504931144</v>
+        <v>0.06961978844758825</v>
       </c>
       <c r="C18">
-        <v>3685.32012017972</v>
+        <v>3643.077525378987</v>
       </c>
       <c r="D18">
-        <v>3810.099770602493</v>
+        <v>3812.237153953183</v>
       </c>
       <c r="E18">
-        <v>-2523.618164719559</v>
+        <v>-2479.238186568135</v>
       </c>
       <c r="F18">
-        <v>710.0796504227732</v>
+        <v>754.4596285741965</v>
       </c>
       <c r="G18">
         <v>585.3</v>
@@ -2757,28 +2757,28 @@
         <v>473.4</v>
       </c>
       <c r="M18">
-        <v>40.99759657632587</v>
+        <v>43.55994636234624</v>
       </c>
       <c r="N18">
-        <v>432.4024034236741</v>
+        <v>429.8400536376537</v>
       </c>
       <c r="O18">
-        <v>108.1006008559185</v>
+        <v>107.4600134094134</v>
       </c>
       <c r="P18">
-        <v>324.3018025677556</v>
+        <v>322.3800402282403</v>
       </c>
       <c r="Q18">
-        <v>1118.901802567756</v>
+        <v>1116.98004022824</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07473770363072303</v>
+        <v>0.07501008412423513</v>
       </c>
       <c r="T18">
-        <v>0.5640497054822355</v>
+        <v>0.569358908282332</v>
       </c>
       <c r="U18">
         <v>0.05773661666253409</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.54701835066511</v>
+        <v>10.86778197709658</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06961978844758825</v>
+        <v>0.06953151184586503</v>
       </c>
       <c r="C19">
-        <v>3643.077525378987</v>
+        <v>3600.837329975687</v>
       </c>
       <c r="D19">
-        <v>3812.237153953183</v>
+        <v>3814.376936701307</v>
       </c>
       <c r="E19">
-        <v>-2479.238186568135</v>
+        <v>-2434.858208416712</v>
       </c>
       <c r="F19">
-        <v>754.4596285741965</v>
+        <v>798.8396067256199</v>
       </c>
       <c r="G19">
         <v>585.3</v>
@@ -2839,28 +2839,28 @@
         <v>473.4</v>
       </c>
       <c r="M19">
-        <v>43.55994636234624</v>
+        <v>46.12229614836661</v>
       </c>
       <c r="N19">
-        <v>429.8400536376537</v>
+        <v>427.2777038516334</v>
       </c>
       <c r="O19">
-        <v>107.4600134094134</v>
+        <v>106.8194259629083</v>
       </c>
       <c r="P19">
-        <v>322.3800402282403</v>
+        <v>320.458277888725</v>
       </c>
       <c r="Q19">
-        <v>1116.98004022824</v>
+        <v>1115.058277888725</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07501008412423513</v>
+        <v>0.07528910804441821</v>
       </c>
       <c r="T19">
-        <v>0.569358908282332</v>
+        <v>0.5747976038336501</v>
       </c>
       <c r="U19">
         <v>0.05773661666253409</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.86778197709658</v>
+        <v>10.26401631170232</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06953151184586503</v>
+        <v>0.06968548524414185</v>
       </c>
       <c r="C20">
-        <v>3600.837329975687</v>
+        <v>3552.726667560803</v>
       </c>
       <c r="D20">
-        <v>3814.376936701307</v>
+        <v>3810.646252437846</v>
       </c>
       <c r="E20">
-        <v>-2434.858208416712</v>
+        <v>-2390.478230265289</v>
       </c>
       <c r="F20">
-        <v>798.8396067256198</v>
+        <v>843.2195848770431</v>
       </c>
       <c r="G20">
         <v>585.3</v>
@@ -2921,45 +2921,45 @@
         <v>473.4</v>
       </c>
       <c r="M20">
-        <v>46.1222961483666</v>
+        <v>50.11811922867794</v>
       </c>
       <c r="N20">
-        <v>427.2777038516334</v>
+        <v>423.2818807713221</v>
       </c>
       <c r="O20">
-        <v>106.8194259629083</v>
+        <v>105.8204701928305</v>
       </c>
       <c r="P20">
-        <v>320.458277888725</v>
+        <v>317.4614105784916</v>
       </c>
       <c r="Q20">
-        <v>1115.058277888725</v>
+        <v>1112.061410578492</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07528910804441821</v>
+        <v>0.07557502144411202</v>
       </c>
       <c r="T20">
-        <v>0.5747976038336501</v>
+        <v>0.5803705881640133</v>
       </c>
       <c r="U20">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04330246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.26401631170232</v>
+        <v>9.445685657915055</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06968548524414185</v>
+        <v>0.06960995864241865</v>
       </c>
       <c r="C21">
-        <v>3552.726667560803</v>
+        <v>3510.175741928796</v>
       </c>
       <c r="D21">
-        <v>3810.646252437846</v>
+        <v>3812.475304957262</v>
       </c>
       <c r="E21">
-        <v>-2390.478230265289</v>
+        <v>-2346.098252113865</v>
       </c>
       <c r="F21">
-        <v>843.2195848770431</v>
+        <v>887.5995630284665</v>
       </c>
       <c r="G21">
         <v>585.3</v>
@@ -3003,28 +3003,28 @@
         <v>473.4</v>
       </c>
       <c r="M21">
-        <v>50.11811922867794</v>
+        <v>52.75591497755573</v>
       </c>
       <c r="N21">
-        <v>423.2818807713221</v>
+        <v>420.6440850224442</v>
       </c>
       <c r="O21">
-        <v>105.8204701928305</v>
+        <v>105.1610212556111</v>
       </c>
       <c r="P21">
-        <v>317.4614105784916</v>
+        <v>315.4830637668332</v>
       </c>
       <c r="Q21">
-        <v>1112.061410578492</v>
+        <v>1110.083063766833</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07557502144411202</v>
+        <v>0.07586808267879816</v>
       </c>
       <c r="T21">
-        <v>0.5803705881640133</v>
+        <v>0.5860828971026354</v>
       </c>
       <c r="U21">
         <v>0.05943661666253409</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.445685657915055</v>
+        <v>8.973401375019302</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06960995864241865</v>
+        <v>0.06953443204069544</v>
       </c>
       <c r="C22">
-        <v>3510.175741928796</v>
+        <v>3467.626572975014</v>
       </c>
       <c r="D22">
-        <v>3812.475304957262</v>
+        <v>3814.306114154904</v>
       </c>
       <c r="E22">
-        <v>-2346.098252113865</v>
+        <v>-2301.718273962442</v>
       </c>
       <c r="F22">
-        <v>887.5995630284665</v>
+        <v>931.9795411798898</v>
       </c>
       <c r="G22">
         <v>585.3</v>
@@ -3085,28 +3085,28 @@
         <v>473.4</v>
       </c>
       <c r="M22">
-        <v>52.75591497755573</v>
+        <v>55.39371072643352</v>
       </c>
       <c r="N22">
-        <v>420.6440850224442</v>
+        <v>418.0062892735664</v>
       </c>
       <c r="O22">
-        <v>105.1610212556111</v>
+        <v>104.5015723183916</v>
       </c>
       <c r="P22">
-        <v>315.4830637668332</v>
+        <v>313.5047169551748</v>
       </c>
       <c r="Q22">
-        <v>1110.083063766833</v>
+        <v>1108.104716955175</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07586808267879816</v>
+        <v>0.07616856318524851</v>
       </c>
       <c r="T22">
-        <v>0.5860828971026354</v>
+        <v>0.5919398214574252</v>
       </c>
       <c r="U22">
         <v>0.05943661666253409</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.973401375019302</v>
+        <v>8.546096547637429</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06953443204069544</v>
+        <v>0.06945890543897223</v>
       </c>
       <c r="C23">
-        <v>3467.626572975014</v>
+        <v>3425.079163231424</v>
       </c>
       <c r="D23">
-        <v>3814.306114154904</v>
+        <v>3816.138682562737</v>
       </c>
       <c r="E23">
-        <v>-2301.718273962442</v>
+        <v>-2257.338295811019</v>
       </c>
       <c r="F23">
-        <v>931.9795411798897</v>
+        <v>976.3595193313131</v>
       </c>
       <c r="G23">
         <v>585.3</v>
@@ -3167,28 +3167,28 @@
         <v>473.4</v>
       </c>
       <c r="M23">
-        <v>55.39371072643351</v>
+        <v>58.0315064753113</v>
       </c>
       <c r="N23">
-        <v>418.0062892735665</v>
+        <v>415.3684935246887</v>
       </c>
       <c r="O23">
-        <v>104.5015723183916</v>
+        <v>103.8421233811722</v>
       </c>
       <c r="P23">
-        <v>313.5047169551749</v>
+        <v>311.5263701435165</v>
       </c>
       <c r="Q23">
-        <v>1108.104716955175</v>
+        <v>1106.126370143516</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07616856318524851</v>
+        <v>0.07647674832006937</v>
       </c>
       <c r="T23">
-        <v>0.5919398214574252</v>
+        <v>0.5979469233597737</v>
       </c>
       <c r="U23">
         <v>0.05943661666253409</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.546096547637433</v>
+        <v>8.157637613653911</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06945890543897223</v>
+        <v>0.06938337883724904</v>
       </c>
       <c r="C24">
-        <v>3425.079163231424</v>
+        <v>3382.533515234863</v>
       </c>
       <c r="D24">
-        <v>3816.138682562737</v>
+        <v>3817.973012717599</v>
       </c>
       <c r="E24">
-        <v>-2257.338295811019</v>
+        <v>-2212.958317659595</v>
       </c>
       <c r="F24">
-        <v>976.3595193313131</v>
+        <v>1020.739497482736</v>
       </c>
       <c r="G24">
         <v>585.3</v>
@@ -3249,28 +3249,28 @@
         <v>473.4</v>
       </c>
       <c r="M24">
-        <v>58.0315064753113</v>
+        <v>60.66930222418909</v>
       </c>
       <c r="N24">
-        <v>415.3684935246887</v>
+        <v>412.7306977758109</v>
       </c>
       <c r="O24">
-        <v>103.8421233811722</v>
+        <v>103.1826744439527</v>
       </c>
       <c r="P24">
-        <v>311.5263701435165</v>
+        <v>309.5480233318582</v>
       </c>
       <c r="Q24">
-        <v>1106.126370143516</v>
+        <v>1104.148023331858</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07647674832006937</v>
+        <v>0.07679293826358689</v>
       </c>
       <c r="T24">
-        <v>0.5979469233597737</v>
+        <v>0.6041100538829626</v>
       </c>
       <c r="U24">
         <v>0.05943661666253409</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.157637613653911</v>
+        <v>7.802957717408089</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06938337883724904</v>
+        <v>0.06945185223552584</v>
       </c>
       <c r="C25">
-        <v>3382.533515234863</v>
+        <v>3336.490434916431</v>
       </c>
       <c r="D25">
-        <v>3817.973012717599</v>
+        <v>3816.309910550591</v>
       </c>
       <c r="E25">
-        <v>-2212.958317659595</v>
+        <v>-2168.578339508172</v>
       </c>
       <c r="F25">
-        <v>1020.739497482736</v>
+        <v>1065.11947563416</v>
       </c>
       <c r="G25">
         <v>585.3</v>
@@ -3331,45 +3331,45 @@
         <v>473.4</v>
       </c>
       <c r="M25">
-        <v>60.66930222418909</v>
+        <v>64.1591935535742</v>
       </c>
       <c r="N25">
-        <v>412.7306977758109</v>
+        <v>409.2408064464258</v>
       </c>
       <c r="O25">
-        <v>103.1826744439527</v>
+        <v>102.3102016116064</v>
       </c>
       <c r="P25">
-        <v>309.5480233318582</v>
+        <v>306.9306048348193</v>
       </c>
       <c r="Q25">
-        <v>1104.148023331858</v>
+        <v>1101.530604834819</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07679293826358689</v>
+        <v>0.07711744899509171</v>
       </c>
       <c r="T25">
-        <v>0.6041100538829626</v>
+        <v>0.6104353720514984</v>
       </c>
       <c r="U25">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.802957717408089</v>
+        <v>7.378521670549079</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06945185223552584</v>
+        <v>0.06938232563380263</v>
       </c>
       <c r="C26">
-        <v>3336.490434916431</v>
+        <v>3293.799150768318</v>
       </c>
       <c r="D26">
-        <v>3816.309910550591</v>
+        <v>3817.998604553901</v>
       </c>
       <c r="E26">
-        <v>-2168.578339508172</v>
+        <v>-2124.198361356749</v>
       </c>
       <c r="F26">
-        <v>1065.11947563416</v>
+        <v>1109.499453785583</v>
       </c>
       <c r="G26">
         <v>585.3</v>
@@ -3413,28 +3413,28 @@
         <v>473.4</v>
       </c>
       <c r="M26">
-        <v>64.1591935535742</v>
+        <v>66.83249328497313</v>
       </c>
       <c r="N26">
-        <v>409.2408064464258</v>
+        <v>406.5675067150269</v>
       </c>
       <c r="O26">
-        <v>102.3102016116064</v>
+        <v>101.6418766787567</v>
       </c>
       <c r="P26">
-        <v>306.9306048348193</v>
+        <v>304.9256300362701</v>
       </c>
       <c r="Q26">
-        <v>1101.530604834819</v>
+        <v>1099.52563003627</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07711744899509171</v>
+        <v>0.07745061334610331</v>
       </c>
       <c r="T26">
-        <v>0.6104353720514984</v>
+        <v>0.6169293653711951</v>
       </c>
       <c r="U26">
         <v>0.0602366166625341</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.378521670549079</v>
+        <v>7.083380803727116</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06938232563380263</v>
+        <v>0.06931279903207944</v>
       </c>
       <c r="C27">
-        <v>3293.799150768318</v>
+        <v>3251.109361755513</v>
       </c>
       <c r="D27">
-        <v>3817.998604553901</v>
+        <v>3819.688793692519</v>
       </c>
       <c r="E27">
-        <v>-2124.198361356749</v>
+        <v>-2079.818383205326</v>
       </c>
       <c r="F27">
-        <v>1109.499453785583</v>
+        <v>1153.879431937006</v>
       </c>
       <c r="G27">
         <v>585.3</v>
@@ -3495,28 +3495,28 @@
         <v>473.4</v>
       </c>
       <c r="M27">
-        <v>66.83249328497313</v>
+        <v>69.50579301637205</v>
       </c>
       <c r="N27">
-        <v>406.5675067150269</v>
+        <v>403.8942069836279</v>
       </c>
       <c r="O27">
-        <v>101.6418766787567</v>
+        <v>100.973551745907</v>
       </c>
       <c r="P27">
-        <v>304.9256300362701</v>
+        <v>302.9206552377209</v>
       </c>
       <c r="Q27">
-        <v>1099.52563003627</v>
+        <v>1097.520655237721</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07745061334610331</v>
+        <v>0.07779278213903418</v>
       </c>
       <c r="T27">
-        <v>0.6169293653711951</v>
+        <v>0.6235988720238568</v>
       </c>
       <c r="U27">
         <v>0.0602366166625341</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.083380803727116</v>
+        <v>6.810943080506841</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06931279903207944</v>
+        <v>0.06924327243035625</v>
       </c>
       <c r="C28">
-        <v>3251.109361755513</v>
+        <v>3208.421069864541</v>
       </c>
       <c r="D28">
-        <v>3819.688793692519</v>
+        <v>3821.380479952971</v>
       </c>
       <c r="E28">
-        <v>-2079.818383205326</v>
+        <v>-2035.438405053902</v>
       </c>
       <c r="F28">
-        <v>1153.879431937006</v>
+        <v>1198.25941008843</v>
       </c>
       <c r="G28">
         <v>585.3</v>
@@ -3577,28 +3577,28 @@
         <v>473.4</v>
       </c>
       <c r="M28">
-        <v>69.50579301637205</v>
+        <v>72.17909274777099</v>
       </c>
       <c r="N28">
-        <v>403.8942069836279</v>
+        <v>401.220907252229</v>
       </c>
       <c r="O28">
-        <v>100.973551745907</v>
+        <v>100.3052268130572</v>
       </c>
       <c r="P28">
-        <v>302.9206552377209</v>
+        <v>300.9156804391718</v>
       </c>
       <c r="Q28">
-        <v>1097.520655237721</v>
+        <v>1095.515680439172</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07779278213903418</v>
+        <v>0.07814432541944258</v>
       </c>
       <c r="T28">
-        <v>0.6235988720238568</v>
+        <v>0.6304511048861804</v>
       </c>
       <c r="U28">
         <v>0.0602366166625341</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.810943080506841</v>
+        <v>6.558685929376957</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06924327243035625</v>
+        <v>0.06917374582863305</v>
       </c>
       <c r="C29">
-        <v>3208.421069864541</v>
+        <v>3165.734277085445</v>
       </c>
       <c r="D29">
-        <v>3821.380479952971</v>
+        <v>3823.073665325298</v>
       </c>
       <c r="E29">
-        <v>-2035.438405053902</v>
+        <v>-1991.058426902479</v>
       </c>
       <c r="F29">
-        <v>1198.25941008843</v>
+        <v>1242.639388239853</v>
       </c>
       <c r="G29">
         <v>585.3</v>
@@ -3659,28 +3659,28 @@
         <v>473.4</v>
       </c>
       <c r="M29">
-        <v>72.17909274777099</v>
+        <v>74.85239247916991</v>
       </c>
       <c r="N29">
-        <v>401.220907252229</v>
+        <v>398.5476075208301</v>
       </c>
       <c r="O29">
-        <v>100.3052268130572</v>
+        <v>99.63690188020752</v>
       </c>
       <c r="P29">
-        <v>300.9156804391718</v>
+        <v>298.9107056406226</v>
       </c>
       <c r="Q29">
-        <v>1095.515680439172</v>
+        <v>1093.510705640623</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07814432541944258</v>
+        <v>0.07850563379097344</v>
       </c>
       <c r="T29">
-        <v>0.6304511048861804</v>
+        <v>0.6374936775502351</v>
       </c>
       <c r="U29">
         <v>0.0602366166625341</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.558685929376957</v>
+        <v>6.324447146184924</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06917374582863305</v>
+        <v>0.06910421922690983</v>
       </c>
       <c r="C30">
-        <v>3165.734277085445</v>
+        <v>3123.048985411798</v>
       </c>
       <c r="D30">
-        <v>3823.073665325298</v>
+        <v>3824.768351803075</v>
       </c>
       <c r="E30">
-        <v>-1991.058426902479</v>
+        <v>-1946.678448751055</v>
       </c>
       <c r="F30">
-        <v>1242.639388239853</v>
+        <v>1287.019366391276</v>
       </c>
       <c r="G30">
         <v>585.3</v>
@@ -3741,28 +3741,28 @@
         <v>473.4</v>
       </c>
       <c r="M30">
-        <v>74.85239247916991</v>
+        <v>77.52569221056883</v>
       </c>
       <c r="N30">
-        <v>398.5476075208301</v>
+        <v>395.8743077894312</v>
       </c>
       <c r="O30">
-        <v>99.63690188020752</v>
+        <v>98.96857694735779</v>
       </c>
       <c r="P30">
-        <v>298.9107056406226</v>
+        <v>296.9057308420734</v>
       </c>
       <c r="Q30">
-        <v>1093.510705640623</v>
+        <v>1091.505730842073</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07850563379097344</v>
+        <v>0.0788771198631108</v>
       </c>
       <c r="T30">
-        <v>0.6374936775502351</v>
+        <v>0.6447346325428547</v>
       </c>
       <c r="U30">
         <v>0.0602366166625341</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.324447146184924</v>
+        <v>6.10636276183372</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06910421922690983</v>
+        <v>0.06925969262518662</v>
       </c>
       <c r="C31">
-        <v>3123.048985411799</v>
+        <v>3074.881472356926</v>
       </c>
       <c r="D31">
-        <v>3824.768351803075</v>
+        <v>3820.980816899626</v>
       </c>
       <c r="E31">
-        <v>-1946.678448751056</v>
+        <v>-1902.298470599632</v>
       </c>
       <c r="F31">
-        <v>1287.019366391276</v>
+        <v>1331.3993445427</v>
       </c>
       <c r="G31">
         <v>585.3</v>
@@ -3823,45 +3823,45 @@
         <v>473.4</v>
       </c>
       <c r="M31">
-        <v>77.52569221056882</v>
+        <v>81.53039128651045</v>
       </c>
       <c r="N31">
-        <v>395.8743077894312</v>
+        <v>391.8696087134895</v>
       </c>
       <c r="O31">
-        <v>98.96857694735779</v>
+        <v>97.96740217837238</v>
       </c>
       <c r="P31">
-        <v>296.9057308420734</v>
+        <v>293.9022065351172</v>
       </c>
       <c r="Q31">
-        <v>1091.505730842073</v>
+        <v>1088.502206535117</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0788771198631108</v>
+        <v>0.07925921982302352</v>
       </c>
       <c r="T31">
-        <v>0.6447346325428547</v>
+        <v>0.6521824719638349</v>
       </c>
       <c r="U31">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04517746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.10636276183372</v>
+        <v>5.806423746163549</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06925969262518662</v>
+        <v>0.06919766602346342</v>
       </c>
       <c r="C32">
-        <v>3074.881472356926</v>
+        <v>3032.011643454216</v>
       </c>
       <c r="D32">
-        <v>3820.980816899626</v>
+        <v>3822.490966148339</v>
       </c>
       <c r="E32">
-        <v>-1902.298470599632</v>
+        <v>-1857.918492448209</v>
       </c>
       <c r="F32">
-        <v>1331.3993445427</v>
+        <v>1375.779322694123</v>
       </c>
       <c r="G32">
         <v>585.3</v>
@@ -3905,28 +3905,28 @@
         <v>473.4</v>
       </c>
       <c r="M32">
-        <v>81.53039128651045</v>
+        <v>84.24807099606079</v>
       </c>
       <c r="N32">
-        <v>391.8696087134895</v>
+        <v>389.1519290039392</v>
       </c>
       <c r="O32">
-        <v>97.96740217837238</v>
+        <v>97.2879822509848</v>
       </c>
       <c r="P32">
-        <v>293.9022065351172</v>
+        <v>291.8639467529544</v>
       </c>
       <c r="Q32">
-        <v>1088.502206535117</v>
+        <v>1086.463946752954</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07925921982302352</v>
+        <v>0.07965239514409311</v>
       </c>
       <c r="T32">
-        <v>0.6521824719638349</v>
+        <v>0.6598461907883217</v>
       </c>
       <c r="U32">
         <v>0.0612366166625341</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.806423746163549</v>
+        <v>5.619119754351822</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06919766602346342</v>
+        <v>0.06913563942174022</v>
       </c>
       <c r="C33">
-        <v>3032.011643454216</v>
+        <v>2989.143008722611</v>
       </c>
       <c r="D33">
-        <v>3822.490966148339</v>
+        <v>3824.002309568158</v>
       </c>
       <c r="E33">
-        <v>-1857.918492448209</v>
+        <v>-1813.538514296785</v>
       </c>
       <c r="F33">
-        <v>1375.779322694123</v>
+        <v>1420.159300845546</v>
       </c>
       <c r="G33">
         <v>585.3</v>
@@ -3987,28 +3987,28 @@
         <v>473.4</v>
       </c>
       <c r="M33">
-        <v>84.24807099606079</v>
+        <v>86.96575070561116</v>
       </c>
       <c r="N33">
-        <v>389.1519290039392</v>
+        <v>386.4342492943888</v>
       </c>
       <c r="O33">
-        <v>97.2879822509848</v>
+        <v>96.6085623235972</v>
       </c>
       <c r="P33">
-        <v>291.8639467529544</v>
+        <v>289.8256869707916</v>
       </c>
       <c r="Q33">
-        <v>1086.463946752954</v>
+        <v>1084.425686970792</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07965239514409311</v>
+        <v>0.08005713444519419</v>
       </c>
       <c r="T33">
-        <v>0.6598461907883217</v>
+        <v>0.6677353131076466</v>
       </c>
       <c r="U33">
         <v>0.0612366166625341</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.619119754351822</v>
+        <v>5.443522262028326</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06913563942174022</v>
+        <v>0.06907361282001702</v>
       </c>
       <c r="C34">
-        <v>2989.143008722611</v>
+        <v>2946.275569579132</v>
       </c>
       <c r="D34">
-        <v>3824.002309568158</v>
+        <v>3825.514848576101</v>
       </c>
       <c r="E34">
-        <v>-1813.538514296785</v>
+        <v>-1769.158536145362</v>
       </c>
       <c r="F34">
-        <v>1420.159300845546</v>
+        <v>1464.53927899697</v>
       </c>
       <c r="G34">
         <v>585.3</v>
@@ -4069,28 +4069,28 @@
         <v>473.4</v>
       </c>
       <c r="M34">
-        <v>86.96575070561116</v>
+        <v>89.68343041516151</v>
       </c>
       <c r="N34">
-        <v>386.4342492943888</v>
+        <v>383.7165695848385</v>
       </c>
       <c r="O34">
-        <v>96.6085623235972</v>
+        <v>95.92914239620961</v>
       </c>
       <c r="P34">
-        <v>289.8256869707916</v>
+        <v>287.7874271886288</v>
       </c>
       <c r="Q34">
-        <v>1084.425686970792</v>
+        <v>1082.387427188629</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08005713444519419</v>
+        <v>0.08047395551647737</v>
       </c>
       <c r="T34">
-        <v>0.6677353131076466</v>
+        <v>0.675859931615608</v>
       </c>
       <c r="U34">
         <v>0.0612366166625341</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.443522262028326</v>
+        <v>5.278567041966862</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06907361282001702</v>
+        <v>0.06901158621829383</v>
       </c>
       <c r="C35">
-        <v>2946.275569579132</v>
+        <v>2903.409327443042</v>
       </c>
       <c r="D35">
-        <v>3825.514848576101</v>
+        <v>3827.028584591435</v>
       </c>
       <c r="E35">
-        <v>-1769.158536145362</v>
+        <v>-1724.778557993939</v>
       </c>
       <c r="F35">
-        <v>1464.53927899697</v>
+        <v>1508.919257148393</v>
       </c>
       <c r="G35">
         <v>585.3</v>
@@ -4151,28 +4151,28 @@
         <v>473.4</v>
       </c>
       <c r="M35">
-        <v>89.68343041516151</v>
+        <v>92.40111012471185</v>
       </c>
       <c r="N35">
-        <v>383.7165695848385</v>
+        <v>380.9988898752881</v>
       </c>
       <c r="O35">
-        <v>95.92914239620961</v>
+        <v>95.24972246882203</v>
       </c>
       <c r="P35">
-        <v>287.7874271886288</v>
+        <v>285.7491674064661</v>
       </c>
       <c r="Q35">
-        <v>1082.387427188629</v>
+        <v>1080.349167406466</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08047395551647737</v>
+        <v>0.0809034075293146</v>
       </c>
       <c r="T35">
-        <v>0.675859931615608</v>
+        <v>0.6842307506844165</v>
       </c>
       <c r="U35">
         <v>0.0612366166625341</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.278567041966862</v>
+        <v>5.123315070144307</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06901158621829383</v>
+        <v>0.06894955961657062</v>
       </c>
       <c r="C36">
-        <v>2903.409327443042</v>
+        <v>2860.544283735851</v>
       </c>
       <c r="D36">
-        <v>3827.028584591435</v>
+        <v>3828.543519035668</v>
       </c>
       <c r="E36">
-        <v>-1724.778557993939</v>
+        <v>-1680.398579842516</v>
       </c>
       <c r="F36">
-        <v>1508.919257148393</v>
+        <v>1553.299235299816</v>
       </c>
       <c r="G36">
         <v>585.3</v>
@@ -4233,28 +4233,28 @@
         <v>473.4</v>
       </c>
       <c r="M36">
-        <v>92.40111012471185</v>
+        <v>95.1187898342622</v>
       </c>
       <c r="N36">
-        <v>380.9988898752881</v>
+        <v>378.2812101657378</v>
       </c>
       <c r="O36">
-        <v>95.24972246882203</v>
+        <v>94.57030254143444</v>
       </c>
       <c r="P36">
-        <v>285.7491674064661</v>
+        <v>283.7109076243033</v>
       </c>
       <c r="Q36">
-        <v>1080.349167406466</v>
+        <v>1078.310907624303</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0809034075293146</v>
+        <v>0.08134607345023911</v>
       </c>
       <c r="T36">
-        <v>0.6842307506844165</v>
+        <v>0.6928591334168808</v>
       </c>
       <c r="U36">
         <v>0.0612366166625341</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.123315070144307</v>
+        <v>4.976934639568755</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06894955961657062</v>
+        <v>0.06888753301484743</v>
       </c>
       <c r="C37">
-        <v>2860.544283735851</v>
+        <v>2817.680439881325</v>
       </c>
       <c r="D37">
-        <v>3828.543519035668</v>
+        <v>3830.059653332565</v>
       </c>
       <c r="E37">
-        <v>-1680.398579842516</v>
+        <v>-1636.018601691092</v>
       </c>
       <c r="F37">
-        <v>1553.299235299816</v>
+        <v>1597.67921345124</v>
       </c>
       <c r="G37">
         <v>585.3</v>
@@ -4315,28 +4315,28 @@
         <v>473.4</v>
       </c>
       <c r="M37">
-        <v>95.1187898342622</v>
+        <v>97.83646954381256</v>
       </c>
       <c r="N37">
-        <v>378.2812101657378</v>
+        <v>375.5635304561874</v>
       </c>
       <c r="O37">
-        <v>94.57030254143444</v>
+        <v>93.89088261404686</v>
       </c>
       <c r="P37">
-        <v>283.7109076243033</v>
+        <v>281.6726478421406</v>
       </c>
       <c r="Q37">
-        <v>1078.310907624303</v>
+        <v>1076.27264784214</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08134607345023911</v>
+        <v>0.08180257268119254</v>
       </c>
       <c r="T37">
-        <v>0.6928591334168808</v>
+        <v>0.7017571531097345</v>
       </c>
       <c r="U37">
         <v>0.0612366166625341</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.976934639568755</v>
+        <v>4.83868645513629</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06888753301484743</v>
+        <v>0.06882550641312422</v>
       </c>
       <c r="C38">
-        <v>2817.680439881325</v>
+        <v>2774.81779730548</v>
       </c>
       <c r="D38">
-        <v>3830.059653332565</v>
+        <v>3831.576988908143</v>
       </c>
       <c r="E38">
-        <v>-1636.018601691092</v>
+        <v>-1591.638623539669</v>
       </c>
       <c r="F38">
-        <v>1597.67921345124</v>
+        <v>1642.059191602663</v>
       </c>
       <c r="G38">
         <v>585.3</v>
@@ -4397,28 +4397,28 @@
         <v>473.4</v>
       </c>
       <c r="M38">
-        <v>97.83646954381254</v>
+        <v>100.5541492533629</v>
       </c>
       <c r="N38">
-        <v>375.5635304561874</v>
+        <v>372.8458507466371</v>
       </c>
       <c r="O38">
-        <v>93.89088261404686</v>
+        <v>93.21146268665927</v>
       </c>
       <c r="P38">
-        <v>281.6726478421406</v>
+        <v>279.6343880599778</v>
       </c>
       <c r="Q38">
-        <v>1076.27264784214</v>
+        <v>1074.234388059978</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08180257268119254</v>
+        <v>0.08227356395122383</v>
       </c>
       <c r="T38">
-        <v>0.7017571531097345</v>
+        <v>0.7109376496182345</v>
       </c>
       <c r="U38">
         <v>0.0612366166625341</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.83868645513629</v>
+        <v>4.707911145538013</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06882550641312422</v>
+        <v>0.06876347981140102</v>
       </c>
       <c r="C39">
-        <v>2774.81779730548</v>
+        <v>2731.956357436598</v>
       </c>
       <c r="D39">
-        <v>3831.576988908143</v>
+        <v>3833.095527190684</v>
       </c>
       <c r="E39">
-        <v>-1591.638623539669</v>
+        <v>-1547.258645388246</v>
       </c>
       <c r="F39">
-        <v>1642.059191602663</v>
+        <v>1686.439169754086</v>
       </c>
       <c r="G39">
         <v>585.3</v>
@@ -4479,28 +4479,28 @@
         <v>473.4</v>
       </c>
       <c r="M39">
-        <v>100.5541492533629</v>
+        <v>103.2718289629132</v>
       </c>
       <c r="N39">
-        <v>372.8458507466371</v>
+        <v>370.1281710370868</v>
       </c>
       <c r="O39">
-        <v>93.21146268665927</v>
+        <v>92.53204275927169</v>
       </c>
       <c r="P39">
-        <v>279.6343880599778</v>
+        <v>277.5961282778151</v>
       </c>
       <c r="Q39">
-        <v>1074.234388059978</v>
+        <v>1072.196128277815</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08227356395122383</v>
+        <v>0.08275974848803033</v>
       </c>
       <c r="T39">
-        <v>0.7109376496182345</v>
+        <v>0.7204142911753957</v>
       </c>
       <c r="U39">
         <v>0.0612366166625341</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.707911145538013</v>
+        <v>4.584018746971223</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06876347981140102</v>
+        <v>0.06943270320967782</v>
       </c>
       <c r="C40">
-        <v>2731.956357436598</v>
+        <v>2671.255713897268</v>
       </c>
       <c r="D40">
-        <v>3833.095527190684</v>
+        <v>3816.774861802778</v>
       </c>
       <c r="E40">
-        <v>-1547.258645388246</v>
+        <v>-1502.878667236822</v>
       </c>
       <c r="F40">
-        <v>1686.439169754086</v>
+        <v>1730.819147905509</v>
       </c>
       <c r="G40">
         <v>585.3</v>
@@ -4561,45 +4561,45 @@
         <v>473.4</v>
       </c>
       <c r="M40">
-        <v>103.2718289629132</v>
+        <v>110.3165565422274</v>
       </c>
       <c r="N40">
-        <v>370.1281710370868</v>
+        <v>363.0834434577726</v>
       </c>
       <c r="O40">
-        <v>92.53204275927169</v>
+        <v>90.77086086444315</v>
       </c>
       <c r="P40">
-        <v>277.5961282778151</v>
+        <v>272.3125825933295</v>
       </c>
       <c r="Q40">
-        <v>1072.196128277815</v>
+        <v>1066.912582593329</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08275974848803033</v>
+        <v>0.08326187350145345</v>
       </c>
       <c r="T40">
-        <v>0.7204142911753957</v>
+        <v>0.7302016422918081</v>
       </c>
       <c r="U40">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04592746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.584018746971223</v>
+        <v>4.291286954907719</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06943270320967782</v>
+        <v>0.06938942660795462</v>
       </c>
       <c r="C41">
-        <v>2671.255713897268</v>
+        <v>2627.926938258624</v>
       </c>
       <c r="D41">
-        <v>3816.774861802778</v>
+        <v>3817.826064315558</v>
       </c>
       <c r="E41">
-        <v>-1502.878667236822</v>
+        <v>-1458.498689085399</v>
       </c>
       <c r="F41">
-        <v>1730.819147905509</v>
+        <v>1775.199126056933</v>
       </c>
       <c r="G41">
         <v>585.3</v>
@@ -4643,28 +4643,28 @@
         <v>473.4</v>
       </c>
       <c r="M41">
-        <v>110.3165565422274</v>
+        <v>113.1451861971563</v>
       </c>
       <c r="N41">
-        <v>363.0834434577726</v>
+        <v>360.2548138028437</v>
       </c>
       <c r="O41">
-        <v>90.77086086444315</v>
+        <v>90.06370345071093</v>
       </c>
       <c r="P41">
-        <v>272.3125825933295</v>
+        <v>270.1911103521328</v>
       </c>
       <c r="Q41">
-        <v>1066.912582593329</v>
+        <v>1064.791110352133</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08326187350145345</v>
+        <v>0.08378073601532399</v>
       </c>
       <c r="T41">
-        <v>0.7302016422918081</v>
+        <v>0.7403152384454342</v>
       </c>
       <c r="U41">
         <v>0.06373661666253409</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.291286954907719</v>
+        <v>4.184004781035025</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06938942660795462</v>
+        <v>0.06934615000623141</v>
       </c>
       <c r="C42">
-        <v>2627.926938258624</v>
+        <v>2584.598741816391</v>
       </c>
       <c r="D42">
-        <v>3817.826064315558</v>
+        <v>3818.877846024748</v>
       </c>
       <c r="E42">
-        <v>-1458.498689085399</v>
+        <v>-1414.118710933976</v>
       </c>
       <c r="F42">
-        <v>1775.199126056933</v>
+        <v>1819.579104208356</v>
       </c>
       <c r="G42">
         <v>585.3</v>
@@ -4725,28 +4725,28 @@
         <v>473.4</v>
       </c>
       <c r="M42">
-        <v>113.1451861971563</v>
+        <v>115.9738158520852</v>
       </c>
       <c r="N42">
-        <v>360.2548138028437</v>
+        <v>357.4261841479148</v>
       </c>
       <c r="O42">
-        <v>90.06370345071093</v>
+        <v>89.3565460369787</v>
       </c>
       <c r="P42">
-        <v>270.1911103521328</v>
+        <v>268.0696381109361</v>
       </c>
       <c r="Q42">
-        <v>1064.791110352133</v>
+        <v>1062.669638110936</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08378073601532399</v>
+        <v>0.08431718708898675</v>
       </c>
       <c r="T42">
-        <v>0.7403152384454342</v>
+        <v>0.7507716683669799</v>
       </c>
       <c r="U42">
         <v>0.06373661666253409</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.184004781035025</v>
+        <v>4.08195588393661</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06934615000623141</v>
+        <v>0.07040537340450823</v>
       </c>
       <c r="C43">
-        <v>2584.598741816391</v>
+        <v>2514.641086532196</v>
       </c>
       <c r="D43">
-        <v>3818.877846024748</v>
+        <v>3793.300168891976</v>
       </c>
       <c r="E43">
-        <v>-1414.118710933976</v>
+        <v>-1369.738732782552</v>
       </c>
       <c r="F43">
-        <v>1819.579104208356</v>
+        <v>1863.95908235978</v>
       </c>
       <c r="G43">
         <v>585.3</v>
@@ -4807,45 +4807,45 @@
         <v>473.4</v>
       </c>
       <c r="M43">
-        <v>115.9738158520852</v>
+        <v>125.3263022952733</v>
       </c>
       <c r="N43">
-        <v>357.4261841479148</v>
+        <v>348.0736977047267</v>
       </c>
       <c r="O43">
-        <v>89.3565460369787</v>
+        <v>87.01842442618167</v>
       </c>
       <c r="P43">
-        <v>268.0696381109361</v>
+        <v>261.055273278545</v>
       </c>
       <c r="Q43">
-        <v>1062.669638110936</v>
+        <v>1055.655273278545</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08431718708898675</v>
+        <v>0.08487213647553445</v>
       </c>
       <c r="T43">
-        <v>0.7507716683669799</v>
+        <v>0.7615886648375444</v>
       </c>
       <c r="U43">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04780246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.08195588393661</v>
+        <v>3.777339563443373</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07040537340450823</v>
+        <v>0.07038834680278502</v>
       </c>
       <c r="C44">
-        <v>2514.641086532197</v>
+        <v>2470.669549742961</v>
       </c>
       <c r="D44">
-        <v>3793.300168891976</v>
+        <v>3793.708610254164</v>
       </c>
       <c r="E44">
-        <v>-1369.738732782552</v>
+        <v>-1325.358754631129</v>
       </c>
       <c r="F44">
-        <v>1863.959082359779</v>
+        <v>1908.339060511203</v>
       </c>
       <c r="G44">
         <v>585.3</v>
@@ -4889,28 +4889,28 @@
         <v>473.4</v>
       </c>
       <c r="M44">
-        <v>125.3263022952733</v>
+        <v>128.3102618737322</v>
       </c>
       <c r="N44">
-        <v>348.0736977047267</v>
+        <v>345.0897381262678</v>
       </c>
       <c r="O44">
-        <v>87.01842442618167</v>
+        <v>86.27243453156694</v>
       </c>
       <c r="P44">
-        <v>261.055273278545</v>
+        <v>258.8173035947008</v>
       </c>
       <c r="Q44">
-        <v>1055.655273278545</v>
+        <v>1053.417303594701</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08487213647553445</v>
+        <v>0.08544655777038206</v>
       </c>
       <c r="T44">
-        <v>0.7615886648375444</v>
+        <v>0.7727852050439181</v>
       </c>
       <c r="U44">
         <v>0.0672366166625341</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.777339563443374</v>
+        <v>3.689494457316783</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07038834680278502</v>
+        <v>0.07037132020106182</v>
       </c>
       <c r="C45">
-        <v>2470.669549742961</v>
+        <v>2426.698100920564</v>
       </c>
       <c r="D45">
-        <v>3793.708610254164</v>
+        <v>3794.11713958319</v>
       </c>
       <c r="E45">
-        <v>-1325.358754631129</v>
+        <v>-1280.978776479706</v>
       </c>
       <c r="F45">
-        <v>1908.339060511203</v>
+        <v>1952.719038662626</v>
       </c>
       <c r="G45">
         <v>585.3</v>
@@ -4971,28 +4971,28 @@
         <v>473.4</v>
       </c>
       <c r="M45">
-        <v>128.3102618737322</v>
+        <v>131.2942214521911</v>
       </c>
       <c r="N45">
-        <v>345.0897381262678</v>
+        <v>342.1057785478089</v>
       </c>
       <c r="O45">
-        <v>86.27243453156694</v>
+        <v>85.52644463695222</v>
       </c>
       <c r="P45">
-        <v>258.8173035947008</v>
+        <v>256.5793339108567</v>
       </c>
       <c r="Q45">
-        <v>1053.417303594701</v>
+        <v>1051.179333910857</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08544655777038206</v>
+        <v>0.08604149411147423</v>
       </c>
       <c r="T45">
-        <v>0.7727852050439181</v>
+        <v>0.7843816216862339</v>
       </c>
       <c r="U45">
         <v>0.0672366166625341</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.689494457316783</v>
+        <v>3.605642310559584</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07037132020106182</v>
+        <v>0.07035429359933862</v>
       </c>
       <c r="C46">
-        <v>2426.698100920564</v>
+        <v>2382.726740093426</v>
       </c>
       <c r="D46">
-        <v>3794.11713958319</v>
+        <v>3794.525756907476</v>
       </c>
       <c r="E46">
-        <v>-1280.978776479706</v>
+        <v>-1236.598798328282</v>
       </c>
       <c r="F46">
-        <v>1952.719038662626</v>
+        <v>1997.099016814049</v>
       </c>
       <c r="G46">
         <v>585.3</v>
@@ -5053,28 +5053,28 @@
         <v>473.4</v>
       </c>
       <c r="M46">
-        <v>131.2942214521911</v>
+        <v>134.27818103065</v>
       </c>
       <c r="N46">
-        <v>342.1057785478089</v>
+        <v>339.12181896935</v>
       </c>
       <c r="O46">
-        <v>85.52644463695222</v>
+        <v>84.7804547423375</v>
       </c>
       <c r="P46">
-        <v>256.5793339108567</v>
+        <v>254.3413642270125</v>
       </c>
       <c r="Q46">
-        <v>1051.179333910857</v>
+        <v>1048.941364227012</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08604149411147423</v>
+        <v>0.08665806450133337</v>
       </c>
       <c r="T46">
-        <v>0.7843816216862339</v>
+        <v>0.7963997262064519</v>
       </c>
       <c r="U46">
         <v>0.0672366166625341</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.605642310559584</v>
+        <v>3.525516925880482</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07035429359933862</v>
+        <v>0.07130326699761542</v>
       </c>
       <c r="C47">
-        <v>2382.726740093426</v>
+        <v>2315.706025611707</v>
       </c>
       <c r="D47">
-        <v>3794.525756907476</v>
+        <v>3771.88502057718</v>
       </c>
       <c r="E47">
-        <v>-1236.598798328282</v>
+        <v>-1192.218820176859</v>
       </c>
       <c r="F47">
-        <v>1997.099016814049</v>
+        <v>2041.478994965473</v>
       </c>
       <c r="G47">
         <v>585.3</v>
@@ -5135,45 +5135,45 @@
         <v>473.4</v>
       </c>
       <c r="M47">
-        <v>134.27818103065</v>
+        <v>142.9782817950122</v>
       </c>
       <c r="N47">
-        <v>339.12181896935</v>
+        <v>330.4217182049878</v>
       </c>
       <c r="O47">
-        <v>84.7804547423375</v>
+        <v>82.60542955124694</v>
       </c>
       <c r="P47">
-        <v>254.3413642270125</v>
+        <v>247.8162886537408</v>
       </c>
       <c r="Q47">
-        <v>1048.941364227012</v>
+        <v>1042.416288653741</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08665806450133337</v>
+        <v>0.0872974708315577</v>
       </c>
       <c r="T47">
-        <v>0.7963997262064519</v>
+        <v>0.8088629457089004</v>
       </c>
       <c r="U47">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.05042746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.525516925880482</v>
+        <v>3.31099236930762</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07130326699761542</v>
+        <v>0.07130724039589222</v>
       </c>
       <c r="C48">
-        <v>2315.706025611707</v>
+        <v>2271.231817567193</v>
       </c>
       <c r="D48">
-        <v>3771.88502057718</v>
+        <v>3771.79079068409</v>
       </c>
       <c r="E48">
-        <v>-1192.218820176859</v>
+        <v>-1147.838842025435</v>
       </c>
       <c r="F48">
-        <v>2041.478994965473</v>
+        <v>2085.858973116896</v>
       </c>
       <c r="G48">
         <v>585.3</v>
@@ -5217,28 +5217,28 @@
         <v>473.4</v>
       </c>
       <c r="M48">
-        <v>142.9782817950122</v>
+        <v>146.0865053122951</v>
       </c>
       <c r="N48">
-        <v>330.4217182049878</v>
+        <v>327.3134946877049</v>
       </c>
       <c r="O48">
-        <v>82.60542955124694</v>
+        <v>81.82837367192623</v>
       </c>
       <c r="P48">
-        <v>247.8162886537408</v>
+        <v>245.4851210157787</v>
       </c>
       <c r="Q48">
-        <v>1042.416288653741</v>
+        <v>1040.085121015779</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0872974708315577</v>
+        <v>0.08796100570254518</v>
       </c>
       <c r="T48">
-        <v>0.8088629457089004</v>
+        <v>0.8217964753812524</v>
       </c>
       <c r="U48">
         <v>0.07003661666253409</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.31099236930762</v>
+        <v>3.240545723152139</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07130724039589222</v>
+        <v>0.07131121379416902</v>
       </c>
       <c r="C49">
-        <v>2271.231817567193</v>
+        <v>2226.757614230698</v>
       </c>
       <c r="D49">
-        <v>3771.79079068409</v>
+        <v>3771.696565499018</v>
       </c>
       <c r="E49">
-        <v>-1147.838842025435</v>
+        <v>-1103.458863874012</v>
       </c>
       <c r="F49">
-        <v>2085.858973116896</v>
+        <v>2130.238951268319</v>
       </c>
       <c r="G49">
         <v>585.3</v>
@@ -5299,28 +5299,28 @@
         <v>473.4</v>
       </c>
       <c r="M49">
-        <v>146.0865053122951</v>
+        <v>149.1947288295779</v>
       </c>
       <c r="N49">
-        <v>327.3134946877049</v>
+        <v>324.2052711704221</v>
       </c>
       <c r="O49">
-        <v>81.82837367192623</v>
+        <v>81.05131779260552</v>
       </c>
       <c r="P49">
-        <v>245.4851210157787</v>
+        <v>243.1539533778165</v>
       </c>
       <c r="Q49">
-        <v>1040.085121015779</v>
+        <v>1037.753953377817</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08796100570254518</v>
+        <v>0.08865006114549373</v>
       </c>
       <c r="T49">
-        <v>0.8217964753812524</v>
+        <v>0.8352274485025412</v>
       </c>
       <c r="U49">
         <v>0.07003661666253409</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.240545723152139</v>
+        <v>3.173034353919803</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07131121379416902</v>
+        <v>0.07131518719244581</v>
       </c>
       <c r="C50">
-        <v>2226.757614230698</v>
+        <v>2182.283415601868</v>
       </c>
       <c r="D50">
-        <v>3771.696565499018</v>
+        <v>3771.60234502161</v>
       </c>
       <c r="E50">
-        <v>-1103.458863874012</v>
+        <v>-1059.078885722589</v>
       </c>
       <c r="F50">
-        <v>2130.238951268319</v>
+        <v>2174.618929419742</v>
       </c>
       <c r="G50">
         <v>585.3</v>
@@ -5381,28 +5381,28 @@
         <v>473.4</v>
       </c>
       <c r="M50">
-        <v>149.1947288295779</v>
+        <v>152.3029523468608</v>
       </c>
       <c r="N50">
-        <v>324.2052711704221</v>
+        <v>321.0970476531392</v>
       </c>
       <c r="O50">
-        <v>81.05131779260552</v>
+        <v>80.27426191328479</v>
       </c>
       <c r="P50">
-        <v>243.1539533778165</v>
+        <v>240.8227857398544</v>
       </c>
       <c r="Q50">
-        <v>1037.753953377817</v>
+        <v>1035.422785739854</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08865006114549373</v>
+        <v>0.08936613837051868</v>
       </c>
       <c r="T50">
-        <v>0.8352274485025412</v>
+        <v>0.8491851264521156</v>
       </c>
       <c r="U50">
         <v>0.07003661666253409</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.173034353919803</v>
+        <v>3.108278550778582</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07131518719244581</v>
+        <v>0.07131916059072262</v>
       </c>
       <c r="C51">
-        <v>2182.283415601868</v>
+        <v>2137.809221680348</v>
       </c>
       <c r="D51">
-        <v>3771.60234502161</v>
+        <v>3771.508129251515</v>
       </c>
       <c r="E51">
-        <v>-1059.078885722589</v>
+        <v>-1014.698907571166</v>
       </c>
       <c r="F51">
-        <v>2174.618929419742</v>
+        <v>2218.998907571166</v>
       </c>
       <c r="G51">
         <v>585.3</v>
@@ -5463,28 +5463,28 @@
         <v>473.4</v>
       </c>
       <c r="M51">
-        <v>152.3029523468608</v>
+        <v>155.4111758641437</v>
       </c>
       <c r="N51">
-        <v>321.0970476531392</v>
+        <v>317.9888241358563</v>
       </c>
       <c r="O51">
-        <v>80.27426191328479</v>
+        <v>79.49720603396408</v>
       </c>
       <c r="P51">
-        <v>240.8227857398544</v>
+        <v>238.4916181018922</v>
       </c>
       <c r="Q51">
-        <v>1035.422785739854</v>
+        <v>1033.091618101892</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08936613837051868</v>
+        <v>0.09011085868454466</v>
       </c>
       <c r="T51">
-        <v>0.8491851264521156</v>
+        <v>0.8637011115196733</v>
       </c>
       <c r="U51">
         <v>0.07003661666253409</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.108278550778582</v>
+        <v>3.046112979763011</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07131916059072262</v>
+        <v>0.07430663398899941</v>
       </c>
       <c r="C52">
-        <v>2137.809221680348</v>
+        <v>2023.899043603045</v>
       </c>
       <c r="D52">
-        <v>3771.508129251515</v>
+        <v>3701.977929325634</v>
       </c>
       <c r="E52">
-        <v>-1014.698907571166</v>
+        <v>-970.3189294197423</v>
       </c>
       <c r="F52">
-        <v>2218.998907571166</v>
+        <v>2263.37888572259</v>
       </c>
       <c r="G52">
         <v>585.3</v>
@@ -5545,45 +5545,45 @@
         <v>473.4</v>
       </c>
       <c r="M52">
-        <v>155.4111758641437</v>
+        <v>176.1737546900628</v>
       </c>
       <c r="N52">
-        <v>317.9888241358563</v>
+        <v>297.2262453099372</v>
       </c>
       <c r="O52">
-        <v>79.49720603396408</v>
+        <v>74.3065613274843</v>
       </c>
       <c r="P52">
-        <v>238.4916181018922</v>
+        <v>222.9196839824529</v>
       </c>
       <c r="Q52">
-        <v>1033.091618101892</v>
+        <v>1017.519683982453</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09011085868454466</v>
+        <v>0.09088597574608187</v>
       </c>
       <c r="T52">
-        <v>0.8637011115196733</v>
+        <v>0.8788095857736617</v>
       </c>
       <c r="U52">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.05252746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.046112979763011</v>
+        <v>2.687119888162901</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07430663398899941</v>
+        <v>0.0743691073872762</v>
       </c>
       <c r="C53">
-        <v>2023.899043603045</v>
+        <v>1978.09242037907</v>
       </c>
       <c r="D53">
-        <v>3701.977929325634</v>
+        <v>3700.551284253082</v>
       </c>
       <c r="E53">
-        <v>-970.3189294197423</v>
+        <v>-925.9389512683192</v>
       </c>
       <c r="F53">
-        <v>2263.37888572259</v>
+        <v>2307.758863874013</v>
       </c>
       <c r="G53">
         <v>585.3</v>
@@ -5627,28 +5627,28 @@
         <v>473.4</v>
       </c>
       <c r="M53">
-        <v>176.1737546900628</v>
+        <v>179.6281420369268</v>
       </c>
       <c r="N53">
-        <v>297.2262453099372</v>
+        <v>293.7718579630732</v>
       </c>
       <c r="O53">
-        <v>74.3065613274843</v>
+        <v>73.4429644907683</v>
       </c>
       <c r="P53">
-        <v>222.9196839824529</v>
+        <v>220.3288934723049</v>
       </c>
       <c r="Q53">
-        <v>1017.519683982453</v>
+        <v>1014.928893472305</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09088597574608187</v>
+        <v>0.09169338935184981</v>
       </c>
       <c r="T53">
-        <v>0.8788095857736617</v>
+        <v>0.8945475797882331</v>
       </c>
       <c r="U53">
         <v>0.07783661666253411</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.687119888162901</v>
+        <v>2.635444505698231</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0743691073872762</v>
+        <v>0.07443158078555301</v>
       </c>
       <c r="C54">
-        <v>1978.09242037907</v>
+        <v>1932.286896314597</v>
       </c>
       <c r="D54">
-        <v>3700.551284253082</v>
+        <v>3699.125738340033</v>
       </c>
       <c r="E54">
-        <v>-925.9389512683192</v>
+        <v>-881.5589731168957</v>
       </c>
       <c r="F54">
-        <v>2307.758863874013</v>
+        <v>2352.138842025436</v>
       </c>
       <c r="G54">
         <v>585.3</v>
@@ -5709,28 +5709,28 @@
         <v>473.4</v>
       </c>
       <c r="M54">
-        <v>179.6281420369268</v>
+        <v>183.0825293837908</v>
       </c>
       <c r="N54">
-        <v>293.7718579630732</v>
+        <v>290.3174706162092</v>
       </c>
       <c r="O54">
-        <v>73.4429644907683</v>
+        <v>72.57936765405231</v>
       </c>
       <c r="P54">
-        <v>220.3288934723049</v>
+        <v>217.7381029621569</v>
       </c>
       <c r="Q54">
-        <v>1014.928893472305</v>
+        <v>1012.338102962157</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09169338935184981</v>
+        <v>0.09253516098339512</v>
       </c>
       <c r="T54">
-        <v>0.8945475797882331</v>
+        <v>0.910955275675765</v>
       </c>
       <c r="U54">
         <v>0.07783661666253411</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.635444505698231</v>
+        <v>2.585719137666188</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07443158078555301</v>
+        <v>0.07449405418382982</v>
       </c>
       <c r="C55">
-        <v>1932.286896314597</v>
+        <v>1886.482470139841</v>
       </c>
       <c r="D55">
-        <v>3699.125738340033</v>
+        <v>3697.701290316701</v>
       </c>
       <c r="E55">
-        <v>-881.5589731168957</v>
+        <v>-837.1789949654722</v>
       </c>
       <c r="F55">
-        <v>2352.138842025436</v>
+        <v>2396.51882017686</v>
       </c>
       <c r="G55">
         <v>585.3</v>
@@ -5791,28 +5791,28 @@
         <v>473.4</v>
       </c>
       <c r="M55">
-        <v>183.0825293837908</v>
+        <v>186.5369167306547</v>
       </c>
       <c r="N55">
-        <v>290.3174706162092</v>
+        <v>286.8630832693452</v>
       </c>
       <c r="O55">
-        <v>72.57936765405231</v>
+        <v>71.71577081733631</v>
       </c>
       <c r="P55">
-        <v>217.7381029621569</v>
+        <v>215.1473124520089</v>
       </c>
       <c r="Q55">
-        <v>1012.338102962157</v>
+        <v>1009.747312452009</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09253516098339512</v>
+        <v>0.09341353138152936</v>
       </c>
       <c r="T55">
-        <v>0.910955275675765</v>
+        <v>0.9280763496453632</v>
       </c>
       <c r="U55">
         <v>0.07783661666253411</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.585719137666188</v>
+        <v>2.537835449931629</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07449405418382982</v>
+        <v>0.0761652775821066</v>
       </c>
       <c r="C56">
-        <v>1886.482470139841</v>
+        <v>1804.400191044563</v>
       </c>
       <c r="D56">
-        <v>3697.701290316701</v>
+        <v>3659.998989372845</v>
       </c>
       <c r="E56">
-        <v>-837.1789949654722</v>
+        <v>-792.7990168140491</v>
       </c>
       <c r="F56">
-        <v>2396.51882017686</v>
+        <v>2440.898798328283</v>
       </c>
       <c r="G56">
         <v>585.3</v>
@@ -5873,45 +5873,45 @@
         <v>473.4</v>
       </c>
       <c r="M56">
-        <v>186.5369167306547</v>
+        <v>199.510809390999</v>
       </c>
       <c r="N56">
-        <v>286.8630832693452</v>
+        <v>273.889190609001</v>
       </c>
       <c r="O56">
-        <v>71.71577081733631</v>
+        <v>68.47229765225026</v>
       </c>
       <c r="P56">
-        <v>215.1473124520089</v>
+        <v>205.4168929567508</v>
       </c>
       <c r="Q56">
-        <v>1009.747312452009</v>
+        <v>1000.016892956751</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09341353138152936</v>
+        <v>0.0943309404640251</v>
       </c>
       <c r="T56">
-        <v>0.9280763496453632</v>
+        <v>0.9459583602358328</v>
       </c>
       <c r="U56">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.05837746249690058</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.537835449931629</v>
+        <v>2.372803766598111</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0761652775821066</v>
+        <v>0.0762570009803834</v>
       </c>
       <c r="C57">
-        <v>1804.400191044563</v>
+        <v>1757.973204326931</v>
       </c>
       <c r="D57">
-        <v>3659.998989372845</v>
+        <v>3657.951980806637</v>
       </c>
       <c r="E57">
-        <v>-792.7990168140491</v>
+        <v>-748.4190386626256</v>
       </c>
       <c r="F57">
-        <v>2440.898798328283</v>
+        <v>2485.278776479706</v>
       </c>
       <c r="G57">
         <v>585.3</v>
@@ -5955,28 +5955,28 @@
         <v>473.4</v>
       </c>
       <c r="M57">
-        <v>199.510809390999</v>
+        <v>203.1382786526535</v>
       </c>
       <c r="N57">
-        <v>273.889190609001</v>
+        <v>270.2617213473465</v>
       </c>
       <c r="O57">
-        <v>68.47229765225026</v>
+        <v>67.56543033683661</v>
       </c>
       <c r="P57">
-        <v>205.4168929567508</v>
+        <v>202.6962910105098</v>
       </c>
       <c r="Q57">
-        <v>1000.016892956751</v>
+        <v>997.2962910105099</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.0943309404640251</v>
+        <v>0.09529004995936155</v>
       </c>
       <c r="T57">
-        <v>0.9459583602358328</v>
+        <v>0.9646531894895052</v>
       </c>
       <c r="U57">
         <v>0.0817366166625341</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.372803766598111</v>
+        <v>2.330432270766001</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0762570009803834</v>
+        <v>0.07634872437866021</v>
       </c>
       <c r="C58">
-        <v>1757.973204326931</v>
+        <v>1711.548506080867</v>
       </c>
       <c r="D58">
-        <v>3657.951980806637</v>
+        <v>3655.907260711996</v>
       </c>
       <c r="E58">
-        <v>-748.4190386626256</v>
+        <v>-704.0390605112025</v>
       </c>
       <c r="F58">
-        <v>2485.278776479706</v>
+        <v>2529.658754631129</v>
       </c>
       <c r="G58">
         <v>585.3</v>
@@ -6037,28 +6037,28 @@
         <v>473.4</v>
       </c>
       <c r="M58">
-        <v>203.1382786526535</v>
+        <v>206.765747914308</v>
       </c>
       <c r="N58">
-        <v>270.2617213473465</v>
+        <v>266.634252085692</v>
       </c>
       <c r="O58">
-        <v>67.56543033683661</v>
+        <v>66.65856302142299</v>
       </c>
       <c r="P58">
-        <v>202.6962910105098</v>
+        <v>199.975689064269</v>
       </c>
       <c r="Q58">
-        <v>997.2962910105099</v>
+        <v>994.575689064269</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09529004995936155</v>
+        <v>0.09629376919866717</v>
       </c>
       <c r="T58">
-        <v>0.9646531894895052</v>
+        <v>0.9842175456852091</v>
       </c>
       <c r="U58">
         <v>0.0817366166625341</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.330432270766001</v>
+        <v>2.289547494085896</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07634872437866021</v>
+        <v>0.07644044777693701</v>
       </c>
       <c r="C59">
-        <v>1711.548506080867</v>
+        <v>1665.126092470886</v>
       </c>
       <c r="D59">
-        <v>3655.907260711996</v>
+        <v>3653.864825253439</v>
       </c>
       <c r="E59">
-        <v>-704.0390605112025</v>
+        <v>-659.6590823597789</v>
       </c>
       <c r="F59">
-        <v>2529.658754631129</v>
+        <v>2574.038732782553</v>
       </c>
       <c r="G59">
         <v>585.3</v>
@@ -6119,28 +6119,28 @@
         <v>473.4</v>
       </c>
       <c r="M59">
-        <v>206.765747914308</v>
+        <v>210.3932171759625</v>
       </c>
       <c r="N59">
-        <v>266.634252085692</v>
+        <v>263.0067828240374</v>
       </c>
       <c r="O59">
-        <v>66.65856302142299</v>
+        <v>65.75169570600936</v>
       </c>
       <c r="P59">
-        <v>199.975689064269</v>
+        <v>197.2550871180281</v>
       </c>
       <c r="Q59">
-        <v>994.575689064269</v>
+        <v>991.8550871180281</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09629376919866717</v>
+        <v>0.09734528459222541</v>
       </c>
       <c r="T59">
-        <v>0.9842175456852091</v>
+        <v>1.004713537890232</v>
       </c>
       <c r="U59">
         <v>0.0817366166625341</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.289547494085896</v>
+        <v>2.250072537291311</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07644044777693701</v>
+        <v>0.0765321711752138</v>
       </c>
       <c r="C60">
-        <v>1665.126092470886</v>
+        <v>1618.705959670073</v>
       </c>
       <c r="D60">
-        <v>3653.864825253439</v>
+        <v>3651.82467060405</v>
       </c>
       <c r="E60">
-        <v>-659.6590823597794</v>
+        <v>-615.2791042083559</v>
       </c>
       <c r="F60">
-        <v>2574.038732782552</v>
+        <v>2618.418710933976</v>
       </c>
       <c r="G60">
         <v>585.3</v>
@@ -6201,28 +6201,28 @@
         <v>473.4</v>
       </c>
       <c r="M60">
-        <v>210.3932171759625</v>
+        <v>214.0206864376171</v>
       </c>
       <c r="N60">
-        <v>263.0067828240375</v>
+        <v>259.3793135623829</v>
       </c>
       <c r="O60">
-        <v>65.75169570600937</v>
+        <v>64.84482839059572</v>
       </c>
       <c r="P60">
-        <v>197.2550871180281</v>
+        <v>194.5344851717872</v>
       </c>
       <c r="Q60">
-        <v>991.8550871180281</v>
+        <v>989.1344851717872</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09734528459222541</v>
+        <v>0.09844809341961577</v>
       </c>
       <c r="T60">
-        <v>1.004713537890232</v>
+        <v>1.026209334593061</v>
       </c>
       <c r="U60">
         <v>0.0817366166625341</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.250072537291312</v>
+        <v>2.211935714625357</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0765321711752138</v>
+        <v>0.0766238945734906</v>
       </c>
       <c r="C61">
-        <v>1618.705959670073</v>
+        <v>1572.288103860056</v>
       </c>
       <c r="D61">
-        <v>3651.82467060405</v>
+        <v>3649.786792945456</v>
       </c>
       <c r="E61">
-        <v>-615.2791042083559</v>
+        <v>-570.8991260569328</v>
       </c>
       <c r="F61">
-        <v>2618.418710933976</v>
+        <v>2662.798689085399</v>
       </c>
       <c r="G61">
         <v>585.3</v>
@@ -6283,28 +6283,28 @@
         <v>473.4</v>
       </c>
       <c r="M61">
-        <v>214.0206864376171</v>
+        <v>217.6481556992716</v>
       </c>
       <c r="N61">
-        <v>259.3793135623829</v>
+        <v>255.7518443007284</v>
       </c>
       <c r="O61">
-        <v>64.84482839059572</v>
+        <v>63.9379610751821</v>
       </c>
       <c r="P61">
-        <v>194.5344851717872</v>
+        <v>191.8138832255463</v>
       </c>
       <c r="Q61">
-        <v>989.1344851717872</v>
+        <v>986.4138832255463</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09844809341961577</v>
+        <v>0.09960604268837564</v>
       </c>
       <c r="T61">
-        <v>1.026209334593061</v>
+        <v>1.048779921131032</v>
       </c>
       <c r="U61">
         <v>0.0817366166625341</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.211935714625357</v>
+        <v>2.175070119381601</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0766238945734906</v>
+        <v>0.0767156179717674</v>
       </c>
       <c r="C62">
-        <v>1572.288103860056</v>
+        <v>1525.872521230979</v>
       </c>
       <c r="D62">
-        <v>3649.786792945456</v>
+        <v>3647.751188467802</v>
       </c>
       <c r="E62">
-        <v>-570.8991260569328</v>
+        <v>-526.5191479055093</v>
       </c>
       <c r="F62">
-        <v>2662.798689085399</v>
+        <v>2707.178667236823</v>
       </c>
       <c r="G62">
         <v>585.3</v>
@@ -6365,28 +6365,28 @@
         <v>473.4</v>
       </c>
       <c r="M62">
-        <v>217.6481556992716</v>
+        <v>221.2756249609261</v>
       </c>
       <c r="N62">
-        <v>255.7518443007284</v>
+        <v>252.1243750390739</v>
       </c>
       <c r="O62">
-        <v>63.9379610751821</v>
+        <v>63.03109375976847</v>
       </c>
       <c r="P62">
-        <v>191.8138832255463</v>
+        <v>189.0932812793054</v>
       </c>
       <c r="Q62">
-        <v>986.4138832255463</v>
+        <v>983.6932812793054</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09960604268837564</v>
+        <v>0.1008233739709181</v>
       </c>
       <c r="T62">
-        <v>1.048779921131032</v>
+        <v>1.072507973645309</v>
       </c>
       <c r="U62">
         <v>0.0817366166625341</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.175070119381601</v>
+        <v>2.139413232178624</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0767156179717674</v>
+        <v>0.0768073413700442</v>
       </c>
       <c r="C63">
-        <v>1525.872521230979</v>
+        <v>1479.459207981482</v>
       </c>
       <c r="D63">
-        <v>3647.751188467802</v>
+        <v>3645.717853369728</v>
       </c>
       <c r="E63">
-        <v>-526.5191479055093</v>
+        <v>-482.1391697540862</v>
       </c>
       <c r="F63">
-        <v>2707.178667236823</v>
+        <v>2751.558645388246</v>
       </c>
       <c r="G63">
         <v>585.3</v>
@@ -6447,28 +6447,28 @@
         <v>473.4</v>
       </c>
       <c r="M63">
-        <v>221.2756249609261</v>
+        <v>224.9030942225806</v>
       </c>
       <c r="N63">
-        <v>252.1243750390739</v>
+        <v>248.4969057774194</v>
       </c>
       <c r="O63">
-        <v>63.03109375976847</v>
+        <v>62.12422644435484</v>
       </c>
       <c r="P63">
-        <v>189.0932812793054</v>
+        <v>186.3726793330645</v>
       </c>
       <c r="Q63">
-        <v>983.6932812793054</v>
+        <v>980.9726793330645</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1008233739709181</v>
+        <v>0.1021047753209628</v>
       </c>
       <c r="T63">
-        <v>1.072507973645309</v>
+        <v>1.097484871028758</v>
       </c>
       <c r="U63">
         <v>0.0817366166625341</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.139413232178624</v>
+        <v>2.104906567143485</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0768073413700442</v>
+        <v>0.07689906476832101</v>
       </c>
       <c r="C64">
-        <v>1479.459207981482</v>
+        <v>1433.048160318676</v>
       </c>
       <c r="D64">
-        <v>3645.717853369728</v>
+        <v>3643.686783858345</v>
       </c>
       <c r="E64">
-        <v>-482.1391697540862</v>
+        <v>-437.7591916026627</v>
       </c>
       <c r="F64">
-        <v>2751.558645388246</v>
+        <v>2795.938623539669</v>
       </c>
       <c r="G64">
         <v>585.3</v>
@@ -6529,28 +6529,28 @@
         <v>473.4</v>
       </c>
       <c r="M64">
-        <v>224.9030942225806</v>
+        <v>228.5305634842352</v>
       </c>
       <c r="N64">
-        <v>248.4969057774194</v>
+        <v>244.8694365157648</v>
       </c>
       <c r="O64">
-        <v>62.12422644435484</v>
+        <v>61.2173591289412</v>
       </c>
       <c r="P64">
-        <v>186.3726793330645</v>
+        <v>183.6520773868236</v>
       </c>
       <c r="Q64">
-        <v>980.9726793330645</v>
+        <v>978.2520773868237</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1021047753209628</v>
+        <v>0.1034554416088477</v>
       </c>
       <c r="T64">
-        <v>1.097484871028758</v>
+        <v>1.123811870973475</v>
       </c>
       <c r="U64">
         <v>0.0817366166625341</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.104906567143485</v>
+        <v>2.071495351792001</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07689906476832101</v>
+        <v>0.0769907881665978</v>
       </c>
       <c r="C65">
-        <v>1433.048160318676</v>
+        <v>1386.63937445812</v>
       </c>
       <c r="D65">
-        <v>3643.686783858345</v>
+        <v>3641.657976149213</v>
       </c>
       <c r="E65">
-        <v>-437.7591916026627</v>
+        <v>-393.3792134512391</v>
       </c>
       <c r="F65">
-        <v>2795.938623539669</v>
+        <v>2840.318601691093</v>
       </c>
       <c r="G65">
         <v>585.3</v>
@@ -6611,28 +6611,28 @@
         <v>473.4</v>
       </c>
       <c r="M65">
-        <v>228.5305634842352</v>
+        <v>232.1580327458897</v>
       </c>
       <c r="N65">
-        <v>244.8694365157648</v>
+        <v>241.2419672541103</v>
       </c>
       <c r="O65">
-        <v>61.2173591289412</v>
+        <v>60.31049181352757</v>
       </c>
       <c r="P65">
-        <v>183.6520773868236</v>
+        <v>180.9314754405827</v>
       </c>
       <c r="Q65">
-        <v>978.2520773868237</v>
+        <v>975.5314754405828</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1034554416088477</v>
+        <v>0.1048811449127262</v>
       </c>
       <c r="T65">
-        <v>1.123811870973475</v>
+        <v>1.151601482026231</v>
       </c>
       <c r="U65">
         <v>0.0817366166625341</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.071495351792001</v>
+        <v>2.039128236920251</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0769907881665978</v>
+        <v>0.0770825115648746</v>
       </c>
       <c r="C66">
-        <v>1386.63937445812</v>
+        <v>1340.232846623797</v>
       </c>
       <c r="D66">
-        <v>3641.657976149213</v>
+        <v>3639.631426466312</v>
       </c>
       <c r="E66">
-        <v>-393.3792134512391</v>
+        <v>-348.9992352998161</v>
       </c>
       <c r="F66">
-        <v>2840.318601691093</v>
+        <v>2884.698579842516</v>
       </c>
       <c r="G66">
         <v>585.3</v>
@@ -6693,28 +6693,28 @@
         <v>473.4</v>
       </c>
       <c r="M66">
-        <v>232.1580327458897</v>
+        <v>235.7855020075442</v>
       </c>
       <c r="N66">
-        <v>241.2419672541103</v>
+        <v>237.6144979924558</v>
       </c>
       <c r="O66">
-        <v>60.31049181352757</v>
+        <v>59.40362449811394</v>
       </c>
       <c r="P66">
-        <v>180.9314754405827</v>
+        <v>178.2108734943418</v>
       </c>
       <c r="Q66">
-        <v>975.5314754405828</v>
+        <v>972.8108734943419</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1048811449127262</v>
+        <v>0.1063883169768264</v>
       </c>
       <c r="T66">
-        <v>1.151601482026231</v>
+        <v>1.180979070853431</v>
       </c>
       <c r="U66">
         <v>0.0817366166625341</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.039128236920251</v>
+        <v>2.007757033275325</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0770825115648746</v>
+        <v>0.08420323496315139</v>
       </c>
       <c r="C67">
-        <v>1340.232846623797</v>
+        <v>1145.125835921453</v>
       </c>
       <c r="D67">
-        <v>3639.631426466312</v>
+        <v>3488.904393915393</v>
       </c>
       <c r="E67">
-        <v>-348.9992352998161</v>
+        <v>-304.6192571483925</v>
       </c>
       <c r="F67">
-        <v>2884.698579842516</v>
+        <v>2929.078557993939</v>
       </c>
       <c r="G67">
         <v>585.3</v>
@@ -6775,45 +6775,45 @@
         <v>473.4</v>
       </c>
       <c r="M67">
-        <v>235.7855020075442</v>
+        <v>281.0058867927127</v>
       </c>
       <c r="N67">
-        <v>237.6144979924558</v>
+        <v>192.3941132072873</v>
       </c>
       <c r="O67">
-        <v>59.40362449811394</v>
+        <v>48.09852830182182</v>
       </c>
       <c r="P67">
-        <v>178.2108734943418</v>
+        <v>144.2955849054654</v>
       </c>
       <c r="Q67">
-        <v>972.8108734943419</v>
+        <v>938.8955849054655</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1063883169768264</v>
+        <v>0.1079841462211677</v>
       </c>
       <c r="T67">
-        <v>1.180979070853431</v>
+        <v>1.212084753141054</v>
       </c>
       <c r="U67">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.06130246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.007757033275325</v>
+        <v>1.684662216166343</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08420323496315139</v>
+        <v>0.08440145836142819</v>
       </c>
       <c r="C68">
-        <v>1145.125835921453</v>
+        <v>1096.728382296647</v>
       </c>
       <c r="D68">
-        <v>3488.904393915393</v>
+        <v>3484.88691844201</v>
       </c>
       <c r="E68">
-        <v>-304.6192571483925</v>
+        <v>-260.239278996969</v>
       </c>
       <c r="F68">
-        <v>2929.078557993939</v>
+        <v>2973.458536145363</v>
       </c>
       <c r="G68">
         <v>585.3</v>
@@ -6857,28 +6857,28 @@
         <v>473.4</v>
       </c>
       <c r="M68">
-        <v>281.0058867927127</v>
+        <v>285.2635517441175</v>
       </c>
       <c r="N68">
-        <v>192.3941132072873</v>
+        <v>188.1364482558825</v>
       </c>
       <c r="O68">
-        <v>48.09852830182182</v>
+        <v>47.03411206397062</v>
       </c>
       <c r="P68">
-        <v>144.2955849054654</v>
+        <v>141.1023361919119</v>
       </c>
       <c r="Q68">
-        <v>938.8955849054655</v>
+        <v>935.7023361919119</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1079841462211677</v>
+        <v>0.1096766923894085</v>
       </c>
       <c r="T68">
-        <v>1.212084753141054</v>
+        <v>1.245075628294594</v>
       </c>
       <c r="U68">
         <v>0.0959366166625341</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.684662216166343</v>
+        <v>1.659518003984756</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08440145836142819</v>
+        <v>0.084599681759705</v>
       </c>
       <c r="C69">
-        <v>1096.728382296647</v>
+        <v>1048.340170280891</v>
       </c>
       <c r="D69">
-        <v>3484.88691844201</v>
+        <v>3480.878684577677</v>
       </c>
       <c r="E69">
-        <v>-260.239278996969</v>
+        <v>-215.8593008455459</v>
       </c>
       <c r="F69">
-        <v>2973.458536145363</v>
+        <v>3017.838514296786</v>
       </c>
       <c r="G69">
         <v>585.3</v>
@@ -6939,28 +6939,28 @@
         <v>473.4</v>
       </c>
       <c r="M69">
-        <v>285.2635517441175</v>
+        <v>289.5212166955222</v>
       </c>
       <c r="N69">
-        <v>188.1364482558825</v>
+        <v>183.8787833044778</v>
       </c>
       <c r="O69">
-        <v>47.03411206397062</v>
+        <v>45.96969582611945</v>
       </c>
       <c r="P69">
-        <v>141.1023361919119</v>
+        <v>137.9090874783583</v>
       </c>
       <c r="Q69">
-        <v>935.7023361919119</v>
+        <v>932.5090874783584</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1096766923894085</v>
+        <v>0.1114750226931644</v>
       </c>
       <c r="T69">
-        <v>1.245075628294594</v>
+        <v>1.28012843314523</v>
       </c>
       <c r="U69">
         <v>0.0959366166625341</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.659518003984756</v>
+        <v>1.635113327455568</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.084599681759705</v>
+        <v>0.0847979051579818</v>
       </c>
       <c r="C70">
-        <v>1048.340170280891</v>
+        <v>999.9611680223838</v>
       </c>
       <c r="D70">
-        <v>3480.878684577677</v>
+        <v>3476.879660470594</v>
       </c>
       <c r="E70">
-        <v>-215.8593008455459</v>
+        <v>-171.4793226941224</v>
       </c>
       <c r="F70">
-        <v>3017.838514296786</v>
+        <v>3062.218492448209</v>
       </c>
       <c r="G70">
         <v>585.3</v>
@@ -7021,28 +7021,28 @@
         <v>473.4</v>
       </c>
       <c r="M70">
-        <v>289.5212166955222</v>
+        <v>293.7788816469269</v>
       </c>
       <c r="N70">
-        <v>183.8787833044778</v>
+        <v>179.621118353073</v>
       </c>
       <c r="O70">
-        <v>45.96969582611945</v>
+        <v>44.90527958826826</v>
       </c>
       <c r="P70">
-        <v>137.9090874783583</v>
+        <v>134.7158387648048</v>
       </c>
       <c r="Q70">
-        <v>932.5090874783584</v>
+        <v>929.3158387648048</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1114750226931644</v>
+        <v>0.11338937430684</v>
       </c>
       <c r="T70">
-        <v>1.28012843314523</v>
+        <v>1.317442709276553</v>
       </c>
       <c r="U70">
         <v>0.0959366166625341</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.635113327455568</v>
+        <v>1.611416032854763</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0847979051579818</v>
+        <v>0.0849961285562586</v>
       </c>
       <c r="C71">
-        <v>999.9611680223838</v>
+        <v>951.5913438155312</v>
       </c>
       <c r="D71">
-        <v>3476.879660470594</v>
+        <v>3472.889814415164</v>
       </c>
       <c r="E71">
-        <v>-171.4793226941224</v>
+        <v>-127.0993445426993</v>
       </c>
       <c r="F71">
-        <v>3062.218492448209</v>
+        <v>3106.598470599632</v>
       </c>
       <c r="G71">
         <v>585.3</v>
@@ -7103,28 +7103,28 @@
         <v>473.4</v>
       </c>
       <c r="M71">
-        <v>293.7788816469269</v>
+        <v>298.0365465983317</v>
       </c>
       <c r="N71">
-        <v>179.621118353073</v>
+        <v>175.3634534016683</v>
       </c>
       <c r="O71">
-        <v>44.90527958826826</v>
+        <v>43.84086335041708</v>
       </c>
       <c r="P71">
-        <v>134.7158387648048</v>
+        <v>131.5225900512513</v>
       </c>
       <c r="Q71">
-        <v>929.3158387648048</v>
+        <v>926.1225900512513</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.11338937430684</v>
+        <v>0.1154313493614273</v>
       </c>
       <c r="T71">
-        <v>1.317442709276553</v>
+        <v>1.35724460381663</v>
       </c>
       <c r="U71">
         <v>0.0959366166625341</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.611416032854763</v>
+        <v>1.588395803813981</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0849961285562586</v>
+        <v>0.0851943519545354</v>
       </c>
       <c r="C72">
-        <v>951.5913438155312</v>
+        <v>903.230666100103</v>
       </c>
       <c r="D72">
-        <v>3472.889814415164</v>
+        <v>3468.909114851159</v>
       </c>
       <c r="E72">
-        <v>-127.0993445426993</v>
+        <v>-82.7193663912758</v>
       </c>
       <c r="F72">
-        <v>3106.598470599632</v>
+        <v>3150.978448751056</v>
       </c>
       <c r="G72">
         <v>585.3</v>
@@ -7185,28 +7185,28 @@
         <v>473.4</v>
       </c>
       <c r="M72">
-        <v>298.0365465983317</v>
+        <v>302.2942115497364</v>
       </c>
       <c r="N72">
-        <v>175.3634534016683</v>
+        <v>171.1057884502636</v>
       </c>
       <c r="O72">
-        <v>43.84086335041708</v>
+        <v>42.77644711256589</v>
       </c>
       <c r="P72">
-        <v>131.5225900512513</v>
+        <v>128.3293413376977</v>
       </c>
       <c r="Q72">
-        <v>926.1225900512513</v>
+        <v>922.9293413376977</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1154313493614273</v>
+        <v>0.1176141502818483</v>
       </c>
       <c r="T72">
-        <v>1.35724460381663</v>
+        <v>1.39979145660085</v>
       </c>
       <c r="U72">
         <v>0.0959366166625341</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.588395803813981</v>
+        <v>1.566024031929277</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0851943519545354</v>
+        <v>0.08539257535281219</v>
       </c>
       <c r="C73">
-        <v>903.2306661001035</v>
+        <v>854.879103460406</v>
       </c>
       <c r="D73">
-        <v>3468.909114851159</v>
+        <v>3464.937530362885</v>
       </c>
       <c r="E73">
-        <v>-82.71936639127625</v>
+        <v>-38.33938823985272</v>
       </c>
       <c r="F73">
-        <v>3150.978448751056</v>
+        <v>3195.358426902479</v>
       </c>
       <c r="G73">
         <v>585.3</v>
@@ -7267,28 +7267,28 @@
         <v>473.4</v>
       </c>
       <c r="M73">
-        <v>302.2942115497364</v>
+        <v>306.5518765011411</v>
       </c>
       <c r="N73">
-        <v>171.1057884502636</v>
+        <v>166.8481234988589</v>
       </c>
       <c r="O73">
-        <v>42.7764471125659</v>
+        <v>41.71203087471471</v>
       </c>
       <c r="P73">
-        <v>128.3293413376977</v>
+        <v>125.1360926241441</v>
       </c>
       <c r="Q73">
-        <v>922.9293413376977</v>
+        <v>919.7360926241441</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1176141502818482</v>
+        <v>0.1199528655537278</v>
       </c>
       <c r="T73">
-        <v>1.39979145660085</v>
+        <v>1.445377370298229</v>
       </c>
       <c r="U73">
         <v>0.0959366166625341</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.566024031929277</v>
+        <v>1.544273698152482</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08539257535281219</v>
+        <v>0.08559079875108899</v>
       </c>
       <c r="C74">
-        <v>854.879103460406</v>
+        <v>806.5366246244503</v>
       </c>
       <c r="D74">
-        <v>3464.937530362885</v>
+        <v>3460.975029678353</v>
       </c>
       <c r="E74">
-        <v>-38.33938823985272</v>
+        <v>6.040589911570351</v>
       </c>
       <c r="F74">
-        <v>3195.358426902479</v>
+        <v>3239.738405053902</v>
       </c>
       <c r="G74">
         <v>585.3</v>
@@ -7349,28 +7349,28 @@
         <v>473.4</v>
       </c>
       <c r="M74">
-        <v>306.5518765011411</v>
+        <v>310.8095414525458</v>
       </c>
       <c r="N74">
-        <v>166.8481234988589</v>
+        <v>162.5904585474541</v>
       </c>
       <c r="O74">
-        <v>41.71203087471471</v>
+        <v>40.64761463686354</v>
       </c>
       <c r="P74">
-        <v>125.1360926241441</v>
+        <v>121.9428439105906</v>
       </c>
       <c r="Q74">
-        <v>919.7360926241441</v>
+        <v>916.5428439105906</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1199528655537278</v>
+        <v>0.1224648189938947</v>
       </c>
       <c r="T74">
-        <v>1.445377370298229</v>
+        <v>1.494340018343562</v>
       </c>
       <c r="U74">
         <v>0.0959366166625341</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.544273698152482</v>
+        <v>1.523119263931215</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08559079875108899</v>
+        <v>0.08578902214936579</v>
       </c>
       <c r="C75">
-        <v>806.5366246244503</v>
+        <v>758.2031984631376</v>
       </c>
       <c r="D75">
-        <v>3460.975029678353</v>
+        <v>3457.021581668464</v>
       </c>
       <c r="E75">
-        <v>6.040589911570351</v>
+        <v>50.42056806299388</v>
       </c>
       <c r="F75">
-        <v>3239.738405053902</v>
+        <v>3284.118383205326</v>
       </c>
       <c r="G75">
         <v>585.3</v>
@@ -7431,28 +7431,28 @@
         <v>473.4</v>
       </c>
       <c r="M75">
-        <v>310.8095414525458</v>
+        <v>315.0672064039506</v>
       </c>
       <c r="N75">
-        <v>162.5904585474541</v>
+        <v>158.3327935960494</v>
       </c>
       <c r="O75">
-        <v>40.64761463686354</v>
+        <v>39.58319839901235</v>
       </c>
       <c r="P75">
-        <v>121.9428439105906</v>
+        <v>118.749595197037</v>
       </c>
       <c r="Q75">
-        <v>916.5428439105906</v>
+        <v>913.349595197037</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1224648189938947</v>
+        <v>0.1251699996217668</v>
       </c>
       <c r="T75">
-        <v>1.494340018343562</v>
+        <v>1.547069023930843</v>
       </c>
       <c r="U75">
         <v>0.0959366166625341</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.523119263931215</v>
+        <v>1.502536571175388</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08578902214936579</v>
+        <v>0.1202346280086119</v>
       </c>
       <c r="C76">
-        <v>758.2031984631376</v>
+        <v>141.2629658018068</v>
       </c>
       <c r="D76">
-        <v>3457.021581668464</v>
+        <v>2884.461327158556</v>
       </c>
       <c r="E76">
-        <v>50.42056806299388</v>
+        <v>94.80054621441741</v>
       </c>
       <c r="F76">
-        <v>3284.118383205326</v>
+        <v>3328.498361356749</v>
       </c>
       <c r="G76">
         <v>585.3</v>
@@ -7513,45 +7513,45 @@
         <v>473.4</v>
       </c>
       <c r="M76">
-        <v>315.0672064039506</v>
+        <v>508.3835782804187</v>
       </c>
       <c r="N76">
-        <v>158.3327935960494</v>
+        <v>-34.98357828041873</v>
       </c>
       <c r="O76">
-        <v>39.58319839901235</v>
+        <v>-8.745894570104682</v>
       </c>
       <c r="P76">
-        <v>118.749595197037</v>
+        <v>-26.23768371031404</v>
       </c>
       <c r="Q76">
-        <v>913.349595197037</v>
+        <v>768.362316289686</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1251699996217668</v>
+        <v>0.1293983855840611</v>
       </c>
       <c r="T76">
-        <v>1.547069023930843</v>
+        <v>1.629488136626613</v>
       </c>
       <c r="U76">
-        <v>0.0959366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V76">
-        <v>0.25</v>
+        <v>0.2327966619227017</v>
       </c>
       <c r="W76">
-        <v>0.07195246249690057</v>
+        <v>0.1171800421501289</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.502536571175388</v>
+        <v>0.9311866476908068</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1202346280086119</v>
+        <v>0.1213039941752373</v>
       </c>
       <c r="C77">
-        <v>141.2629658018068</v>
+        <v>82.12765100856768</v>
       </c>
       <c r="D77">
-        <v>2884.461327158556</v>
+        <v>2869.70599051674</v>
       </c>
       <c r="E77">
-        <v>94.80054621441741</v>
+        <v>139.1805243658405</v>
       </c>
       <c r="F77">
-        <v>3328.498361356749</v>
+        <v>3372.878339508172</v>
       </c>
       <c r="G77">
         <v>585.3</v>
@@ -7595,37 +7595,37 @@
         <v>473.4</v>
       </c>
       <c r="M77">
-        <v>508.3835782804187</v>
+        <v>515.1620259908243</v>
       </c>
       <c r="N77">
-        <v>-34.98357828041873</v>
+        <v>-41.76202599082433</v>
       </c>
       <c r="O77">
-        <v>-8.745894570104682</v>
+        <v>-10.44050649770608</v>
       </c>
       <c r="P77">
-        <v>-26.23768371031404</v>
+        <v>-31.32151949311825</v>
       </c>
       <c r="Q77">
-        <v>768.362316289686</v>
+        <v>763.2784805068818</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1293983855840611</v>
+        <v>0.1328816516500637</v>
       </c>
       <c r="T77">
-        <v>1.629488136626613</v>
+        <v>1.697383475652721</v>
       </c>
       <c r="U77">
         <v>0.1527366166625341</v>
       </c>
       <c r="V77">
-        <v>0.2327966619227017</v>
+        <v>0.2297335479500346</v>
       </c>
       <c r="W77">
-        <v>0.1171800421501289</v>
+        <v>0.1176478918147658</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9311866476908068</v>
+        <v>0.9189341918001384</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1213039941752373</v>
+        <v>0.1223733603418626</v>
       </c>
       <c r="C78">
-        <v>82.12765100856768</v>
+        <v>23.14252848079877</v>
       </c>
       <c r="D78">
-        <v>2869.70599051674</v>
+        <v>2855.100846140395</v>
       </c>
       <c r="E78">
-        <v>139.1805243658405</v>
+        <v>183.560502517264</v>
       </c>
       <c r="F78">
-        <v>3372.878339508172</v>
+        <v>3417.258317659596</v>
       </c>
       <c r="G78">
         <v>585.3</v>
@@ -7677,37 +7677,37 @@
         <v>473.4</v>
       </c>
       <c r="M78">
-        <v>515.1620259908243</v>
+        <v>521.9404737012298</v>
       </c>
       <c r="N78">
-        <v>-41.76202599082433</v>
+        <v>-48.54047370122987</v>
       </c>
       <c r="O78">
-        <v>-10.44050649770608</v>
+        <v>-12.13511842530747</v>
       </c>
       <c r="P78">
-        <v>-31.32151949311825</v>
+        <v>-36.4053552759224</v>
       </c>
       <c r="Q78">
-        <v>763.2784805068818</v>
+        <v>758.1946447240776</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1328816516500637</v>
+        <v>0.1366678104174577</v>
       </c>
       <c r="T78">
-        <v>1.697383475652721</v>
+        <v>1.77118275720284</v>
       </c>
       <c r="U78">
         <v>0.1527366166625341</v>
       </c>
       <c r="V78">
-        <v>0.2297335479500346</v>
+        <v>0.2267499953792549</v>
       </c>
       <c r="W78">
-        <v>0.1176478918147658</v>
+        <v>0.1181035895400615</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9189341918001384</v>
+        <v>0.9069999815170197</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1223733603418626</v>
+        <v>0.1234427265084879</v>
       </c>
       <c r="C79">
-        <v>23.14252848079877</v>
+        <v>-35.69468334505291</v>
       </c>
       <c r="D79">
-        <v>2855.100846140395</v>
+        <v>2840.643612465966</v>
       </c>
       <c r="E79">
-        <v>183.560502517264</v>
+        <v>227.9404806686871</v>
       </c>
       <c r="F79">
-        <v>3417.258317659596</v>
+        <v>3461.638295811019</v>
       </c>
       <c r="G79">
         <v>585.3</v>
@@ -7759,37 +7759,37 @@
         <v>473.4</v>
       </c>
       <c r="M79">
-        <v>521.9404737012298</v>
+        <v>528.7189214116354</v>
       </c>
       <c r="N79">
-        <v>-48.54047370122987</v>
+        <v>-55.31892141163542</v>
       </c>
       <c r="O79">
-        <v>-12.13511842530747</v>
+        <v>-13.82973035290885</v>
       </c>
       <c r="P79">
-        <v>-36.4053552759224</v>
+        <v>-41.48919105872656</v>
       </c>
       <c r="Q79">
-        <v>758.1946447240776</v>
+        <v>753.1108089412735</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1366678104174577</v>
+        <v>0.1407981654364331</v>
       </c>
       <c r="T79">
-        <v>1.77118275720284</v>
+        <v>1.851691064348423</v>
       </c>
       <c r="U79">
         <v>0.1527366166625341</v>
       </c>
       <c r="V79">
-        <v>0.2267499953792549</v>
+        <v>0.223842944156444</v>
       </c>
       <c r="W79">
-        <v>0.1181035895400615</v>
+        <v>0.1185476027082983</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9069999815170197</v>
+        <v>0.8953717766257759</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1234427265084879</v>
+        <v>0.1245120926751133</v>
       </c>
       <c r="C80">
-        <v>-35.69468334505291</v>
+        <v>-94.38622005320121</v>
       </c>
       <c r="D80">
-        <v>2840.643612465966</v>
+        <v>2826.332053909241</v>
       </c>
       <c r="E80">
-        <v>227.9404806686871</v>
+        <v>272.3204588201106</v>
       </c>
       <c r="F80">
-        <v>3461.638295811019</v>
+        <v>3506.018273962442</v>
       </c>
       <c r="G80">
         <v>585.3</v>
@@ -7841,37 +7841,37 @@
         <v>473.4</v>
       </c>
       <c r="M80">
-        <v>528.7189214116354</v>
+        <v>535.4973691220411</v>
       </c>
       <c r="N80">
-        <v>-55.31892141163542</v>
+        <v>-62.09736912204107</v>
       </c>
       <c r="O80">
-        <v>-13.82973035290885</v>
+        <v>-15.52434228051027</v>
       </c>
       <c r="P80">
-        <v>-41.48919105872656</v>
+        <v>-46.5730268415308</v>
       </c>
       <c r="Q80">
-        <v>753.1108089412735</v>
+        <v>748.0269731584692</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1407981654364331</v>
+        <v>0.1453218876000728</v>
       </c>
       <c r="T80">
-        <v>1.851691064348423</v>
+        <v>1.939866829317396</v>
       </c>
       <c r="U80">
         <v>0.1527366166625341</v>
       </c>
       <c r="V80">
-        <v>0.223842944156444</v>
+        <v>0.2210094891671219</v>
       </c>
       <c r="W80">
-        <v>0.1185476027082983</v>
+        <v>0.1189803750368329</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8953717766257759</v>
+        <v>0.8840379566684875</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1245120926751133</v>
+        <v>0.1255814588417386</v>
       </c>
       <c r="C81">
-        <v>-94.38622005320121</v>
+        <v>-152.9342724009648</v>
       </c>
       <c r="D81">
-        <v>2826.332053909241</v>
+        <v>2812.163979712901</v>
       </c>
       <c r="E81">
-        <v>272.3204588201106</v>
+        <v>316.7004369715341</v>
       </c>
       <c r="F81">
-        <v>3506.018273962442</v>
+        <v>3550.398252113866</v>
       </c>
       <c r="G81">
         <v>585.3</v>
@@ -7923,37 +7923,37 @@
         <v>473.4</v>
       </c>
       <c r="M81">
-        <v>535.4973691220411</v>
+        <v>542.2758168324467</v>
       </c>
       <c r="N81">
-        <v>-62.09736912204107</v>
+        <v>-68.87581683244673</v>
       </c>
       <c r="O81">
-        <v>-15.52434228051027</v>
+        <v>-17.21895420811168</v>
       </c>
       <c r="P81">
-        <v>-46.5730268415308</v>
+        <v>-51.65686262433505</v>
       </c>
       <c r="Q81">
-        <v>748.0269731584692</v>
+        <v>742.9431373756649</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1453218876000728</v>
+        <v>0.1502979819800764</v>
       </c>
       <c r="T81">
-        <v>1.939866829317396</v>
+        <v>2.036860170783267</v>
       </c>
       <c r="U81">
         <v>0.1527366166625341</v>
       </c>
       <c r="V81">
-        <v>0.2210094891671219</v>
+        <v>0.2182468705525328</v>
       </c>
       <c r="W81">
-        <v>0.1189803750368329</v>
+        <v>0.1194023280571542</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8840379566684875</v>
+        <v>0.8729874822101313</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1255814588417386</v>
+        <v>0.126650825008364</v>
       </c>
       <c r="C82">
-        <v>-152.9342724009648</v>
+        <v>-211.3409874367185</v>
       </c>
       <c r="D82">
-        <v>2812.163979712901</v>
+        <v>2798.137242828571</v>
       </c>
       <c r="E82">
-        <v>316.7004369715341</v>
+        <v>361.0804151229572</v>
       </c>
       <c r="F82">
-        <v>3550.398252113866</v>
+        <v>3594.778230265289</v>
       </c>
       <c r="G82">
         <v>585.3</v>
@@ -8005,37 +8005,37 @@
         <v>473.4</v>
       </c>
       <c r="M82">
-        <v>542.2758168324467</v>
+        <v>549.0542645428523</v>
       </c>
       <c r="N82">
-        <v>-68.87581683244673</v>
+        <v>-75.65426454285227</v>
       </c>
       <c r="O82">
-        <v>-17.21895420811168</v>
+        <v>-18.91356613571307</v>
       </c>
       <c r="P82">
-        <v>-51.65686262433505</v>
+        <v>-56.74069840713921</v>
       </c>
       <c r="Q82">
-        <v>742.9431373756649</v>
+        <v>737.8593015928608</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1502979819800764</v>
+        <v>0.1557978757685015</v>
       </c>
       <c r="T82">
-        <v>2.036860170783267</v>
+        <v>2.144063337666596</v>
       </c>
       <c r="U82">
         <v>0.1527366166625341</v>
       </c>
       <c r="V82">
-        <v>0.2182468705525328</v>
+        <v>0.2155524647432423</v>
       </c>
       <c r="W82">
-        <v>0.1194023280571542</v>
+        <v>0.1198138624843811</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8729874822101313</v>
+        <v>0.8622098589729692</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.126650825008364</v>
+        <v>0.1277201911749893</v>
       </c>
       <c r="C83">
-        <v>-211.3409874367185</v>
+        <v>-269.608469584567</v>
       </c>
       <c r="D83">
-        <v>2798.137242828571</v>
+        <v>2784.249738832146</v>
       </c>
       <c r="E83">
-        <v>361.0804151229572</v>
+        <v>405.4603932743807</v>
       </c>
       <c r="F83">
-        <v>3594.778230265289</v>
+        <v>3639.158208416713</v>
       </c>
       <c r="G83">
         <v>585.3</v>
@@ -8087,37 +8087,37 @@
         <v>473.4</v>
       </c>
       <c r="M83">
-        <v>549.0542645428523</v>
+        <v>555.8327122532578</v>
       </c>
       <c r="N83">
-        <v>-75.65426454285227</v>
+        <v>-82.43271225325782</v>
       </c>
       <c r="O83">
-        <v>-18.91356613571307</v>
+        <v>-20.60817806331445</v>
       </c>
       <c r="P83">
-        <v>-56.74069840713921</v>
+        <v>-61.82453418994336</v>
       </c>
       <c r="Q83">
-        <v>737.8593015928608</v>
+        <v>732.7754658100566</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1557978757685015</v>
+        <v>0.1619088688667516</v>
       </c>
       <c r="T83">
-        <v>2.144063337666596</v>
+        <v>2.263177967536962</v>
       </c>
       <c r="U83">
         <v>0.1527366166625341</v>
       </c>
       <c r="V83">
-        <v>0.2155524647432423</v>
+        <v>0.2129237761488125</v>
       </c>
       <c r="W83">
-        <v>0.1198138624843811</v>
+        <v>0.1202153594865537</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8622098589729692</v>
+        <v>0.8516951045952501</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1277201911749893</v>
+        <v>0.1287895573416147</v>
       </c>
       <c r="C84">
-        <v>-269.608469584567</v>
+        <v>-327.7387816968608</v>
       </c>
       <c r="D84">
-        <v>2784.249738832146</v>
+        <v>2770.499404871275</v>
       </c>
       <c r="E84">
-        <v>405.4603932743807</v>
+        <v>449.8403714258043</v>
       </c>
       <c r="F84">
-        <v>3639.158208416713</v>
+        <v>3683.538186568136</v>
       </c>
       <c r="G84">
         <v>585.3</v>
@@ -8169,37 +8169,37 @@
         <v>473.4</v>
       </c>
       <c r="M84">
-        <v>555.8327122532578</v>
+        <v>562.6111599636635</v>
       </c>
       <c r="N84">
-        <v>-82.43271225325782</v>
+        <v>-89.21115996366348</v>
       </c>
       <c r="O84">
-        <v>-20.60817806331445</v>
+        <v>-22.30278999091587</v>
       </c>
       <c r="P84">
-        <v>-61.82453418994336</v>
+        <v>-66.90836997274761</v>
       </c>
       <c r="Q84">
-        <v>732.7754658100566</v>
+        <v>727.6916300272524</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1619088688667516</v>
+        <v>0.1687388023295017</v>
       </c>
       <c r="T84">
-        <v>2.263177967536962</v>
+        <v>2.396306083274431</v>
       </c>
       <c r="U84">
         <v>0.1527366166625341</v>
       </c>
       <c r="V84">
-        <v>0.2129237761488125</v>
+        <v>0.2103584294482244</v>
       </c>
       <c r="W84">
-        <v>0.1202153594865537</v>
+        <v>0.1206071818621679</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8516951045952501</v>
+        <v>0.8414337177928977</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1287895573416147</v>
+        <v>0.12985892350824</v>
       </c>
       <c r="C85">
-        <v>-327.7387816968608</v>
+        <v>-385.7339460756903</v>
       </c>
       <c r="D85">
-        <v>2770.499404871275</v>
+        <v>2756.884218643869</v>
       </c>
       <c r="E85">
-        <v>449.8403714258043</v>
+        <v>494.2203495772274</v>
       </c>
       <c r="F85">
-        <v>3683.538186568136</v>
+        <v>3727.918164719559</v>
       </c>
       <c r="G85">
         <v>585.3</v>
@@ -8251,37 +8251,37 @@
         <v>473.4</v>
       </c>
       <c r="M85">
-        <v>562.6111599636635</v>
+        <v>569.389607674069</v>
       </c>
       <c r="N85">
-        <v>-89.21115996366348</v>
+        <v>-95.98960767406902</v>
       </c>
       <c r="O85">
-        <v>-22.30278999091587</v>
+        <v>-23.99740191851726</v>
       </c>
       <c r="P85">
-        <v>-66.90836997274761</v>
+        <v>-71.99220575555177</v>
       </c>
       <c r="Q85">
-        <v>727.6916300272524</v>
+        <v>722.6077942444483</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1687388023295017</v>
+        <v>0.1764224774750956</v>
       </c>
       <c r="T85">
-        <v>2.396306083274431</v>
+        <v>2.546075213479084</v>
       </c>
       <c r="U85">
         <v>0.1527366166625341</v>
       </c>
       <c r="V85">
-        <v>0.2103584294482244</v>
+        <v>0.2078541624309836</v>
       </c>
       <c r="W85">
-        <v>0.1206071818621679</v>
+        <v>0.1209896751336009</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8414337177928977</v>
+        <v>0.8314166497239346</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.12985892350824</v>
+        <v>0.1309282896748653</v>
       </c>
       <c r="C86">
-        <v>-385.7339460756898</v>
+        <v>-443.5959454644012</v>
       </c>
       <c r="D86">
-        <v>2756.884218643869</v>
+        <v>2743.402197406581</v>
       </c>
       <c r="E86">
-        <v>494.2203495772269</v>
+        <v>538.6003277286504</v>
       </c>
       <c r="F86">
-        <v>3727.918164719559</v>
+        <v>3772.298142870982</v>
       </c>
       <c r="G86">
         <v>585.3</v>
@@ -8333,37 +8333,37 @@
         <v>473.4</v>
       </c>
       <c r="M86">
-        <v>569.3896076740689</v>
+        <v>576.1680553844745</v>
       </c>
       <c r="N86">
-        <v>-95.98960767406891</v>
+        <v>-102.7680553844746</v>
       </c>
       <c r="O86">
-        <v>-23.99740191851723</v>
+        <v>-25.69201384611864</v>
       </c>
       <c r="P86">
-        <v>-71.99220575555168</v>
+        <v>-77.07604153835592</v>
       </c>
       <c r="Q86">
-        <v>722.6077942444483</v>
+        <v>717.523958461644</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1764224774750955</v>
+        <v>0.1851306426401018</v>
       </c>
       <c r="T86">
-        <v>2.546075213479082</v>
+        <v>2.715813561044353</v>
       </c>
       <c r="U86">
         <v>0.1527366166625341</v>
       </c>
       <c r="V86">
-        <v>0.2078541624309837</v>
+        <v>0.2054088193435603</v>
       </c>
       <c r="W86">
-        <v>0.1209896751336008</v>
+        <v>0.121363168563353</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8314166497239348</v>
+        <v>0.8216352773742414</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1309282896748653</v>
+        <v>0.1319976558414907</v>
       </c>
       <c r="C87">
-        <v>-443.5959454644012</v>
+        <v>-501.3267240101586</v>
       </c>
       <c r="D87">
-        <v>2743.402197406581</v>
+        <v>2730.051397012247</v>
       </c>
       <c r="E87">
-        <v>538.6003277286504</v>
+        <v>582.9803058800735</v>
       </c>
       <c r="F87">
-        <v>3772.298142870982</v>
+        <v>3816.678121022405</v>
       </c>
       <c r="G87">
         <v>585.3</v>
@@ -8415,37 +8415,37 @@
         <v>473.4</v>
       </c>
       <c r="M87">
-        <v>576.1680553844745</v>
+        <v>582.9465030948801</v>
       </c>
       <c r="N87">
-        <v>-102.7680553844746</v>
+        <v>-109.5465030948801</v>
       </c>
       <c r="O87">
-        <v>-25.69201384611864</v>
+        <v>-27.38662577372003</v>
       </c>
       <c r="P87">
-        <v>-77.07604153835592</v>
+        <v>-82.15987732116008</v>
       </c>
       <c r="Q87">
-        <v>717.523958461644</v>
+        <v>712.44012267884</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1851306426401018</v>
+        <v>0.1950828314001091</v>
       </c>
       <c r="T87">
-        <v>2.715813561044353</v>
+        <v>2.909800243976093</v>
       </c>
       <c r="U87">
         <v>0.1527366166625341</v>
       </c>
       <c r="V87">
-        <v>0.2054088193435603</v>
+        <v>0.2030203447000306</v>
       </c>
       <c r="W87">
-        <v>0.121363168563353</v>
+        <v>0.12172797609939</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8216352773742414</v>
+        <v>0.8120813788001223</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1319976558414907</v>
+        <v>0.133067022008116</v>
       </c>
       <c r="C88">
-        <v>-501.3267240101586</v>
+        <v>-558.9281881985462</v>
       </c>
       <c r="D88">
-        <v>2730.051397012247</v>
+        <v>2716.829910975282</v>
       </c>
       <c r="E88">
-        <v>582.9803058800735</v>
+        <v>627.360284031497</v>
       </c>
       <c r="F88">
-        <v>3816.678121022405</v>
+        <v>3861.058099173829</v>
       </c>
       <c r="G88">
         <v>585.3</v>
@@ -8497,37 +8497,37 @@
         <v>473.4</v>
       </c>
       <c r="M88">
-        <v>582.9465030948801</v>
+        <v>589.7249508052856</v>
       </c>
       <c r="N88">
-        <v>-109.5465030948801</v>
+        <v>-116.3249508052857</v>
       </c>
       <c r="O88">
-        <v>-27.38662577372003</v>
+        <v>-29.08123770132141</v>
       </c>
       <c r="P88">
-        <v>-82.15987732116008</v>
+        <v>-87.24371310396424</v>
       </c>
       <c r="Q88">
-        <v>712.44012267884</v>
+        <v>707.3562868960357</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1950828314001091</v>
+        <v>0.2065661261231944</v>
       </c>
       <c r="T88">
-        <v>2.909800243976093</v>
+        <v>3.133631031974255</v>
       </c>
       <c r="U88">
         <v>0.1527366166625341</v>
       </c>
       <c r="V88">
-        <v>0.2030203447000306</v>
+        <v>0.2006867775195705</v>
       </c>
       <c r="W88">
-        <v>0.12172797609939</v>
+        <v>0.1220843972552882</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8120813788001223</v>
+        <v>0.8027471100782819</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.133067022008116</v>
+        <v>0.1828111342232197</v>
       </c>
       <c r="C89">
-        <v>-558.9281881985462</v>
+        <v>-1102.826485258935</v>
       </c>
       <c r="D89">
-        <v>2716.829910975282</v>
+        <v>2217.311592066317</v>
       </c>
       <c r="E89">
-        <v>627.360284031497</v>
+        <v>671.7402621829206</v>
       </c>
       <c r="F89">
-        <v>3861.058099173829</v>
+        <v>3905.438077325252</v>
       </c>
       <c r="G89">
         <v>585.3</v>
@@ -8579,45 +8579,45 @@
         <v>473.4</v>
       </c>
       <c r="M89">
-        <v>589.7249508052856</v>
+        <v>807.3970546912549</v>
       </c>
       <c r="N89">
-        <v>-116.3249508052857</v>
+        <v>-333.9970546912549</v>
       </c>
       <c r="O89">
-        <v>-29.08123770132141</v>
+        <v>-83.49926367281373</v>
       </c>
       <c r="P89">
-        <v>-87.24371310396424</v>
+        <v>-250.4977910184412</v>
       </c>
       <c r="Q89">
-        <v>707.3562868960357</v>
+        <v>544.1022089815589</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2065661261231944</v>
+        <v>0.2295861870374467</v>
       </c>
       <c r="T89">
-        <v>3.133631031974255</v>
+        <v>3.582334866409878</v>
       </c>
       <c r="U89">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.2006867775195705</v>
+        <v>0.1465821547308672</v>
       </c>
       <c r="W89">
-        <v>0.1220843972552882</v>
+        <v>0.1764327179303705</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8027471100782819</v>
+        <v>0.5863286189234689</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1828111342232197</v>
+        <v>0.184420500389845</v>
       </c>
       <c r="C90">
-        <v>-1102.826485258935</v>
+        <v>-1160.317987099972</v>
       </c>
       <c r="D90">
-        <v>2217.311592066317</v>
+        <v>2204.200068376703</v>
       </c>
       <c r="E90">
-        <v>671.7402621829206</v>
+        <v>716.1202403343436</v>
       </c>
       <c r="F90">
-        <v>3905.438077325252</v>
+        <v>3949.818055476675</v>
       </c>
       <c r="G90">
         <v>585.3</v>
@@ -8661,37 +8661,37 @@
         <v>473.4</v>
       </c>
       <c r="M90">
-        <v>807.3970546912549</v>
+        <v>816.5720212218373</v>
       </c>
       <c r="N90">
-        <v>-333.9970546912549</v>
+        <v>-343.1720212218373</v>
       </c>
       <c r="O90">
-        <v>-83.49926367281373</v>
+        <v>-85.79300530545933</v>
       </c>
       <c r="P90">
-        <v>-250.4977910184412</v>
+        <v>-257.379015916378</v>
       </c>
       <c r="Q90">
-        <v>544.1022089815589</v>
+        <v>537.2209840836221</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2295861870374467</v>
+        <v>0.2462940222226691</v>
       </c>
       <c r="T90">
-        <v>3.582334866409878</v>
+        <v>3.90800167244714</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.1465821547308672</v>
+        <v>0.1449351642282732</v>
       </c>
       <c r="W90">
-        <v>0.1764327179303705</v>
+        <v>0.1767732111745521</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5863286189234689</v>
+        <v>0.579740656913093</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.184420500389845</v>
+        <v>0.1860298665564704</v>
       </c>
       <c r="C91">
-        <v>-1160.317987099972</v>
+        <v>-1217.655336975628</v>
       </c>
       <c r="D91">
-        <v>2204.200068376703</v>
+        <v>2191.242696652471</v>
       </c>
       <c r="E91">
-        <v>716.1202403343436</v>
+        <v>760.5002184857672</v>
       </c>
       <c r="F91">
-        <v>3949.818055476675</v>
+        <v>3994.198033628099</v>
       </c>
       <c r="G91">
         <v>585.3</v>
@@ -8743,37 +8743,37 @@
         <v>473.4</v>
       </c>
       <c r="M91">
-        <v>816.5720212218373</v>
+        <v>825.7469877524197</v>
       </c>
       <c r="N91">
-        <v>-343.1720212218373</v>
+        <v>-352.3469877524197</v>
       </c>
       <c r="O91">
-        <v>-85.79300530545933</v>
+        <v>-88.08674693810494</v>
       </c>
       <c r="P91">
-        <v>-257.379015916378</v>
+        <v>-264.2602408143148</v>
       </c>
       <c r="Q91">
-        <v>537.2209840836221</v>
+        <v>530.3397591856852</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2462940222226691</v>
+        <v>0.266343424444936</v>
       </c>
       <c r="T91">
-        <v>3.90800167244714</v>
+        <v>4.298801839691854</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.1449351642282732</v>
+        <v>0.1433247735146257</v>
       </c>
       <c r="W91">
-        <v>0.1767732111745521</v>
+        <v>0.1771061379021964</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.579740656913093</v>
+        <v>0.573299094058503</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1860298665564704</v>
+        <v>0.1876392327230957</v>
       </c>
       <c r="C92">
-        <v>-1217.655336975628</v>
+        <v>-1274.841237541493</v>
       </c>
       <c r="D92">
-        <v>2191.242696652471</v>
+        <v>2178.436774238029</v>
       </c>
       <c r="E92">
-        <v>760.5002184857672</v>
+        <v>804.8801966371902</v>
       </c>
       <c r="F92">
-        <v>3994.198033628099</v>
+        <v>4038.578011779522</v>
       </c>
       <c r="G92">
         <v>585.3</v>
@@ -8825,37 +8825,37 @@
         <v>473.4</v>
       </c>
       <c r="M92">
-        <v>825.7469877524197</v>
+        <v>834.9219542830022</v>
       </c>
       <c r="N92">
-        <v>-352.3469877524197</v>
+        <v>-361.5219542830022</v>
       </c>
       <c r="O92">
-        <v>-88.08674693810494</v>
+        <v>-90.38048857075054</v>
       </c>
       <c r="P92">
-        <v>-264.2602408143148</v>
+        <v>-271.1414657122516</v>
       </c>
       <c r="Q92">
-        <v>530.3397591856852</v>
+        <v>523.4585342877484</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.266343424444936</v>
+        <v>0.2908482493832623</v>
       </c>
       <c r="T92">
-        <v>4.298801839691854</v>
+        <v>4.776446488546505</v>
       </c>
       <c r="U92">
         <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.1433247735146257</v>
+        <v>0.141749776003476</v>
       </c>
       <c r="W92">
-        <v>0.1771061379021964</v>
+        <v>0.1774317475589034</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.573299094058503</v>
+        <v>0.5669991040139041</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1876392327230957</v>
+        <v>0.189248598889721</v>
       </c>
       <c r="C93">
-        <v>-1274.841237541493</v>
+        <v>-1331.878328641481</v>
       </c>
       <c r="D93">
-        <v>2178.436774238029</v>
+        <v>2165.779661289464</v>
       </c>
       <c r="E93">
-        <v>804.8801966371902</v>
+        <v>849.2601747886138</v>
       </c>
       <c r="F93">
-        <v>4038.578011779522</v>
+        <v>4082.957989930946</v>
       </c>
       <c r="G93">
         <v>585.3</v>
@@ -8907,37 +8907,37 @@
         <v>473.4</v>
       </c>
       <c r="M93">
-        <v>834.9219542830022</v>
+        <v>844.0969208135847</v>
       </c>
       <c r="N93">
-        <v>-361.5219542830022</v>
+        <v>-370.6969208135847</v>
       </c>
       <c r="O93">
-        <v>-90.38048857075054</v>
+        <v>-92.67423020339618</v>
       </c>
       <c r="P93">
-        <v>-271.1414657122516</v>
+        <v>-278.0226906101885</v>
       </c>
       <c r="Q93">
-        <v>523.4585342877484</v>
+        <v>516.5773093898115</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2908482493832623</v>
+        <v>0.3214792805561701</v>
       </c>
       <c r="T93">
-        <v>4.776446488546505</v>
+        <v>5.373502299614819</v>
       </c>
       <c r="U93">
         <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.141749776003476</v>
+        <v>0.1402090175686556</v>
       </c>
       <c r="W93">
-        <v>0.1774317475589034</v>
+        <v>0.1777502787448124</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5669991040139041</v>
+        <v>0.5608360702746225</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.189248598889721</v>
+        <v>0.1908579650563464</v>
       </c>
       <c r="C94">
-        <v>-1331.878328641481</v>
+        <v>-1388.769189122026</v>
       </c>
       <c r="D94">
-        <v>2165.779661289464</v>
+        <v>2153.268778960344</v>
       </c>
       <c r="E94">
-        <v>849.2601747886138</v>
+        <v>893.6401529400373</v>
       </c>
       <c r="F94">
-        <v>4082.957989930946</v>
+        <v>4127.337968082369</v>
       </c>
       <c r="G94">
         <v>585.3</v>
@@ -8989,37 +8989,37 @@
         <v>473.4</v>
       </c>
       <c r="M94">
-        <v>844.0969208135847</v>
+        <v>853.2718873441671</v>
       </c>
       <c r="N94">
-        <v>-370.6969208135847</v>
+        <v>-379.8718873441671</v>
       </c>
       <c r="O94">
-        <v>-92.67423020339618</v>
+        <v>-94.96797183604178</v>
       </c>
       <c r="P94">
-        <v>-278.0226906101885</v>
+        <v>-284.9039155081254</v>
       </c>
       <c r="Q94">
-        <v>516.5773093898115</v>
+        <v>509.6960844918747</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3214792805561701</v>
+        <v>0.3608620349213373</v>
       </c>
       <c r="T94">
-        <v>5.373502299614819</v>
+        <v>6.14114548527408</v>
       </c>
       <c r="U94">
         <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.1402090175686556</v>
+        <v>0.1387013937238314</v>
       </c>
       <c r="W94">
-        <v>0.1777502787448124</v>
+        <v>0.1780619597976912</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5608360702746225</v>
+        <v>0.5548055748953253</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1908579650563464</v>
+        <v>0.1924673312229717</v>
       </c>
       <c r="C95">
-        <v>-1388.769189122026</v>
+        <v>-1445.51633858375</v>
       </c>
       <c r="D95">
-        <v>2153.268778960344</v>
+        <v>2140.901607650042</v>
       </c>
       <c r="E95">
-        <v>893.6401529400373</v>
+        <v>938.0201310914608</v>
       </c>
       <c r="F95">
-        <v>4127.337968082369</v>
+        <v>4171.717946233793</v>
       </c>
       <c r="G95">
         <v>585.3</v>
@@ -9071,37 +9071,37 @@
         <v>473.4</v>
       </c>
       <c r="M95">
-        <v>853.2718873441671</v>
+        <v>862.4468538747496</v>
       </c>
       <c r="N95">
-        <v>-379.8718873441671</v>
+        <v>-389.0468538747497</v>
       </c>
       <c r="O95">
-        <v>-94.96797183604178</v>
+        <v>-97.26171346868742</v>
       </c>
       <c r="P95">
-        <v>-284.9039155081254</v>
+        <v>-291.7851404060623</v>
       </c>
       <c r="Q95">
-        <v>509.6960844918747</v>
+        <v>502.8148595939377</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3608620349213373</v>
+        <v>0.4133723740748937</v>
       </c>
       <c r="T95">
-        <v>6.14114548527408</v>
+        <v>7.164669732819763</v>
       </c>
       <c r="U95">
         <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.1387013937238314</v>
+        <v>0.1372258469820885</v>
       </c>
       <c r="W95">
-        <v>0.1780619597976912</v>
+        <v>0.1783670093388065</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5548055748953253</v>
+        <v>0.5489033879283538</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1924673312229717</v>
+        <v>0.1940766973895971</v>
       </c>
       <c r="C96">
-        <v>-1445.51633858375</v>
+        <v>-1502.122239073135</v>
       </c>
       <c r="D96">
-        <v>2140.901607650042</v>
+        <v>2128.67568531208</v>
       </c>
       <c r="E96">
-        <v>938.0201310914608</v>
+        <v>982.4001092428834</v>
       </c>
       <c r="F96">
-        <v>4171.717946233793</v>
+        <v>4216.097924385215</v>
       </c>
       <c r="G96">
         <v>585.3</v>
@@ -9153,37 +9153,37 @@
         <v>473.4</v>
       </c>
       <c r="M96">
-        <v>862.4468538747496</v>
+        <v>871.621820405332</v>
       </c>
       <c r="N96">
-        <v>-389.0468538747497</v>
+        <v>-398.221820405332</v>
       </c>
       <c r="O96">
-        <v>-97.26171346868742</v>
+        <v>-99.555455101333</v>
       </c>
       <c r="P96">
-        <v>-291.7851404060623</v>
+        <v>-298.666365303999</v>
       </c>
       <c r="Q96">
-        <v>502.8148595939377</v>
+        <v>495.933634696001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4133723740748937</v>
+        <v>0.4868868488898726</v>
       </c>
       <c r="T96">
-        <v>7.164669732819763</v>
+        <v>8.597603679383719</v>
       </c>
       <c r="U96">
         <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.1372258469820885</v>
+        <v>0.135781364382277</v>
       </c>
       <c r="W96">
-        <v>0.1783670093388065</v>
+        <v>0.1786656367843194</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5489033879283538</v>
+        <v>0.543125457529108</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1940766973895971</v>
+        <v>0.1956860635562224</v>
       </c>
       <c r="C97">
-        <v>-1502.122239073135</v>
+        <v>-1558.589296716538</v>
       </c>
       <c r="D97">
-        <v>2128.67568531208</v>
+        <v>2116.5886058201</v>
       </c>
       <c r="E97">
-        <v>982.4001092428834</v>
+        <v>1026.780087394307</v>
       </c>
       <c r="F97">
-        <v>4216.097924385215</v>
+        <v>4260.477902536639</v>
       </c>
       <c r="G97">
         <v>585.3</v>
@@ -9235,37 +9235,37 @@
         <v>473.4</v>
       </c>
       <c r="M97">
-        <v>871.621820405332</v>
+        <v>880.7967869359144</v>
       </c>
       <c r="N97">
-        <v>-398.221820405332</v>
+        <v>-407.3967869359144</v>
       </c>
       <c r="O97">
-        <v>-99.555455101333</v>
+        <v>-101.8491967339786</v>
       </c>
       <c r="P97">
-        <v>-298.666365303999</v>
+        <v>-305.5475902019358</v>
       </c>
       <c r="Q97">
-        <v>495.933634696001</v>
+        <v>489.0524097980642</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4868868488898726</v>
+        <v>0.5971585611123409</v>
       </c>
       <c r="T97">
-        <v>8.597603679383719</v>
+        <v>10.74700459922965</v>
       </c>
       <c r="U97">
         <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.135781364382277</v>
+        <v>0.1343669751699616</v>
       </c>
       <c r="W97">
-        <v>0.1786656367843194</v>
+        <v>0.1789580428247175</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.543125457529108</v>
+        <v>0.5374679006798465</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1956860635562224</v>
+        <v>0.1972954297228477</v>
       </c>
       <c r="C98">
-        <v>-1558.589296716538</v>
+        <v>-1614.91986329886</v>
       </c>
       <c r="D98">
-        <v>2116.5886058201</v>
+        <v>2104.638017389202</v>
       </c>
       <c r="E98">
-        <v>1026.780087394307</v>
+        <v>1071.160065545731</v>
       </c>
       <c r="F98">
-        <v>4260.477902536639</v>
+        <v>4304.857880688062</v>
       </c>
       <c r="G98">
         <v>585.3</v>
@@ -9317,37 +9317,37 @@
         <v>473.4</v>
       </c>
       <c r="M98">
-        <v>880.7967869359144</v>
+        <v>889.9717534664969</v>
       </c>
       <c r="N98">
-        <v>-407.3967869359144</v>
+        <v>-416.5717534664969</v>
       </c>
       <c r="O98">
-        <v>-101.8491967339786</v>
+        <v>-104.1429383666242</v>
       </c>
       <c r="P98">
-        <v>-305.5475902019358</v>
+        <v>-312.4288150998727</v>
       </c>
       <c r="Q98">
-        <v>489.0524097980642</v>
+        <v>482.1711849001273</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5971585611123394</v>
+        <v>0.780944748149786</v>
       </c>
       <c r="T98">
-        <v>10.74700459922962</v>
+        <v>14.3293394656395</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.1343669751699616</v>
+        <v>0.1329817486218177</v>
       </c>
       <c r="W98">
-        <v>0.1789580428247175</v>
+        <v>0.1792444198745919</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5374679006798465</v>
+        <v>0.5319269944872707</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1972954297228477</v>
+        <v>0.1989047958894731</v>
       </c>
       <c r="C99">
-        <v>-1614.91986329886</v>
+        <v>-1671.116237789037</v>
       </c>
       <c r="D99">
-        <v>2104.638017389202</v>
+        <v>2092.821621050448</v>
       </c>
       <c r="E99">
-        <v>1071.160065545731</v>
+        <v>1115.540043697153</v>
       </c>
       <c r="F99">
-        <v>4304.857880688062</v>
+        <v>4349.237858839485</v>
       </c>
       <c r="G99">
         <v>585.3</v>
@@ -9399,37 +9399,37 @@
         <v>473.4</v>
       </c>
       <c r="M99">
-        <v>889.9717534664969</v>
+        <v>899.1467199970791</v>
       </c>
       <c r="N99">
-        <v>-416.5717534664969</v>
+        <v>-425.7467199970791</v>
       </c>
       <c r="O99">
-        <v>-104.1429383666242</v>
+        <v>-106.4366799992698</v>
       </c>
       <c r="P99">
-        <v>-312.4288150998727</v>
+        <v>-319.3100399978093</v>
       </c>
       <c r="Q99">
-        <v>482.1711849001273</v>
+        <v>475.2899600021907</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.780944748149786</v>
+        <v>1.148517122224679</v>
       </c>
       <c r="T99">
-        <v>14.3293394656395</v>
+        <v>21.49400919845925</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.1329817486218177</v>
+        <v>0.1316247920032277</v>
       </c>
       <c r="W99">
-        <v>0.1792444198745919</v>
+        <v>0.179524952494877</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5319269944872707</v>
+        <v>0.526499168012911</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1989047958894731</v>
+        <v>0.2005141620560984</v>
       </c>
       <c r="C100">
-        <v>-1671.116237789037</v>
+        <v>-1727.180667814425</v>
       </c>
       <c r="D100">
-        <v>2092.821621050448</v>
+        <v>2081.137169176484</v>
       </c>
       <c r="E100">
-        <v>1115.540043697153</v>
+        <v>1159.920021848577</v>
       </c>
       <c r="F100">
-        <v>4349.237858839485</v>
+        <v>4393.617836990908</v>
       </c>
       <c r="G100">
         <v>585.3</v>
@@ -9481,37 +9481,37 @@
         <v>473.4</v>
       </c>
       <c r="M100">
-        <v>899.1467199970791</v>
+        <v>908.3216865276617</v>
       </c>
       <c r="N100">
-        <v>-425.7467199970791</v>
+        <v>-434.9216865276617</v>
       </c>
       <c r="O100">
-        <v>-106.4366799992698</v>
+        <v>-108.7304216319154</v>
       </c>
       <c r="P100">
-        <v>-319.3100399978093</v>
+        <v>-326.1912648957463</v>
       </c>
       <c r="Q100">
-        <v>475.2899600021907</v>
+        <v>468.4087351042538</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.148517122224679</v>
+        <v>2.251234244449358</v>
       </c>
       <c r="T100">
-        <v>21.49400919845925</v>
+        <v>42.9880183969185</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.1316247920032277</v>
+        <v>0.1302952486496598</v>
       </c>
       <c r="W100">
-        <v>0.179524952494877</v>
+        <v>0.1797998177894998</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.526499168012911</v>
+        <v>0.5211809945986391</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2005141620560984</v>
-      </c>
-      <c r="C101">
-        <v>-1727.180667814425</v>
-      </c>
-      <c r="D101">
-        <v>2081.137169176484</v>
-      </c>
-      <c r="E101">
-        <v>1159.920021848577</v>
-      </c>
-      <c r="F101">
-        <v>4393.617836990908</v>
-      </c>
-      <c r="G101">
-        <v>585.3</v>
-      </c>
-      <c r="H101">
-        <v>1204.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1268</v>
-      </c>
-      <c r="K101">
-        <v>794.6</v>
-      </c>
-      <c r="L101">
-        <v>473.4</v>
-      </c>
-      <c r="M101">
-        <v>908.3216865276617</v>
-      </c>
-      <c r="N101">
-        <v>-434.9216865276617</v>
-      </c>
-      <c r="O101">
-        <v>-108.7304216319154</v>
-      </c>
-      <c r="P101">
-        <v>-326.1912648957463</v>
-      </c>
-      <c r="Q101">
-        <v>468.4087351042538</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.251234244449358</v>
-      </c>
-      <c r="T101">
-        <v>42.9880183969185</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.1302952486496598</v>
-      </c>
-      <c r="W101">
-        <v>0.1797998177894998</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5211809945986391</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
